--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123417364</v>
+        <v>123406533</v>
       </c>
       <c r="B2" t="n">
-        <v>78769</v>
+        <v>95914</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620549</v>
+        <v>620593</v>
       </c>
       <c r="R2" t="n">
-        <v>6648158</v>
+        <v>6648325</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,9 +752,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,7 +797,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123410978</v>
+        <v>123407003</v>
       </c>
       <c r="B3" t="n">
         <v>98368</v>
@@ -821,17 +837,17 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620617</v>
+        <v>620581</v>
       </c>
       <c r="R3" t="n">
-        <v>6648344</v>
+        <v>6648381</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,7 +881,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ca 30 bladrosetter</t>
+          <t>Mer än 35 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123409471</v>
+        <v>123404593</v>
       </c>
       <c r="B4" t="n">
-        <v>74805</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,41 +921,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6426</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620802</v>
+        <v>620575</v>
       </c>
       <c r="R4" t="n">
-        <v>6648510</v>
+        <v>6648228</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -981,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -990,7 +1008,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1009,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123398368</v>
+        <v>123406069</v>
       </c>
       <c r="B5" t="n">
-        <v>56683</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,46 +1038,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620347</v>
+        <v>620600</v>
       </c>
       <c r="R5" t="n">
-        <v>6648171</v>
+        <v>6648303</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1092,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1102,12 +1111,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Två stycken stöttes upp från samma ställe, flög tillsammans ca 20 meter söderut.</t>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123399110</v>
+        <v>123401959</v>
       </c>
       <c r="B6" t="n">
-        <v>95032</v>
+        <v>78414</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1146,25 +1155,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1174,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620370</v>
+        <v>620544</v>
       </c>
       <c r="R6" t="n">
-        <v>6648255</v>
+        <v>6648151</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1209,7 +1218,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1219,7 +1228,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1246,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123408488</v>
+        <v>123398864</v>
       </c>
       <c r="B7" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,38 +1267,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620679</v>
+        <v>620370</v>
       </c>
       <c r="R7" t="n">
-        <v>6648540</v>
+        <v>6648255</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1321,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,12 +1348,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>2 krokar på tallåga</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1363,10 +1380,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123404274</v>
+        <v>123417137</v>
       </c>
       <c r="B8" t="n">
-        <v>78414</v>
+        <v>79387</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1379,21 +1396,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>353</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1402,17 +1419,17 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620569</v>
+        <v>620541</v>
       </c>
       <c r="R8" t="n">
-        <v>6648238</v>
+        <v>6648142</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1439,19 +1456,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,7 +1486,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123407003</v>
+        <v>123417333</v>
       </c>
       <c r="B9" t="n">
         <v>98368</v>
@@ -1523,13 +1530,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620581</v>
+        <v>620596</v>
       </c>
       <c r="R9" t="n">
-        <v>6648381</v>
+        <v>6648322</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1563,7 +1570,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Mer än 35 bladrosetter</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123410527</v>
+        <v>123402052</v>
       </c>
       <c r="B10" t="n">
-        <v>98368</v>
+        <v>79387</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1603,42 +1610,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620777</v>
+        <v>620544</v>
       </c>
       <c r="R10" t="n">
-        <v>6648494</v>
+        <v>6648151</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1670,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1680,12 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ca 10 bladroseter</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1694,7 +1692,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1713,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123408853</v>
+        <v>123397574</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1725,31 +1722,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1757,10 +1758,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620759</v>
+        <v>620364</v>
       </c>
       <c r="R11" t="n">
-        <v>6648492</v>
+        <v>6648233</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1792,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1802,12 +1803,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1816,7 +1817,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1835,7 +1835,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123407548</v>
+        <v>123411112</v>
       </c>
       <c r="B12" t="n">
         <v>98368</v>
@@ -1871,14 +1871,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
         <v>620609</v>
       </c>
       <c r="R12" t="n">
-        <v>6648383</v>
+        <v>6648334</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,10 +1952,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123406069</v>
+        <v>123408009</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,38 +1964,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620600</v>
+        <v>620718</v>
       </c>
       <c r="R13" t="n">
-        <v>6648303</v>
+        <v>6648486</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2027,7 +2035,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2037,12 +2045,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2069,10 +2072,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123404593</v>
+        <v>123404576</v>
       </c>
       <c r="B14" t="n">
-        <v>57634</v>
+        <v>56691</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2081,33 +2084,36 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bålmyran, norr om , Upl</t>
@@ -2149,7 +2155,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2159,7 +2165,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,10 +2197,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123405636</v>
+        <v>123400078</v>
       </c>
       <c r="B15" t="n">
-        <v>95032</v>
+        <v>74678</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2202,34 +2213,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>6428</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620633</v>
+        <v>620467</v>
       </c>
       <c r="R15" t="n">
-        <v>6648297</v>
+        <v>6648236</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2261,7 +2275,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2271,7 +2285,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På granbark i fuktig del av skogen</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2280,6 +2299,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2298,10 +2318,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123411227</v>
+        <v>123405636</v>
       </c>
       <c r="B16" t="n">
-        <v>98368</v>
+        <v>95032</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2310,42 +2330,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620502</v>
+        <v>620633</v>
       </c>
       <c r="R16" t="n">
-        <v>6648313</v>
+        <v>6648297</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2377,7 +2393,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,12 +2403,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,7 +2412,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2420,10 +2430,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123398864</v>
+        <v>123408853</v>
       </c>
       <c r="B17" t="n">
-        <v>56691</v>
+        <v>98368</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2432,46 +2442,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620370</v>
+        <v>620759</v>
       </c>
       <c r="R17" t="n">
-        <v>6648255</v>
+        <v>6648492</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2503,7 +2509,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2513,12 +2519,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2 krokar på tallåga</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2527,6 +2533,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2545,10 +2552,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123417137</v>
+        <v>123398368</v>
       </c>
       <c r="B18" t="n">
-        <v>79387</v>
+        <v>56683</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2561,26 +2568,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2588,13 +2600,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620541</v>
+        <v>620347</v>
       </c>
       <c r="R18" t="n">
-        <v>6648142</v>
+        <v>6648171</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2621,18 +2633,32 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Två stycken stöttes upp från samma ställe, flög tillsammans ca 20 meter söderut.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2651,7 +2677,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123411112</v>
+        <v>123405294</v>
       </c>
       <c r="B19" t="n">
         <v>98368</v>
@@ -2687,14 +2713,14 @@
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620609</v>
+        <v>620610</v>
       </c>
       <c r="R19" t="n">
-        <v>6648334</v>
+        <v>6648299</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2726,7 +2752,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2736,12 +2762,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>3 bladrosetter</t>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2768,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123402991</v>
+        <v>123410527</v>
       </c>
       <c r="B20" t="n">
-        <v>56691</v>
+        <v>98368</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2780,49 +2806,45 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620551</v>
+        <v>620777</v>
       </c>
       <c r="R20" t="n">
-        <v>6648134</v>
+        <v>6648494</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2851,7 +2873,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2861,7 +2883,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2870,6 +2897,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2888,10 +2916,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123402052</v>
+        <v>123399558</v>
       </c>
       <c r="B21" t="n">
-        <v>79387</v>
+        <v>56691</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2900,38 +2928,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620544</v>
+        <v>620398</v>
       </c>
       <c r="R21" t="n">
-        <v>6648151</v>
+        <v>6648248</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2963,7 +2999,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2973,7 +3009,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3000,10 +3036,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123399558</v>
+        <v>123408488</v>
       </c>
       <c r="B22" t="n">
-        <v>56691</v>
+        <v>98368</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3012,46 +3048,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620398</v>
+        <v>620679</v>
       </c>
       <c r="R22" t="n">
-        <v>6648248</v>
+        <v>6648540</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3083,7 +3111,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3093,7 +3121,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3120,10 +3153,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123408009</v>
+        <v>123417364</v>
       </c>
       <c r="B23" t="n">
-        <v>56691</v>
+        <v>78769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3132,49 +3165,44 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620718</v>
+        <v>620549</v>
       </c>
       <c r="R23" t="n">
-        <v>6648486</v>
+        <v>6648158</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3201,27 +3229,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3240,10 +3259,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123404576</v>
+        <v>123404274</v>
       </c>
       <c r="B24" t="n">
-        <v>56691</v>
+        <v>78414</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3252,35 +3271,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3288,10 +3302,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620575</v>
+        <v>620569</v>
       </c>
       <c r="R24" t="n">
-        <v>6648228</v>
+        <v>6648238</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3323,7 +3337,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3333,12 +3347,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3347,6 +3356,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3365,10 +3375,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123397574</v>
+        <v>123410978</v>
       </c>
       <c r="B25" t="n">
-        <v>56691</v>
+        <v>98368</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3377,46 +3387,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620364</v>
+        <v>620617</v>
       </c>
       <c r="R25" t="n">
-        <v>6648233</v>
+        <v>6648344</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3446,24 +3452,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>5 krokar på höjd</t>
+          <t>Ca 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3472,6 +3468,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3490,7 +3487,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123405294</v>
+        <v>123411227</v>
       </c>
       <c r="B26" t="n">
         <v>98368</v>
@@ -3524,16 +3521,20 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620610</v>
+        <v>620502</v>
       </c>
       <c r="R26" t="n">
-        <v>6648299</v>
+        <v>6648313</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3565,7 +3566,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3575,12 +3576,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3589,6 +3590,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3607,10 +3609,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123400078</v>
+        <v>123409471</v>
       </c>
       <c r="B27" t="n">
-        <v>74678</v>
+        <v>74805</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3623,21 +3625,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6428</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3646,14 +3648,14 @@
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620467</v>
+        <v>620802</v>
       </c>
       <c r="R27" t="n">
-        <v>6648236</v>
+        <v>6648510</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3685,7 +3687,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3695,12 +3697,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:41</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På granbark i fuktig del av skogen</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3728,10 +3725,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123406533</v>
+        <v>123407548</v>
       </c>
       <c r="B28" t="n">
-        <v>95914</v>
+        <v>98368</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3740,42 +3737,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620593</v>
+        <v>620609</v>
       </c>
       <c r="R28" t="n">
-        <v>6648325</v>
+        <v>6648383</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3807,7 +3800,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3817,12 +3810,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På understa lågan</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3831,7 +3824,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3850,10 +3842,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123417333</v>
+        <v>123402991</v>
       </c>
       <c r="B29" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3862,31 +3854,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3894,13 +3890,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620596</v>
+        <v>620551</v>
       </c>
       <c r="R29" t="n">
-        <v>6648322</v>
+        <v>6648134</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3927,14 +3923,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>13 bladrosetter</t>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3943,7 +3944,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3962,10 +3962,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123401959</v>
+        <v>123399110</v>
       </c>
       <c r="B30" t="n">
-        <v>78414</v>
+        <v>95032</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3974,25 +3974,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4002,10 +4002,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620544</v>
+        <v>620370</v>
       </c>
       <c r="R30" t="n">
-        <v>6648151</v>
+        <v>6648255</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123406533</v>
+        <v>123399110</v>
       </c>
       <c r="B2" t="n">
-        <v>95914</v>
+        <v>95034</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620593</v>
+        <v>620370</v>
       </c>
       <c r="R2" t="n">
-        <v>6648325</v>
+        <v>6648255</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På understa lågan</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123407003</v>
+        <v>123408853</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -841,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620581</v>
+        <v>620759</v>
       </c>
       <c r="R3" t="n">
-        <v>6648381</v>
+        <v>6648492</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,14 +864,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mer än 35 bladrosetter</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123404593</v>
+        <v>123407003</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>98370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,46 +921,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620575</v>
+        <v>620581</v>
       </c>
       <c r="R4" t="n">
-        <v>6648228</v>
+        <v>6648381</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,19 +986,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:17</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Mer än 35 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,6 +1002,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1026,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406069</v>
+        <v>123408488</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1066,10 +1061,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620600</v>
+        <v>620679</v>
       </c>
       <c r="R5" t="n">
-        <v>6648303</v>
+        <v>6648540</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,12 +1106,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>12 bladrosetter</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1143,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123401959</v>
+        <v>123404274</v>
       </c>
       <c r="B6" t="n">
-        <v>78414</v>
+        <v>78416</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1177,16 +1172,19 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620544</v>
+        <v>620569</v>
       </c>
       <c r="R6" t="n">
-        <v>6648151</v>
+        <v>6648238</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1218,7 +1216,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1228,7 +1226,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,6 +1235,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1255,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123398864</v>
+        <v>123417364</v>
       </c>
       <c r="B7" t="n">
-        <v>56691</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1267,35 +1266,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1303,13 +1297,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620370</v>
+        <v>620549</v>
       </c>
       <c r="R7" t="n">
-        <v>6648255</v>
+        <v>6648158</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1336,32 +1330,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2 krokar på tallåga</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1380,10 +1360,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123417137</v>
+        <v>123408009</v>
       </c>
       <c r="B8" t="n">
-        <v>79387</v>
+        <v>56691</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,44 +1372,49 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620541</v>
+        <v>620718</v>
       </c>
       <c r="R8" t="n">
-        <v>6648142</v>
+        <v>6648486</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1456,18 +1441,27 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:05</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1486,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123417333</v>
+        <v>123402991</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,31 +1492,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1530,13 +1528,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620596</v>
+        <v>620551</v>
       </c>
       <c r="R9" t="n">
-        <v>6648322</v>
+        <v>6648134</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1563,14 +1561,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>13 bladrosetter</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,7 +1582,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1598,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123402052</v>
+        <v>123398368</v>
       </c>
       <c r="B10" t="n">
-        <v>79387</v>
+        <v>56683</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,34 +1616,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620544</v>
+        <v>620347</v>
       </c>
       <c r="R10" t="n">
-        <v>6648151</v>
+        <v>6648171</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1673,7 +1683,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1693,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Två stycken stöttes upp från samma ställe, flög tillsammans ca 20 meter söderut.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123397574</v>
+        <v>123409471</v>
       </c>
       <c r="B11" t="n">
-        <v>56691</v>
+        <v>74805</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,31 +1741,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1758,10 +1768,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620364</v>
+        <v>620802</v>
       </c>
       <c r="R11" t="n">
-        <v>6648233</v>
+        <v>6648510</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1793,7 +1803,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1813,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>5 krokar på höjd</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,6 +1822,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1835,10 +1841,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123411112</v>
+        <v>123406533</v>
       </c>
       <c r="B12" t="n">
-        <v>98368</v>
+        <v>95916</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,38 +1853,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620609</v>
+        <v>620593</v>
       </c>
       <c r="R12" t="n">
-        <v>6648334</v>
+        <v>6648325</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1910,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1920,12 +1930,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>3 bladrosetter</t>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1934,6 +1944,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1952,10 +1963,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408009</v>
+        <v>123405294</v>
       </c>
       <c r="B13" t="n">
-        <v>56691</v>
+        <v>98370</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1964,46 +1975,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620718</v>
+        <v>620610</v>
       </c>
       <c r="R13" t="n">
-        <v>6648486</v>
+        <v>6648299</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2035,7 +2038,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2045,7 +2048,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,10 +2080,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123404576</v>
+        <v>123411227</v>
       </c>
       <c r="B14" t="n">
-        <v>56691</v>
+        <v>98370</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2084,46 +2092,42 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620575</v>
+        <v>620502</v>
       </c>
       <c r="R14" t="n">
-        <v>6648228</v>
+        <v>6648313</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2155,7 +2159,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2165,12 +2169,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,6 +2183,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2197,10 +2202,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123400078</v>
+        <v>123411112</v>
       </c>
       <c r="B15" t="n">
-        <v>74678</v>
+        <v>98370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2209,41 +2214,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620467</v>
+        <v>620609</v>
       </c>
       <c r="R15" t="n">
-        <v>6648236</v>
+        <v>6648334</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2275,7 +2277,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2285,12 +2287,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På granbark i fuktig del av skogen</t>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2299,7 +2301,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2318,10 +2319,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123405636</v>
+        <v>123407548</v>
       </c>
       <c r="B16" t="n">
-        <v>95032</v>
+        <v>98370</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2330,25 +2331,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2358,10 +2359,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620633</v>
+        <v>620609</v>
       </c>
       <c r="R16" t="n">
-        <v>6648297</v>
+        <v>6648383</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2393,7 +2394,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2403,7 +2404,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2430,10 +2436,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123408853</v>
+        <v>123401959</v>
       </c>
       <c r="B17" t="n">
-        <v>98368</v>
+        <v>78416</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2442,42 +2448,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620759</v>
+        <v>620544</v>
       </c>
       <c r="R17" t="n">
-        <v>6648492</v>
+        <v>6648151</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2509,7 +2511,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2519,12 +2521,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>5 bladrosetter</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2533,7 +2530,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2552,10 +2548,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123398368</v>
+        <v>123404593</v>
       </c>
       <c r="B18" t="n">
-        <v>56683</v>
+        <v>57634</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2568,42 +2564,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620347</v>
+        <v>620575</v>
       </c>
       <c r="R18" t="n">
-        <v>6648171</v>
+        <v>6648228</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2635,7 +2628,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2645,12 +2638,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Två stycken stöttes upp från samma ställe, flög tillsammans ca 20 meter söderut.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2677,10 +2665,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123405294</v>
+        <v>123406069</v>
       </c>
       <c r="B19" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2717,10 +2705,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620610</v>
+        <v>620600</v>
       </c>
       <c r="R19" t="n">
-        <v>6648299</v>
+        <v>6648303</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2752,7 +2740,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2762,12 +2750,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,10 +2782,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123410527</v>
+        <v>123399558</v>
       </c>
       <c r="B20" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,31 +2794,35 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2838,10 +2830,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620777</v>
+        <v>620398</v>
       </c>
       <c r="R20" t="n">
-        <v>6648494</v>
+        <v>6648248</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2873,7 +2865,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2883,12 +2875,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca 10 bladroseter</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2897,7 +2884,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2916,10 +2902,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123399558</v>
+        <v>123410527</v>
       </c>
       <c r="B21" t="n">
-        <v>56691</v>
+        <v>98370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2928,35 +2914,31 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2964,10 +2946,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620398</v>
+        <v>620777</v>
       </c>
       <c r="R21" t="n">
-        <v>6648248</v>
+        <v>6648494</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2999,7 +2981,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3009,7 +2991,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3018,6 +3005,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3036,10 +3024,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123408488</v>
+        <v>123402052</v>
       </c>
       <c r="B22" t="n">
-        <v>98368</v>
+        <v>79389</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3048,38 +3036,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620679</v>
+        <v>620544</v>
       </c>
       <c r="R22" t="n">
-        <v>6648540</v>
+        <v>6648151</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3111,7 +3099,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3121,12 +3109,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3153,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123417364</v>
+        <v>123400078</v>
       </c>
       <c r="B23" t="n">
-        <v>78769</v>
+        <v>74678</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3165,25 +3148,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6428</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3196,13 +3179,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620549</v>
+        <v>620467</v>
       </c>
       <c r="R23" t="n">
-        <v>6648158</v>
+        <v>6648236</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3229,9 +3212,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:41</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På granbark i fuktig del av skogen</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3259,10 +3257,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123404274</v>
+        <v>123404576</v>
       </c>
       <c r="B24" t="n">
-        <v>78414</v>
+        <v>56691</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3271,30 +3269,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3302,10 +3305,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620569</v>
+        <v>620575</v>
       </c>
       <c r="R24" t="n">
-        <v>6648238</v>
+        <v>6648228</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3337,7 +3340,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3347,7 +3350,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3356,7 +3364,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3375,10 +3382,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123410978</v>
+        <v>123398864</v>
       </c>
       <c r="B25" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3387,31 +3394,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3419,10 +3430,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620617</v>
+        <v>620370</v>
       </c>
       <c r="R25" t="n">
-        <v>6648344</v>
+        <v>6648255</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3452,14 +3463,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ca 30 bladrosetter</t>
+          <t>2 krokar på tallåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3468,7 +3489,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3487,10 +3507,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123411227</v>
+        <v>123417137</v>
       </c>
       <c r="B26" t="n">
-        <v>98368</v>
+        <v>79389</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3499,31 +3519,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3531,13 +3550,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620502</v>
+        <v>620541</v>
       </c>
       <c r="R26" t="n">
-        <v>6648313</v>
+        <v>6648142</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3564,24 +3583,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3609,10 +3613,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123409471</v>
+        <v>123410978</v>
       </c>
       <c r="B27" t="n">
-        <v>74805</v>
+        <v>98370</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3621,41 +3625,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620802</v>
+        <v>620617</v>
       </c>
       <c r="R27" t="n">
-        <v>6648510</v>
+        <v>6648344</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3685,19 +3690,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:52</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:52</t>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ca 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3725,10 +3725,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123407548</v>
+        <v>123397574</v>
       </c>
       <c r="B28" t="n">
-        <v>98368</v>
+        <v>56691</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3737,38 +3737,46 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620609</v>
+        <v>620364</v>
       </c>
       <c r="R28" t="n">
-        <v>6648383</v>
+        <v>6648233</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3800,7 +3808,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3810,12 +3818,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3842,10 +3850,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123402991</v>
+        <v>123405636</v>
       </c>
       <c r="B29" t="n">
-        <v>56691</v>
+        <v>95034</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3858,45 +3866,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620551</v>
+        <v>620633</v>
       </c>
       <c r="R29" t="n">
-        <v>6648134</v>
+        <v>6648297</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3935,7 +3935,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3962,10 +3962,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123399110</v>
+        <v>123417333</v>
       </c>
       <c r="B30" t="n">
-        <v>95032</v>
+        <v>98370</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3974,38 +3974,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620370</v>
+        <v>620596</v>
       </c>
       <c r="R30" t="n">
-        <v>6648255</v>
+        <v>6648322</v>
       </c>
       <c r="S30" t="n">
         <v>25</v>
@@ -4035,19 +4039,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:17</t>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4056,6 +4055,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1725,10 +1725,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123409471</v>
+        <v>123405294</v>
       </c>
       <c r="B11" t="n">
-        <v>74805</v>
+        <v>98370</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1737,41 +1737,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620802</v>
+        <v>620610</v>
       </c>
       <c r="R11" t="n">
-        <v>6648510</v>
+        <v>6648299</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1803,7 +1800,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1813,7 +1810,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1822,7 +1824,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1841,10 +1842,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123406533</v>
+        <v>123409471</v>
       </c>
       <c r="B12" t="n">
-        <v>95916</v>
+        <v>74805</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1853,31 +1854,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1885,10 +1885,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620593</v>
+        <v>620802</v>
       </c>
       <c r="R12" t="n">
-        <v>6648325</v>
+        <v>6648510</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,12 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>På understa lågan</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123405294</v>
+        <v>123406533</v>
       </c>
       <c r="B13" t="n">
-        <v>98370</v>
+        <v>95916</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1975,38 +1970,42 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620610</v>
+        <v>620593</v>
       </c>
       <c r="R13" t="n">
-        <v>6648299</v>
+        <v>6648325</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2038,7 +2037,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2048,12 +2047,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2062,6 +2061,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2202,10 +2202,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123411112</v>
+        <v>123401959</v>
       </c>
       <c r="B15" t="n">
-        <v>98370</v>
+        <v>78416</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2214,25 +2214,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2242,10 +2242,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620609</v>
+        <v>620544</v>
       </c>
       <c r="R15" t="n">
-        <v>6648334</v>
+        <v>6648151</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2287,12 +2287,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>3 bladrosetter</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2319,7 +2314,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123407548</v>
+        <v>123411112</v>
       </c>
       <c r="B16" t="n">
         <v>98370</v>
@@ -2355,14 +2350,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
         <v>620609</v>
       </c>
       <c r="R16" t="n">
-        <v>6648383</v>
+        <v>6648334</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2394,7 +2389,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2404,12 +2399,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2436,10 +2431,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123401959</v>
+        <v>123407548</v>
       </c>
       <c r="B17" t="n">
-        <v>78416</v>
+        <v>98370</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2448,38 +2443,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620544</v>
+        <v>620609</v>
       </c>
       <c r="R17" t="n">
-        <v>6648151</v>
+        <v>6648383</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2511,7 +2506,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2521,7 +2516,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3136,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123400078</v>
+        <v>123404576</v>
       </c>
       <c r="B23" t="n">
-        <v>74678</v>
+        <v>56691</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3152,37 +3152,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6428</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620467</v>
+        <v>620575</v>
       </c>
       <c r="R23" t="n">
-        <v>6648236</v>
+        <v>6648228</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3214,7 +3219,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3224,12 +3229,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På granbark i fuktig del av skogen</t>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3238,7 +3243,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3257,7 +3261,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123404576</v>
+        <v>123398864</v>
       </c>
       <c r="B24" t="n">
         <v>56691</v>
@@ -3301,14 +3305,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620575</v>
+        <v>620370</v>
       </c>
       <c r="R24" t="n">
-        <v>6648228</v>
+        <v>6648255</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3340,7 +3344,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3350,12 +3354,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
+          <t>2 krokar på tallåga</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3382,10 +3386,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123398864</v>
+        <v>123417137</v>
       </c>
       <c r="B25" t="n">
-        <v>56691</v>
+        <v>79389</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3394,35 +3398,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3430,13 +3429,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620370</v>
+        <v>620541</v>
       </c>
       <c r="R25" t="n">
-        <v>6648255</v>
+        <v>6648142</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3463,32 +3462,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 krokar på tallåga</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3507,10 +3492,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123417137</v>
+        <v>123410978</v>
       </c>
       <c r="B26" t="n">
-        <v>79389</v>
+        <v>98370</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3519,30 +3504,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3550,13 +3536,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620541</v>
+        <v>620617</v>
       </c>
       <c r="R26" t="n">
-        <v>6648142</v>
+        <v>6648344</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3586,6 +3572,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ca 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3613,10 +3604,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123410978</v>
+        <v>123397574</v>
       </c>
       <c r="B27" t="n">
-        <v>98370</v>
+        <v>56691</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3625,42 +3616,46 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620617</v>
+        <v>620364</v>
       </c>
       <c r="R27" t="n">
-        <v>6648344</v>
+        <v>6648233</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3690,14 +3685,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Ca 30 bladrosetter</t>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3706,7 +3711,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3725,10 +3729,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123397574</v>
+        <v>123405636</v>
       </c>
       <c r="B28" t="n">
-        <v>56691</v>
+        <v>95034</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3741,42 +3745,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620364</v>
+        <v>620633</v>
       </c>
       <c r="R28" t="n">
-        <v>6648233</v>
+        <v>6648297</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3808,7 +3804,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3818,12 +3814,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>5 krokar på höjd</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3850,10 +3841,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123405636</v>
+        <v>123417333</v>
       </c>
       <c r="B29" t="n">
-        <v>95034</v>
+        <v>98370</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3862,38 +3853,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620633</v>
+        <v>620596</v>
       </c>
       <c r="R29" t="n">
-        <v>6648297</v>
+        <v>6648322</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3923,19 +3918,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>13:44</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>13:44</t>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3944,6 +3934,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3959,118 +3950,6 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>123417333</v>
-      </c>
-      <c r="B30" t="n">
-        <v>98370</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Bålmyran, norr om, Upl</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>620596</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6648322</v>
-      </c>
-      <c r="S30" t="n">
-        <v>25</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Järlåsa</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>13 bladrosetter</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Vilhelm Kroon</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123399110</v>
+        <v>123408009</v>
       </c>
       <c r="B2" t="n">
-        <v>95034</v>
+        <v>56691</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620370</v>
+        <v>620718</v>
       </c>
       <c r="R2" t="n">
-        <v>6648255</v>
+        <v>6648486</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408853</v>
+        <v>123404576</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>56691</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +807,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620759</v>
+        <v>620575</v>
       </c>
       <c r="R3" t="n">
-        <v>6648492</v>
+        <v>6648228</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +878,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +888,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +902,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123407003</v>
+        <v>123410978</v>
       </c>
       <c r="B4" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -949,17 +960,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620581</v>
+        <v>620617</v>
       </c>
       <c r="R4" t="n">
-        <v>6648381</v>
+        <v>6648344</v>
       </c>
       <c r="S4" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -993,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Mer än 35 bladrosetter</t>
+          <t>Ca 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1032,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408488</v>
+        <v>123398368</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>56683</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,38 +1044,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620679</v>
+        <v>620347</v>
       </c>
       <c r="R5" t="n">
-        <v>6648540</v>
+        <v>6648171</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1115,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,12 +1125,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>Två stycken stöttes upp från samma ställe, flög tillsammans ca 20 meter söderut.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1157,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123404274</v>
+        <v>123404593</v>
       </c>
       <c r="B6" t="n">
-        <v>78416</v>
+        <v>57634</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,37 +1173,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>353</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620569</v>
+        <v>620575</v>
       </c>
       <c r="R6" t="n">
-        <v>6648238</v>
+        <v>6648228</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,7 +1237,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1226,7 +1247,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,7 +1256,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1254,10 +1274,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123417364</v>
+        <v>123402052</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>79390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,40 +1290,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620549</v>
+        <v>620544</v>
       </c>
       <c r="R7" t="n">
-        <v>6648158</v>
+        <v>6648151</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1330,18 +1347,27 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1360,10 +1386,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408009</v>
+        <v>123409471</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>74805</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1376,31 +1402,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1408,10 +1429,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620718</v>
+        <v>620802</v>
       </c>
       <c r="R8" t="n">
-        <v>6648486</v>
+        <v>6648510</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1443,7 +1464,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1453,7 +1474,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,6 +1483,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1480,10 +1502,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123402991</v>
+        <v>123404274</v>
       </c>
       <c r="B9" t="n">
-        <v>56691</v>
+        <v>78417</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1492,49 +1514,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620551</v>
+        <v>620569</v>
       </c>
       <c r="R9" t="n">
-        <v>6648134</v>
+        <v>6648238</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1563,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1590,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,6 +1599,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1600,10 +1618,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123398368</v>
+        <v>123397574</v>
       </c>
       <c r="B10" t="n">
-        <v>56683</v>
+        <v>56691</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1612,46 +1630,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620347</v>
+        <v>620364</v>
       </c>
       <c r="R10" t="n">
-        <v>6648171</v>
+        <v>6648233</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1698,7 +1716,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Två stycken stöttes upp från samma ställe, flög tillsammans ca 20 meter söderut.</t>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1725,10 +1743,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123405294</v>
+        <v>123406069</v>
       </c>
       <c r="B11" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1765,10 +1783,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620610</v>
+        <v>620600</v>
       </c>
       <c r="R11" t="n">
-        <v>6648299</v>
+        <v>6648303</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1800,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1810,12 +1828,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,10 +1860,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123409471</v>
+        <v>123411112</v>
       </c>
       <c r="B12" t="n">
-        <v>74805</v>
+        <v>98376</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1854,41 +1872,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620802</v>
+        <v>620609</v>
       </c>
       <c r="R12" t="n">
-        <v>6648510</v>
+        <v>6648334</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1920,7 +1935,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1930,7 +1945,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,7 +1959,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1958,10 +1977,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123406533</v>
+        <v>123398864</v>
       </c>
       <c r="B13" t="n">
-        <v>95916</v>
+        <v>56691</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,42 +1989,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620593</v>
+        <v>620370</v>
       </c>
       <c r="R13" t="n">
-        <v>6648325</v>
+        <v>6648255</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2037,7 +2060,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2047,12 +2070,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>På understa lågan</t>
+          <t>2 krokar på tallåga</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2061,7 +2084,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2080,10 +2102,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123411227</v>
+        <v>123408488</v>
       </c>
       <c r="B14" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2114,20 +2136,16 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620502</v>
+        <v>620679</v>
       </c>
       <c r="R14" t="n">
-        <v>6648313</v>
+        <v>6648540</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2159,7 +2177,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2169,12 +2187,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2183,7 +2201,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2205,7 +2222,7 @@
         <v>123401959</v>
       </c>
       <c r="B15" t="n">
-        <v>78416</v>
+        <v>78417</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2314,10 +2331,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123411112</v>
+        <v>123405636</v>
       </c>
       <c r="B16" t="n">
-        <v>98370</v>
+        <v>95040</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2326,38 +2343,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620609</v>
+        <v>620633</v>
       </c>
       <c r="R16" t="n">
-        <v>6648334</v>
+        <v>6648297</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2389,7 +2406,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2399,12 +2416,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>3 bladrosetter</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2431,10 +2443,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123407548</v>
+        <v>123399558</v>
       </c>
       <c r="B17" t="n">
-        <v>98370</v>
+        <v>56691</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2443,38 +2455,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620609</v>
+        <v>620398</v>
       </c>
       <c r="R17" t="n">
-        <v>6648383</v>
+        <v>6648248</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2506,7 +2526,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2516,12 +2536,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2548,10 +2563,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123404593</v>
+        <v>123408853</v>
       </c>
       <c r="B18" t="n">
-        <v>57634</v>
+        <v>98376</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2560,43 +2575,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620575</v>
+        <v>620759</v>
       </c>
       <c r="R18" t="n">
-        <v>6648228</v>
+        <v>6648492</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2628,7 +2642,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2638,7 +2652,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2647,6 +2666,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2665,10 +2685,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123406069</v>
+        <v>123405294</v>
       </c>
       <c r="B19" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2705,10 +2725,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620600</v>
+        <v>620610</v>
       </c>
       <c r="R19" t="n">
-        <v>6648303</v>
+        <v>6648299</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2740,7 +2760,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2750,12 +2770,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>12 bladrosetter</t>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2782,10 +2802,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123399558</v>
+        <v>123399110</v>
       </c>
       <c r="B20" t="n">
-        <v>56691</v>
+        <v>95040</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2798,42 +2818,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620398</v>
+        <v>620370</v>
       </c>
       <c r="R20" t="n">
-        <v>6648248</v>
+        <v>6648255</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2865,7 +2877,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,7 +2887,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,10 +2914,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123410527</v>
+        <v>123407003</v>
       </c>
       <c r="B21" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2942,17 +2954,17 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620777</v>
+        <v>620581</v>
       </c>
       <c r="R21" t="n">
-        <v>6648494</v>
+        <v>6648381</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2979,24 +2991,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ca 10 bladroseter</t>
+          <t>Mer än 35 bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3024,10 +3026,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123402052</v>
+        <v>123407548</v>
       </c>
       <c r="B22" t="n">
-        <v>79389</v>
+        <v>98376</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3036,38 +3038,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620544</v>
+        <v>620609</v>
       </c>
       <c r="R22" t="n">
-        <v>6648151</v>
+        <v>6648383</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3099,7 +3101,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3109,7 +3111,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3136,10 +3143,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123404576</v>
+        <v>123417137</v>
       </c>
       <c r="B23" t="n">
-        <v>56691</v>
+        <v>79390</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3148,49 +3155,44 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620575</v>
+        <v>620541</v>
       </c>
       <c r="R23" t="n">
-        <v>6648228</v>
+        <v>6648142</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3217,32 +3219,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3261,7 +3249,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123398864</v>
+        <v>123402991</v>
       </c>
       <c r="B24" t="n">
         <v>56691</v>
@@ -3305,17 +3293,17 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620370</v>
+        <v>620551</v>
       </c>
       <c r="R24" t="n">
-        <v>6648255</v>
+        <v>6648134</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3344,7 +3332,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3354,12 +3342,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2 krokar på tallåga</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3386,10 +3369,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123417137</v>
+        <v>123417333</v>
       </c>
       <c r="B25" t="n">
-        <v>79389</v>
+        <v>98376</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3398,44 +3381,45 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620541</v>
+        <v>620596</v>
       </c>
       <c r="R25" t="n">
-        <v>6648142</v>
+        <v>6648322</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3465,6 +3449,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3492,10 +3481,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123410978</v>
+        <v>123411227</v>
       </c>
       <c r="B26" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3536,10 +3525,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620617</v>
+        <v>620502</v>
       </c>
       <c r="R26" t="n">
-        <v>6648344</v>
+        <v>6648313</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3569,14 +3558,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca 30 bladrosetter</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3604,10 +3603,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123397574</v>
+        <v>123417364</v>
       </c>
       <c r="B27" t="n">
-        <v>56691</v>
+        <v>78772</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3616,49 +3615,44 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620364</v>
+        <v>620549</v>
       </c>
       <c r="R27" t="n">
-        <v>6648233</v>
+        <v>6648158</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3685,32 +3679,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>5 krokar på höjd</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3729,10 +3709,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123405636</v>
+        <v>123406533</v>
       </c>
       <c r="B28" t="n">
-        <v>95034</v>
+        <v>95922</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3741,38 +3721,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620633</v>
+        <v>620593</v>
       </c>
       <c r="R28" t="n">
-        <v>6648297</v>
+        <v>6648325</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3804,7 +3788,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3814,7 +3798,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3823,6 +3812,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3841,10 +3831,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123417333</v>
+        <v>123410527</v>
       </c>
       <c r="B29" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3881,14 +3871,14 @@
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620596</v>
+        <v>620777</v>
       </c>
       <c r="R29" t="n">
-        <v>6648322</v>
+        <v>6648494</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3918,14 +3908,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -5409,7 +5409,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123634655</v>
+        <v>123638047</v>
       </c>
       <c r="B42" t="n">
         <v>98379</v>
@@ -5442,34 +5442,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620626</v>
+        <v>620519</v>
       </c>
       <c r="R42" t="n">
-        <v>6648342</v>
+        <v>6648333</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5498,7 +5484,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5508,7 +5494,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5523,19 +5514,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123638047</v>
+        <v>123634655</v>
       </c>
       <c r="B43" t="n">
         <v>98379</v>
@@ -5568,20 +5559,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620519</v>
+        <v>620626</v>
       </c>
       <c r="R43" t="n">
-        <v>6648333</v>
+        <v>6648342</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5610,7 +5615,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5620,12 +5625,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5640,12 +5640,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123417137</v>
+        <v>123404274</v>
       </c>
       <c r="B2" t="n">
-        <v>79393</v>
+        <v>78426</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,17 +714,17 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620541</v>
+        <v>620569</v>
       </c>
       <c r="R2" t="n">
-        <v>6648142</v>
+        <v>6648238</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,9 +751,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123407548</v>
+        <v>123407003</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,19 +825,23 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620609</v>
+        <v>620581</v>
       </c>
       <c r="R3" t="n">
-        <v>6648383</v>
+        <v>6648381</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -854,24 +868,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Mer än 35 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -880,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -898,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123408853</v>
+        <v>123402991</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
+        <v>56697</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,31 +915,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,13 +951,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620759</v>
+        <v>620551</v>
       </c>
       <c r="R4" t="n">
-        <v>6648492</v>
+        <v>6648134</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +986,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,12 +996,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5 bladrosetter</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +1005,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1020,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123410527</v>
+        <v>123405636</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
+        <v>95060</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,42 +1035,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620777</v>
+        <v>620633</v>
       </c>
       <c r="R5" t="n">
-        <v>6648494</v>
+        <v>6648297</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1099,7 +1098,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1109,12 +1108,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ca 10 bladroseter</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1117,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1142,10 +1135,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123417333</v>
+        <v>123408853</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,10 +1179,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620596</v>
+        <v>620759</v>
       </c>
       <c r="R6" t="n">
-        <v>6648322</v>
+        <v>6648492</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1219,14 +1212,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1257,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123406533</v>
+        <v>123410978</v>
       </c>
       <c r="B7" t="n">
-        <v>95925</v>
+        <v>98396</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,25 +1269,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1294,14 +1297,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620593</v>
+        <v>620617</v>
       </c>
       <c r="R7" t="n">
-        <v>6648325</v>
+        <v>6648344</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1331,24 +1334,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På understa lågan</t>
+          <t>Ca 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1369,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123402991</v>
+        <v>123404593</v>
       </c>
       <c r="B8" t="n">
-        <v>56691</v>
+        <v>57640</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1388,49 +1381,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620551</v>
+        <v>620575</v>
       </c>
       <c r="R8" t="n">
-        <v>6648134</v>
+        <v>6648228</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1459,7 +1449,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1459,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123404576</v>
+        <v>123401959</v>
       </c>
       <c r="B9" t="n">
-        <v>56691</v>
+        <v>78426</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,46 +1498,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620575</v>
+        <v>620544</v>
       </c>
       <c r="R9" t="n">
-        <v>6648228</v>
+        <v>6648151</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1579,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1589,12 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1621,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123404274</v>
+        <v>123399110</v>
       </c>
       <c r="B10" t="n">
-        <v>78420</v>
+        <v>95060</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1633,41 +1610,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620569</v>
+        <v>620370</v>
       </c>
       <c r="R10" t="n">
-        <v>6648238</v>
+        <v>6648255</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1699,7 +1673,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,7 +1683,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1718,7 +1692,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1737,10 +1710,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123402052</v>
+        <v>123404576</v>
       </c>
       <c r="B11" t="n">
-        <v>79393</v>
+        <v>56697</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1749,38 +1722,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620544</v>
+        <v>620575</v>
       </c>
       <c r="R11" t="n">
-        <v>6648151</v>
+        <v>6648228</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1812,7 +1793,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,7 +1803,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1849,10 +1835,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123411227</v>
+        <v>123410527</v>
       </c>
       <c r="B12" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1893,10 +1879,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620502</v>
+        <v>620777</v>
       </c>
       <c r="R12" t="n">
-        <v>6648313</v>
+        <v>6648494</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1928,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,12 +1924,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1971,10 +1957,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123398864</v>
+        <v>123408009</v>
       </c>
       <c r="B13" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2015,14 +2001,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620370</v>
+        <v>620718</v>
       </c>
       <c r="R13" t="n">
-        <v>6648255</v>
+        <v>6648486</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2054,7 +2040,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2064,12 +2050,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2 krokar på tallåga</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2096,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123405294</v>
+        <v>123417364</v>
       </c>
       <c r="B14" t="n">
-        <v>98379</v>
+        <v>78781</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2108,41 +2089,44 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620610</v>
+        <v>620549</v>
       </c>
       <c r="R14" t="n">
-        <v>6648299</v>
+        <v>6648158</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2169,32 +2153,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2213,10 +2183,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123399558</v>
+        <v>123407548</v>
       </c>
       <c r="B15" t="n">
-        <v>56691</v>
+        <v>98396</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,46 +2195,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620398</v>
+        <v>620609</v>
       </c>
       <c r="R15" t="n">
-        <v>6648248</v>
+        <v>6648383</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2296,7 +2258,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2306,7 +2268,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2333,10 +2300,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123407003</v>
+        <v>123406069</v>
       </c>
       <c r="B16" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2367,23 +2334,19 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620581</v>
+        <v>620600</v>
       </c>
       <c r="R16" t="n">
-        <v>6648381</v>
+        <v>6648303</v>
       </c>
       <c r="S16" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2410,14 +2373,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Mer än 35 bladrosetter</t>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2426,7 +2399,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2445,10 +2417,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123406069</v>
+        <v>123402052</v>
       </c>
       <c r="B17" t="n">
-        <v>98379</v>
+        <v>79399</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2457,38 +2429,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620600</v>
+        <v>620544</v>
       </c>
       <c r="R17" t="n">
-        <v>6648303</v>
+        <v>6648151</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2520,7 +2492,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2530,12 +2502,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2562,10 +2529,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123417364</v>
+        <v>123411112</v>
       </c>
       <c r="B18" t="n">
-        <v>78775</v>
+        <v>98396</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2574,44 +2541,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620549</v>
+        <v>620609</v>
       </c>
       <c r="R18" t="n">
-        <v>6648158</v>
+        <v>6648334</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2638,18 +2602,32 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>3 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2668,10 +2646,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123408488</v>
+        <v>123399558</v>
       </c>
       <c r="B19" t="n">
-        <v>98379</v>
+        <v>56697</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2680,38 +2658,46 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620679</v>
+        <v>620398</v>
       </c>
       <c r="R19" t="n">
-        <v>6648540</v>
+        <v>6648248</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2743,7 +2729,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2753,12 +2739,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2785,10 +2766,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123408009</v>
+        <v>123398864</v>
       </c>
       <c r="B20" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2829,14 +2810,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620718</v>
+        <v>620370</v>
       </c>
       <c r="R20" t="n">
-        <v>6648486</v>
+        <v>6648255</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2868,7 +2849,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2878,7 +2859,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>2 krokar på tallåga</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2905,10 +2891,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123409471</v>
+        <v>123408488</v>
       </c>
       <c r="B21" t="n">
-        <v>74808</v>
+        <v>98396</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2917,41 +2903,38 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620802</v>
+        <v>620679</v>
       </c>
       <c r="R21" t="n">
-        <v>6648510</v>
+        <v>6648540</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2983,7 +2966,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2993,7 +2976,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3002,7 +2990,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3021,10 +3008,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123404593</v>
+        <v>123397574</v>
       </c>
       <c r="B22" t="n">
-        <v>57634</v>
+        <v>56697</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3033,43 +3020,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620575</v>
+        <v>620364</v>
       </c>
       <c r="R22" t="n">
-        <v>6648228</v>
+        <v>6648233</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3101,7 +3091,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3111,7 +3101,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3138,10 +3133,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123397574</v>
+        <v>123417137</v>
       </c>
       <c r="B23" t="n">
-        <v>56691</v>
+        <v>79399</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3150,49 +3145,44 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620364</v>
+        <v>620541</v>
       </c>
       <c r="R23" t="n">
-        <v>6648233</v>
+        <v>6648142</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3219,32 +3209,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>5 krokar på höjd</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3263,10 +3239,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123411112</v>
+        <v>123406533</v>
       </c>
       <c r="B24" t="n">
-        <v>98379</v>
+        <v>95942</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3275,38 +3251,42 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620609</v>
+        <v>620593</v>
       </c>
       <c r="R24" t="n">
-        <v>6648334</v>
+        <v>6648325</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3338,7 +3318,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3348,12 +3328,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>3 bladrosetter</t>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3362,6 +3342,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3380,10 +3361,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123405636</v>
+        <v>123409471</v>
       </c>
       <c r="B25" t="n">
-        <v>95043</v>
+        <v>74814</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3396,34 +3377,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620633</v>
+        <v>620802</v>
       </c>
       <c r="R25" t="n">
-        <v>6648297</v>
+        <v>6648510</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3455,7 +3439,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3465,7 +3449,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3474,6 +3458,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3492,10 +3477,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123410978</v>
+        <v>123411227</v>
       </c>
       <c r="B26" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3536,10 +3521,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620617</v>
+        <v>620502</v>
       </c>
       <c r="R26" t="n">
-        <v>6648344</v>
+        <v>6648313</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3569,14 +3554,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca 30 bladrosetter</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3604,10 +3599,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123399110</v>
+        <v>123405294</v>
       </c>
       <c r="B27" t="n">
-        <v>95043</v>
+        <v>98396</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3616,38 +3611,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620370</v>
+        <v>620610</v>
       </c>
       <c r="R27" t="n">
-        <v>6648255</v>
+        <v>6648299</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3679,7 +3674,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3689,7 +3684,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3716,10 +3716,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123401959</v>
+        <v>123417333</v>
       </c>
       <c r="B28" t="n">
-        <v>78420</v>
+        <v>98396</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3728,38 +3728,42 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620544</v>
+        <v>620596</v>
       </c>
       <c r="R28" t="n">
-        <v>6648151</v>
+        <v>6648322</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3789,19 +3793,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:03</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3810,6 +3809,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>123398368</v>
       </c>
       <c r="B29" t="n">
-        <v>56683</v>
+        <v>56689</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3957,10 +3957,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123635541</v>
+        <v>123634578</v>
       </c>
       <c r="B30" t="n">
-        <v>57497</v>
+        <v>74814</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3969,46 +3969,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620556</v>
+        <v>620451</v>
       </c>
       <c r="R30" t="n">
-        <v>6648344</v>
+        <v>6648229</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4037,7 +4032,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4047,7 +4042,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4062,22 +4057,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123634264</v>
+        <v>123633877</v>
       </c>
       <c r="B31" t="n">
-        <v>98379</v>
+        <v>57857</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4086,40 +4081,40 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4128,13 +4123,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620584</v>
+        <v>620537</v>
       </c>
       <c r="R31" t="n">
-        <v>6648323</v>
+        <v>6648292</v>
       </c>
       <c r="S31" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4163,7 +4158,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4173,7 +4168,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4200,10 +4195,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123634578</v>
+        <v>123634559</v>
       </c>
       <c r="B32" t="n">
-        <v>74808</v>
+        <v>98396</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4212,41 +4207,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620451</v>
+        <v>620614</v>
       </c>
       <c r="R32" t="n">
-        <v>6648229</v>
+        <v>6648335</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4275,7 +4284,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4285,7 +4294,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4300,22 +4309,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123636168</v>
+        <v>123638984</v>
       </c>
       <c r="B33" t="n">
-        <v>95925</v>
+        <v>98396</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4324,25 +4333,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4356,10 +4365,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620443</v>
+        <v>620528</v>
       </c>
       <c r="R33" t="n">
-        <v>6648200</v>
+        <v>6648364</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4391,7 +4400,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4401,7 +4410,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4429,10 +4443,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123635547</v>
+        <v>123637283</v>
       </c>
       <c r="B34" t="n">
-        <v>98379</v>
+        <v>95942</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4441,55 +4455,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620556</v>
+        <v>620603</v>
       </c>
       <c r="R34" t="n">
-        <v>6648344</v>
+        <v>6648146</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4543,22 +4543,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123638984</v>
+        <v>123635547</v>
       </c>
       <c r="B35" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4588,24 +4588,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620528</v>
+        <v>620556</v>
       </c>
       <c r="R35" t="n">
-        <v>6648364</v>
+        <v>6648344</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4634,7 +4644,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4644,12 +4654,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4658,29 +4663,28 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123640236</v>
+        <v>123635541</v>
       </c>
       <c r="B36" t="n">
-        <v>105485</v>
+        <v>57503</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4689,45 +4693,46 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620584</v>
+        <v>620556</v>
       </c>
       <c r="R36" t="n">
-        <v>6648414</v>
+        <v>6648344</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4756,7 +4761,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4766,7 +4771,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4775,29 +4780,28 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123634559</v>
+        <v>123635839</v>
       </c>
       <c r="B37" t="n">
-        <v>98379</v>
+        <v>57640</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4806,52 +4810,47 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620614</v>
+        <v>620523</v>
       </c>
       <c r="R37" t="n">
-        <v>6648335</v>
+        <v>6648363</v>
       </c>
       <c r="S37" t="n">
         <v>12</v>
@@ -4883,7 +4882,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4893,7 +4892,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4920,10 +4919,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123634500</v>
+        <v>123635666</v>
       </c>
       <c r="B38" t="n">
-        <v>98379</v>
+        <v>57640</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4932,40 +4931,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4974,13 +4973,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620604</v>
+        <v>620526</v>
       </c>
       <c r="R38" t="n">
-        <v>6648323</v>
+        <v>6648364</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5009,7 +5008,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5019,7 +5018,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5046,10 +5045,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123635666</v>
+        <v>123635824</v>
       </c>
       <c r="B39" t="n">
-        <v>57634</v>
+        <v>98396</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5058,40 +5057,40 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5100,10 +5099,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620526</v>
+        <v>620523</v>
       </c>
       <c r="R39" t="n">
-        <v>6648364</v>
+        <v>6648363</v>
       </c>
       <c r="S39" t="n">
         <v>12</v>
@@ -5135,7 +5134,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5145,7 +5144,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5172,10 +5171,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123635390</v>
+        <v>123634264</v>
       </c>
       <c r="B40" t="n">
-        <v>90966</v>
+        <v>98396</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5184,41 +5183,55 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620591</v>
+        <v>620584</v>
       </c>
       <c r="R40" t="n">
-        <v>6648347</v>
+        <v>6648323</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5247,7 +5260,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5257,7 +5270,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5284,10 +5297,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123635548</v>
+        <v>123634500</v>
       </c>
       <c r="B41" t="n">
-        <v>57634</v>
+        <v>98396</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5296,49 +5309,55 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620334</v>
+        <v>620604</v>
       </c>
       <c r="R41" t="n">
-        <v>6648148</v>
+        <v>6648323</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5367,7 +5386,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5377,12 +5396,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>1 ex sjöng från tallgren</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5397,22 +5411,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123638047</v>
+        <v>123639666</v>
       </c>
       <c r="B42" t="n">
-        <v>98379</v>
+        <v>57640</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5421,41 +5435,55 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620519</v>
+        <v>620713</v>
       </c>
       <c r="R42" t="n">
-        <v>6648333</v>
+        <v>6648583</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5484,7 +5512,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5494,12 +5522,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5514,22 +5537,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123634655</v>
+        <v>123638047</v>
       </c>
       <c r="B43" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5559,34 +5582,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620626</v>
+        <v>620519</v>
       </c>
       <c r="R43" t="n">
-        <v>6648342</v>
+        <v>6648333</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5615,7 +5624,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5625,7 +5634,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5640,22 +5654,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123635824</v>
+        <v>123636168</v>
       </c>
       <c r="B44" t="n">
-        <v>98379</v>
+        <v>95942</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5664,55 +5678,45 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620523</v>
+        <v>620443</v>
       </c>
       <c r="R44" t="n">
-        <v>6648363</v>
+        <v>6648200</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5741,7 +5745,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5751,7 +5755,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5760,28 +5764,29 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
+      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123634710</v>
+        <v>123635390</v>
       </c>
       <c r="B45" t="n">
-        <v>98379</v>
+        <v>90983</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5790,55 +5795,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620635</v>
+        <v>620591</v>
       </c>
       <c r="R45" t="n">
-        <v>6648363</v>
+        <v>6648347</v>
       </c>
       <c r="S45" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5867,7 +5858,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5877,7 +5868,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5904,10 +5895,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123634512</v>
+        <v>123635230</v>
       </c>
       <c r="B46" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5939,7 +5930,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5958,13 +5949,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620600</v>
+        <v>620593</v>
       </c>
       <c r="R46" t="n">
-        <v>6648328</v>
+        <v>6648376</v>
       </c>
       <c r="S46" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5993,7 +5984,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6003,7 +5994,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6030,10 +6021,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123635230</v>
+        <v>123634512</v>
       </c>
       <c r="B47" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6065,7 +6056,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -6084,13 +6075,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620593</v>
+        <v>620600</v>
       </c>
       <c r="R47" t="n">
-        <v>6648376</v>
+        <v>6648328</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6119,7 +6110,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6129,7 +6120,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6156,10 +6147,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123635839</v>
+        <v>123635548</v>
       </c>
       <c r="B48" t="n">
-        <v>57634</v>
+        <v>57640</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6189,29 +6180,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620523</v>
+        <v>620334</v>
       </c>
       <c r="R48" t="n">
-        <v>6648363</v>
+        <v>6648148</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6240,7 +6230,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6250,7 +6240,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 ex sjöng från tallgren</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6265,12 +6260,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -6280,7 +6275,7 @@
         <v>123637481</v>
       </c>
       <c r="B49" t="n">
-        <v>56691</v>
+        <v>56697</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6394,10 +6389,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123637283</v>
+        <v>123632944</v>
       </c>
       <c r="B50" t="n">
-        <v>95925</v>
+        <v>105502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6406,41 +6401,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620603</v>
+        <v>620398</v>
       </c>
       <c r="R50" t="n">
-        <v>6648146</v>
+        <v>6648248</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6469,7 +6468,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6479,7 +6478,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>25 bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6488,6 +6492,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -6506,10 +6511,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123633877</v>
+        <v>123634655</v>
       </c>
       <c r="B51" t="n">
-        <v>57851</v>
+        <v>98396</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6518,40 +6523,40 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6560,13 +6565,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620537</v>
+        <v>620626</v>
       </c>
       <c r="R51" t="n">
-        <v>6648292</v>
+        <v>6648342</v>
       </c>
       <c r="S51" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6595,7 +6600,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6605,7 +6610,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6632,10 +6637,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123635032</v>
+        <v>123634710</v>
       </c>
       <c r="B52" t="n">
-        <v>98379</v>
+        <v>98396</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6667,7 +6672,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -6686,13 +6691,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620640</v>
+        <v>620635</v>
       </c>
       <c r="R52" t="n">
-        <v>6648367</v>
+        <v>6648363</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6721,7 +6726,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6731,7 +6736,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6758,10 +6763,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123641070</v>
+        <v>123640236</v>
       </c>
       <c r="B53" t="n">
-        <v>74681</v>
+        <v>105502</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6774,37 +6779,41 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6428</v>
+        <v>221144</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620466</v>
+        <v>620584</v>
       </c>
       <c r="R53" t="n">
-        <v>6648235</v>
+        <v>6648414</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6833,7 +6842,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6843,7 +6852,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6852,28 +6861,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123639666</v>
+        <v>123635032</v>
       </c>
       <c r="B54" t="n">
-        <v>57634</v>
+        <v>98396</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6882,52 +6892,52 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620713</v>
+        <v>620640</v>
       </c>
       <c r="R54" t="n">
-        <v>6648583</v>
+        <v>6648367</v>
       </c>
       <c r="S54" t="n">
         <v>12</v>
@@ -6959,7 +6969,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6969,7 +6979,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6996,10 +7006,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123632944</v>
+        <v>123641070</v>
       </c>
       <c r="B55" t="n">
-        <v>105485</v>
+        <v>74687</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7012,41 +7022,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221144</v>
+        <v>6428</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620398</v>
+        <v>620466</v>
       </c>
       <c r="R55" t="n">
-        <v>6648248</v>
+        <v>6648235</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7075,7 +7081,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7085,12 +7091,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>25 bladrosetter</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7099,19 +7100,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -2077,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123417364</v>
+        <v>123407548</v>
       </c>
       <c r="B14" t="n">
-        <v>78781</v>
+        <v>98396</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2089,44 +2089,41 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620549</v>
+        <v>620609</v>
       </c>
       <c r="R14" t="n">
-        <v>6648158</v>
+        <v>6648383</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2153,18 +2150,32 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2183,10 +2194,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123407548</v>
+        <v>123417364</v>
       </c>
       <c r="B15" t="n">
-        <v>98396</v>
+        <v>78781</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2195,41 +2206,44 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620609</v>
+        <v>620549</v>
       </c>
       <c r="R15" t="n">
-        <v>6648383</v>
+        <v>6648158</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2256,32 +2270,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -5297,7 +5297,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123634500</v>
+        <v>123638047</v>
       </c>
       <c r="B41" t="n">
         <v>98396</v>
@@ -5330,34 +5330,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620604</v>
+        <v>620519</v>
       </c>
       <c r="R41" t="n">
-        <v>6648323</v>
+        <v>6648333</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5386,7 +5372,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5396,7 +5382,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5411,12 +5402,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5549,7 +5540,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123638047</v>
+        <v>123634500</v>
       </c>
       <c r="B43" t="n">
         <v>98396</v>
@@ -5582,20 +5573,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620519</v>
+        <v>620604</v>
       </c>
       <c r="R43" t="n">
-        <v>6648333</v>
+        <v>6648323</v>
       </c>
       <c r="S43" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5624,7 +5629,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5634,12 +5639,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5654,12 +5654,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -6147,10 +6147,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123635548</v>
+        <v>123637481</v>
       </c>
       <c r="B48" t="n">
-        <v>57640</v>
+        <v>56697</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6159,49 +6159,46 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620334</v>
+        <v>620714</v>
       </c>
       <c r="R48" t="n">
-        <v>6648148</v>
+        <v>6648494</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6230,7 +6227,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6240,12 +6237,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>1 ex sjöng från tallgren</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6260,22 +6252,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123637481</v>
+        <v>123635548</v>
       </c>
       <c r="B49" t="n">
-        <v>56697</v>
+        <v>57640</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6284,46 +6276,49 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620714</v>
+        <v>620334</v>
       </c>
       <c r="R49" t="n">
-        <v>6648494</v>
+        <v>6648148</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6352,7 +6347,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6362,7 +6357,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>1 ex sjöng från tallgren</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6377,12 +6377,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -4919,10 +4919,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123635666</v>
+        <v>123635824</v>
       </c>
       <c r="B38" t="n">
-        <v>57640</v>
+        <v>98396</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4931,40 +4931,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620526</v>
+        <v>620523</v>
       </c>
       <c r="R38" t="n">
-        <v>6648364</v>
+        <v>6648363</v>
       </c>
       <c r="S38" t="n">
         <v>12</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5045,7 +5045,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123635824</v>
+        <v>123634264</v>
       </c>
       <c r="B39" t="n">
         <v>98396</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5099,13 +5099,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620523</v>
+        <v>620584</v>
       </c>
       <c r="R39" t="n">
-        <v>6648363</v>
+        <v>6648323</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5171,10 +5171,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123634264</v>
+        <v>123635666</v>
       </c>
       <c r="B40" t="n">
-        <v>98396</v>
+        <v>57640</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5183,40 +5183,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620584</v>
+        <v>620526</v>
       </c>
       <c r="R40" t="n">
-        <v>6648323</v>
+        <v>6648364</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6147,10 +6147,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123637481</v>
+        <v>123635548</v>
       </c>
       <c r="B48" t="n">
-        <v>56697</v>
+        <v>57640</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6159,46 +6159,49 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620714</v>
+        <v>620334</v>
       </c>
       <c r="R48" t="n">
-        <v>6648494</v>
+        <v>6648148</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6227,7 +6230,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6237,7 +6240,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 ex sjöng från tallgren</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6252,22 +6260,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123635548</v>
+        <v>123637481</v>
       </c>
       <c r="B49" t="n">
-        <v>57640</v>
+        <v>56697</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6276,49 +6284,46 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620334</v>
+        <v>620714</v>
       </c>
       <c r="R49" t="n">
-        <v>6648148</v>
+        <v>6648494</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6347,7 +6352,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6357,12 +6362,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>1 ex sjöng från tallgren</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6377,12 +6377,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY55"/>
+  <dimension ref="A1:AY56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123399110</v>
+        <v>123404576</v>
       </c>
       <c r="B10" t="n">
-        <v>95060</v>
+        <v>56697</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1614,34 +1614,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620370</v>
+        <v>620575</v>
       </c>
       <c r="R10" t="n">
-        <v>6648255</v>
+        <v>6648228</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1673,7 +1681,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1683,7 +1691,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,10 +1723,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123404576</v>
+        <v>123399110</v>
       </c>
       <c r="B11" t="n">
-        <v>56697</v>
+        <v>95060</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1726,42 +1739,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620575</v>
+        <v>620370</v>
       </c>
       <c r="R11" t="n">
-        <v>6648228</v>
+        <v>6648255</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1793,7 +1798,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1803,12 +1808,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -4919,10 +4919,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123635824</v>
+        <v>123635666</v>
       </c>
       <c r="B38" t="n">
-        <v>98396</v>
+        <v>57640</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4931,40 +4931,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4973,10 +4973,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620523</v>
+        <v>620526</v>
       </c>
       <c r="R38" t="n">
-        <v>6648363</v>
+        <v>6648364</v>
       </c>
       <c r="S38" t="n">
         <v>12</v>
@@ -5008,7 +5008,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5045,7 +5045,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123634264</v>
+        <v>123635824</v>
       </c>
       <c r="B39" t="n">
         <v>98396</v>
@@ -5080,7 +5080,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -5099,13 +5099,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620584</v>
+        <v>620523</v>
       </c>
       <c r="R39" t="n">
-        <v>6648323</v>
+        <v>6648363</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5171,10 +5171,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123635666</v>
+        <v>123634264</v>
       </c>
       <c r="B40" t="n">
-        <v>57640</v>
+        <v>98396</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5183,40 +5183,40 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620526</v>
+        <v>620584</v>
       </c>
       <c r="R40" t="n">
-        <v>6648364</v>
+        <v>6648323</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5297,7 +5297,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123638047</v>
+        <v>123634500</v>
       </c>
       <c r="B41" t="n">
         <v>98396</v>
@@ -5330,20 +5330,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620519</v>
+        <v>620604</v>
       </c>
       <c r="R41" t="n">
-        <v>6648333</v>
+        <v>6648323</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5372,7 +5386,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5382,12 +5396,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5402,22 +5411,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123639666</v>
+        <v>123638047</v>
       </c>
       <c r="B42" t="n">
-        <v>57640</v>
+        <v>98396</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5426,55 +5435,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620713</v>
+        <v>620519</v>
       </c>
       <c r="R42" t="n">
-        <v>6648583</v>
+        <v>6648333</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5503,7 +5498,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5513,7 +5508,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5528,22 +5528,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123634500</v>
+        <v>123639666</v>
       </c>
       <c r="B43" t="n">
-        <v>98396</v>
+        <v>57640</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5552,55 +5552,55 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620604</v>
+        <v>620713</v>
       </c>
       <c r="R43" t="n">
-        <v>6648323</v>
+        <v>6648583</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5629,7 +5629,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -7116,6 +7116,132 @@
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>123829229</v>
+      </c>
+      <c r="B56" t="n">
+        <v>57643</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Bålmyran, Bålmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>620373</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6648191</v>
+      </c>
+      <c r="S56" t="n">
+        <v>12</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-04-07</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123404274</v>
+        <v>123408009</v>
       </c>
       <c r="B2" t="n">
-        <v>78426</v>
+        <v>56700</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,46 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620569</v>
+        <v>620718</v>
       </c>
       <c r="R2" t="n">
-        <v>6648238</v>
+        <v>6648486</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -753,7 +758,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,7 +768,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,7 +777,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -791,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123407003</v>
+        <v>123397574</v>
       </c>
       <c r="B3" t="n">
-        <v>98396</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,31 +807,35 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +843,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620581</v>
+        <v>620364</v>
       </c>
       <c r="R3" t="n">
-        <v>6648381</v>
+        <v>6648233</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -868,14 +876,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Mer än 35 bladrosetter</t>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,7 +902,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -903,10 +920,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123402991</v>
+        <v>123404274</v>
       </c>
       <c r="B4" t="n">
-        <v>56697</v>
+        <v>78431</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,49 +932,44 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620551</v>
+        <v>620569</v>
       </c>
       <c r="R4" t="n">
-        <v>6648134</v>
+        <v>6648238</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -986,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -996,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1005,6 +1017,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1023,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123405636</v>
+        <v>123406069</v>
       </c>
       <c r="B5" t="n">
-        <v>95060</v>
+        <v>98502</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,25 +1048,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1063,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620633</v>
+        <v>620600</v>
       </c>
       <c r="R5" t="n">
-        <v>6648297</v>
+        <v>6648303</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1098,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1108,7 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408853</v>
+        <v>123411227</v>
       </c>
       <c r="B6" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,14 +1193,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620759</v>
+        <v>620502</v>
       </c>
       <c r="R6" t="n">
-        <v>6648492</v>
+        <v>6648313</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1214,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1224,12 +1242,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123410978</v>
+        <v>123409471</v>
       </c>
       <c r="B7" t="n">
-        <v>98396</v>
+        <v>74817</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1269,42 +1287,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620617</v>
+        <v>620802</v>
       </c>
       <c r="R7" t="n">
-        <v>6648344</v>
+        <v>6648510</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,14 +1351,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ca 30 bladrosetter</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123404593</v>
+        <v>123399558</v>
       </c>
       <c r="B8" t="n">
-        <v>57640</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1381,43 +1403,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620575</v>
+        <v>620398</v>
       </c>
       <c r="R8" t="n">
-        <v>6648228</v>
+        <v>6648248</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1449,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1459,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123401959</v>
+        <v>123408488</v>
       </c>
       <c r="B9" t="n">
-        <v>78426</v>
+        <v>98502</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1498,38 +1523,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620544</v>
+        <v>620679</v>
       </c>
       <c r="R9" t="n">
-        <v>6648151</v>
+        <v>6648540</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1561,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1571,7 +1596,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1598,10 +1628,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123404576</v>
+        <v>123407548</v>
       </c>
       <c r="B10" t="n">
-        <v>56697</v>
+        <v>98502</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,46 +1640,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620575</v>
+        <v>620609</v>
       </c>
       <c r="R10" t="n">
-        <v>6648228</v>
+        <v>6648383</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1681,7 +1703,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1691,12 +1713,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1723,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123399110</v>
+        <v>123410978</v>
       </c>
       <c r="B11" t="n">
-        <v>95060</v>
+        <v>98502</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1735,38 +1757,42 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620370</v>
+        <v>620617</v>
       </c>
       <c r="R11" t="n">
-        <v>6648255</v>
+        <v>6648344</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1796,19 +1822,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>11:17</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ca 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1817,6 +1838,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1835,10 +1857,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123410527</v>
+        <v>123401959</v>
       </c>
       <c r="B12" t="n">
-        <v>98396</v>
+        <v>78431</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1847,42 +1869,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620777</v>
+        <v>620544</v>
       </c>
       <c r="R12" t="n">
-        <v>6648494</v>
+        <v>6648151</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1914,7 +1932,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,12 +1942,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 10 bladroseter</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,7 +1951,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1957,10 +1969,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408009</v>
+        <v>123408853</v>
       </c>
       <c r="B13" t="n">
-        <v>56697</v>
+        <v>98502</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,35 +1981,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2005,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620718</v>
+        <v>620759</v>
       </c>
       <c r="R13" t="n">
-        <v>6648486</v>
+        <v>6648492</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2040,7 +2048,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2050,7 +2058,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2059,6 +2072,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2077,10 +2091,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123407548</v>
+        <v>123411112</v>
       </c>
       <c r="B14" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,14 +2127,14 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>620609</v>
       </c>
       <c r="R14" t="n">
-        <v>6648383</v>
+        <v>6648334</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2152,7 +2166,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2162,12 +2176,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2197,7 +2211,7 @@
         <v>123417364</v>
       </c>
       <c r="B15" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2300,10 +2314,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123406069</v>
+        <v>123399110</v>
       </c>
       <c r="B16" t="n">
-        <v>98396</v>
+        <v>95066</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2312,38 +2326,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620600</v>
+        <v>620370</v>
       </c>
       <c r="R16" t="n">
-        <v>6648303</v>
+        <v>6648255</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2375,7 +2389,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2385,12 +2399,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2417,10 +2426,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123402052</v>
+        <v>123398864</v>
       </c>
       <c r="B17" t="n">
-        <v>79399</v>
+        <v>56700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2429,38 +2438,46 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620544</v>
+        <v>620370</v>
       </c>
       <c r="R17" t="n">
-        <v>6648151</v>
+        <v>6648255</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2492,7 +2509,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2502,7 +2519,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2 krokar på tallåga</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2529,10 +2551,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123411112</v>
+        <v>123405636</v>
       </c>
       <c r="B18" t="n">
-        <v>98396</v>
+        <v>95066</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2541,38 +2563,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620609</v>
+        <v>620633</v>
       </c>
       <c r="R18" t="n">
-        <v>6648334</v>
+        <v>6648297</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2604,7 +2626,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2614,12 +2636,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>3 bladrosetter</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123399558</v>
+        <v>123402052</v>
       </c>
       <c r="B19" t="n">
-        <v>56697</v>
+        <v>79404</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2658,46 +2675,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620398</v>
+        <v>620544</v>
       </c>
       <c r="R19" t="n">
-        <v>6648248</v>
+        <v>6648151</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2729,7 +2738,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2739,7 +2748,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2766,10 +2775,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123398864</v>
+        <v>123404576</v>
       </c>
       <c r="B20" t="n">
-        <v>56697</v>
+        <v>56700</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,14 +2819,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620370</v>
+        <v>620575</v>
       </c>
       <c r="R20" t="n">
-        <v>6648255</v>
+        <v>6648228</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2849,7 +2858,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2859,12 +2868,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>2 krokar på tallåga</t>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,10 +2900,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123408488</v>
+        <v>123417137</v>
       </c>
       <c r="B21" t="n">
-        <v>98396</v>
+        <v>79404</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2903,41 +2912,44 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620679</v>
+        <v>620541</v>
       </c>
       <c r="R21" t="n">
-        <v>6648540</v>
+        <v>6648142</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2964,32 +2976,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Mer än 10 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3008,10 +3006,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123397574</v>
+        <v>123410527</v>
       </c>
       <c r="B22" t="n">
-        <v>56697</v>
+        <v>98502</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3020,46 +3018,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620364</v>
+        <v>620777</v>
       </c>
       <c r="R22" t="n">
-        <v>6648233</v>
+        <v>6648494</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3091,7 +3085,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3101,12 +3095,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>5 krokar på höjd</t>
+          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3115,6 +3109,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3133,10 +3128,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123417137</v>
+        <v>123417333</v>
       </c>
       <c r="B23" t="n">
-        <v>79399</v>
+        <v>98502</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3145,44 +3140,45 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620541</v>
+        <v>620596</v>
       </c>
       <c r="R23" t="n">
-        <v>6648142</v>
+        <v>6648322</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3212,6 +3208,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3239,10 +3240,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123406533</v>
+        <v>123405294</v>
       </c>
       <c r="B24" t="n">
-        <v>95942</v>
+        <v>98502</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3251,42 +3252,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620593</v>
+        <v>620610</v>
       </c>
       <c r="R24" t="n">
-        <v>6648325</v>
+        <v>6648299</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3318,7 +3315,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3328,12 +3325,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På understa lågan</t>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3342,7 +3339,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3361,10 +3357,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123409471</v>
+        <v>123402991</v>
       </c>
       <c r="B25" t="n">
-        <v>74814</v>
+        <v>56700</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3377,26 +3373,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6426</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3404,13 +3405,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620802</v>
+        <v>620551</v>
       </c>
       <c r="R25" t="n">
-        <v>6648510</v>
+        <v>6648134</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3439,7 +3440,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3449,7 +3450,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3458,7 +3459,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123411227</v>
+        <v>123407003</v>
       </c>
       <c r="B26" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3517,17 +3517,17 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620502</v>
+        <v>620581</v>
       </c>
       <c r="R26" t="n">
-        <v>6648313</v>
+        <v>6648381</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3554,24 +3554,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Mer än 35 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3599,10 +3589,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123405294</v>
+        <v>123406533</v>
       </c>
       <c r="B27" t="n">
-        <v>98396</v>
+        <v>95949</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3611,38 +3601,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620610</v>
+        <v>620593</v>
       </c>
       <c r="R27" t="n">
-        <v>6648299</v>
+        <v>6648325</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3674,7 +3668,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3684,12 +3678,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3698,6 +3692,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3716,10 +3711,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123417333</v>
+        <v>123404593</v>
       </c>
       <c r="B28" t="n">
-        <v>98396</v>
+        <v>57643</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3728,42 +3723,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620596</v>
+        <v>620575</v>
       </c>
       <c r="R28" t="n">
-        <v>6648322</v>
+        <v>6648228</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3793,14 +3789,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>13 bladrosetter</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3809,7 +3810,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>123398368</v>
       </c>
       <c r="B29" t="n">
-        <v>56689</v>
+        <v>56692</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3957,10 +3957,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123634578</v>
+        <v>123634710</v>
       </c>
       <c r="B30" t="n">
-        <v>74814</v>
+        <v>98502</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3969,41 +3969,55 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620451</v>
+        <v>620635</v>
       </c>
       <c r="R30" t="n">
-        <v>6648229</v>
+        <v>6648363</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4032,7 +4046,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4042,7 +4056,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4057,12 +4071,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4072,7 +4086,7 @@
         <v>123633877</v>
       </c>
       <c r="B31" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4195,10 +4209,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123634559</v>
+        <v>123632944</v>
       </c>
       <c r="B32" t="n">
-        <v>98396</v>
+        <v>105518</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4207,55 +4221,45 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620614</v>
+        <v>620398</v>
       </c>
       <c r="R32" t="n">
-        <v>6648335</v>
+        <v>6648248</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4284,7 +4288,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4294,7 +4298,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>25 bladrosetter</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4303,28 +4312,29 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123638984</v>
+        <v>123634512</v>
       </c>
       <c r="B33" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4354,24 +4364,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620528</v>
+        <v>620600</v>
       </c>
       <c r="R33" t="n">
-        <v>6648364</v>
+        <v>6648328</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4400,7 +4420,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4410,12 +4430,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4424,29 +4439,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123637283</v>
+        <v>123640236</v>
       </c>
       <c r="B34" t="n">
-        <v>95942</v>
+        <v>105518</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4455,38 +4469,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620603</v>
+        <v>620584</v>
       </c>
       <c r="R34" t="n">
-        <v>6648146</v>
+        <v>6648414</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4518,7 +4536,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4528,7 +4546,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4537,6 +4555,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4555,10 +4574,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123635547</v>
+        <v>123637481</v>
       </c>
       <c r="B35" t="n">
-        <v>98396</v>
+        <v>56700</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4567,55 +4586,46 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620556</v>
+        <v>620714</v>
       </c>
       <c r="R35" t="n">
-        <v>6648344</v>
+        <v>6648494</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4644,7 +4654,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4654,7 +4664,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4681,10 +4691,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123635541</v>
+        <v>123634578</v>
       </c>
       <c r="B36" t="n">
-        <v>57503</v>
+        <v>74817</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4693,46 +4703,41 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620556</v>
+        <v>620451</v>
       </c>
       <c r="R36" t="n">
-        <v>6648344</v>
+        <v>6648229</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4761,7 +4766,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4771,7 +4776,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4786,22 +4791,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123635839</v>
+        <v>123638047</v>
       </c>
       <c r="B37" t="n">
-        <v>57640</v>
+        <v>98502</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4810,50 +4815,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620523</v>
+        <v>620519</v>
       </c>
       <c r="R37" t="n">
-        <v>6648363</v>
+        <v>6648333</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4882,7 +4878,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4892,7 +4888,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4907,22 +4908,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123635666</v>
+        <v>123634655</v>
       </c>
       <c r="B38" t="n">
-        <v>57640</v>
+        <v>98502</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4931,40 +4932,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4973,13 +4974,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620526</v>
+        <v>620626</v>
       </c>
       <c r="R38" t="n">
-        <v>6648364</v>
+        <v>6648342</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5008,7 +5009,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5018,7 +5019,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5045,10 +5046,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123635824</v>
+        <v>123638984</v>
       </c>
       <c r="B39" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5078,34 +5079,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620523</v>
+        <v>620528</v>
       </c>
       <c r="R39" t="n">
-        <v>6648363</v>
+        <v>6648364</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5134,7 +5125,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5144,7 +5135,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5153,28 +5149,29 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123634264</v>
+        <v>123634559</v>
       </c>
       <c r="B40" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5206,7 +5203,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5225,13 +5222,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620584</v>
+        <v>620614</v>
       </c>
       <c r="R40" t="n">
-        <v>6648323</v>
+        <v>6648335</v>
       </c>
       <c r="S40" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5260,7 +5257,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5270,7 +5267,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5297,10 +5294,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123634500</v>
+        <v>123635839</v>
       </c>
       <c r="B41" t="n">
-        <v>98396</v>
+        <v>57643</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5309,55 +5306,50 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620604</v>
+        <v>620523</v>
       </c>
       <c r="R41" t="n">
-        <v>6648323</v>
+        <v>6648363</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5386,7 +5378,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5396,7 +5388,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5423,10 +5415,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123638047</v>
+        <v>123635824</v>
       </c>
       <c r="B42" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5456,20 +5448,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620519</v>
+        <v>620523</v>
       </c>
       <c r="R42" t="n">
-        <v>6648333</v>
+        <v>6648363</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5498,7 +5504,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5508,12 +5514,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5528,22 +5529,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123639666</v>
+        <v>123635230</v>
       </c>
       <c r="B43" t="n">
-        <v>57640</v>
+        <v>98502</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5552,55 +5553,55 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620713</v>
+        <v>620593</v>
       </c>
       <c r="R43" t="n">
-        <v>6648583</v>
+        <v>6648376</v>
       </c>
       <c r="S43" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5629,7 +5630,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5639,7 +5640,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5666,10 +5667,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123636168</v>
+        <v>123634264</v>
       </c>
       <c r="B44" t="n">
-        <v>95942</v>
+        <v>98502</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5678,45 +5679,55 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620443</v>
+        <v>620584</v>
       </c>
       <c r="R44" t="n">
-        <v>6648200</v>
+        <v>6648323</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5745,7 +5756,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5755,7 +5766,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5764,29 +5775,28 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123635390</v>
+        <v>123641070</v>
       </c>
       <c r="B45" t="n">
-        <v>90983</v>
+        <v>74690</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5795,25 +5805,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>6428</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5823,10 +5833,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620591</v>
+        <v>620466</v>
       </c>
       <c r="R45" t="n">
-        <v>6648347</v>
+        <v>6648235</v>
       </c>
       <c r="S45" t="n">
         <v>4</v>
@@ -5858,7 +5868,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5868,7 +5878,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5895,10 +5905,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123635230</v>
+        <v>123636168</v>
       </c>
       <c r="B46" t="n">
-        <v>98396</v>
+        <v>95949</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5907,55 +5917,45 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620593</v>
+        <v>620443</v>
       </c>
       <c r="R46" t="n">
-        <v>6648376</v>
+        <v>6648200</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5994,7 +5994,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6003,28 +6003,29 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123634512</v>
+        <v>123637283</v>
       </c>
       <c r="B47" t="n">
-        <v>98396</v>
+        <v>95949</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6033,55 +6034,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620600</v>
+        <v>620603</v>
       </c>
       <c r="R47" t="n">
-        <v>6648328</v>
+        <v>6648146</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6110,7 +6097,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6120,7 +6107,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6135,12 +6122,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6150,7 +6137,7 @@
         <v>123635548</v>
       </c>
       <c r="B48" t="n">
-        <v>57640</v>
+        <v>57643</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6272,10 +6259,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123637481</v>
+        <v>123635666</v>
       </c>
       <c r="B49" t="n">
-        <v>56697</v>
+        <v>57643</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6284,46 +6271,55 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620714</v>
+        <v>620526</v>
       </c>
       <c r="R49" t="n">
-        <v>6648494</v>
+        <v>6648364</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6352,7 +6348,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6362,7 +6358,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6389,10 +6385,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123632944</v>
+        <v>123635032</v>
       </c>
       <c r="B50" t="n">
-        <v>105502</v>
+        <v>98502</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6401,45 +6397,55 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620398</v>
+        <v>620640</v>
       </c>
       <c r="R50" t="n">
-        <v>6648248</v>
+        <v>6648367</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6468,7 +6474,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6478,12 +6484,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>25 bladrosetter</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6492,29 +6493,28 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123634655</v>
+        <v>123639666</v>
       </c>
       <c r="B51" t="n">
-        <v>98396</v>
+        <v>57643</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6523,55 +6523,55 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620626</v>
+        <v>620713</v>
       </c>
       <c r="R51" t="n">
-        <v>6648342</v>
+        <v>6648583</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6637,10 +6637,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123634710</v>
+        <v>123635390</v>
       </c>
       <c r="B52" t="n">
-        <v>98396</v>
+        <v>90988</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6649,55 +6649,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620635</v>
+        <v>620591</v>
       </c>
       <c r="R52" t="n">
-        <v>6648363</v>
+        <v>6648347</v>
       </c>
       <c r="S52" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6726,7 +6712,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6736,7 +6722,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6763,10 +6749,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123640236</v>
+        <v>123635547</v>
       </c>
       <c r="B53" t="n">
-        <v>105502</v>
+        <v>98502</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6775,45 +6761,55 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620584</v>
+        <v>620556</v>
       </c>
       <c r="R53" t="n">
-        <v>6648414</v>
+        <v>6648344</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6842,7 +6838,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6852,7 +6848,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6861,29 +6857,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123635032</v>
+        <v>123634500</v>
       </c>
       <c r="B54" t="n">
-        <v>98396</v>
+        <v>98502</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6915,7 +6910,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6934,13 +6929,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620640</v>
+        <v>620604</v>
       </c>
       <c r="R54" t="n">
-        <v>6648367</v>
+        <v>6648323</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6969,7 +6964,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6979,7 +6974,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7006,10 +7001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123641070</v>
+        <v>123635541</v>
       </c>
       <c r="B55" t="n">
-        <v>74687</v>
+        <v>57506</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7018,41 +7013,46 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620466</v>
+        <v>620556</v>
       </c>
       <c r="R55" t="n">
-        <v>6648235</v>
+        <v>6648344</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123408009</v>
+        <v>123417137</v>
       </c>
       <c r="B2" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,49 +687,44 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620718</v>
+        <v>620541</v>
       </c>
       <c r="R2" t="n">
-        <v>6648486</v>
+        <v>6648142</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -756,27 +751,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123397574</v>
+        <v>123410527</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>98504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,46 +793,42 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620364</v>
+        <v>620777</v>
       </c>
       <c r="R3" t="n">
-        <v>6648233</v>
+        <v>6648494</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -878,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -888,12 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>5 krokar på höjd</t>
+          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,6 +884,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -920,10 +903,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123404274</v>
+        <v>123417364</v>
       </c>
       <c r="B4" t="n">
-        <v>78431</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,21 +919,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -959,17 +942,17 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620569</v>
+        <v>620549</v>
       </c>
       <c r="R4" t="n">
-        <v>6648238</v>
+        <v>6648158</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,19 +979,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1036,10 +1009,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406069</v>
+        <v>123405636</v>
       </c>
       <c r="B5" t="n">
-        <v>98502</v>
+        <v>95068</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,25 +1021,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1076,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620600</v>
+        <v>620633</v>
       </c>
       <c r="R5" t="n">
-        <v>6648303</v>
+        <v>6648297</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1111,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1094,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1121,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123411227</v>
+        <v>123408488</v>
       </c>
       <c r="B6" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1187,20 +1155,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620502</v>
+        <v>620679</v>
       </c>
       <c r="R6" t="n">
-        <v>6648313</v>
+        <v>6648540</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1232,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1206,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,7 +1220,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1275,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123409471</v>
+        <v>123402991</v>
       </c>
       <c r="B7" t="n">
-        <v>74817</v>
+        <v>56700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,26 +1254,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6426</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1318,13 +1286,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620802</v>
+        <v>620551</v>
       </c>
       <c r="R7" t="n">
-        <v>6648510</v>
+        <v>6648134</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1353,7 +1321,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1331,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,7 +1340,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1391,10 +1358,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123399558</v>
+        <v>123404593</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1403,46 +1370,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620398</v>
+        <v>620575</v>
       </c>
       <c r="R8" t="n">
-        <v>6648248</v>
+        <v>6648228</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1474,7 +1438,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1448,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,10 +1475,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408488</v>
+        <v>123405294</v>
       </c>
       <c r="B9" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1551,10 +1515,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620679</v>
+        <v>620610</v>
       </c>
       <c r="R9" t="n">
-        <v>6648540</v>
+        <v>6648299</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1550,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,12 +1560,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1628,10 +1592,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123407548</v>
+        <v>123406069</v>
       </c>
       <c r="B10" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1668,10 +1632,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620609</v>
+        <v>620600</v>
       </c>
       <c r="R10" t="n">
-        <v>6648383</v>
+        <v>6648303</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1703,7 +1667,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1713,12 +1677,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1745,10 +1709,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123410978</v>
+        <v>123409471</v>
       </c>
       <c r="B11" t="n">
-        <v>98502</v>
+        <v>74818</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,42 +1721,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620617</v>
+        <v>620802</v>
       </c>
       <c r="R11" t="n">
-        <v>6648344</v>
+        <v>6648510</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1822,14 +1785,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:52</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 30 bladrosetter</t>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1857,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123401959</v>
+        <v>123407003</v>
       </c>
       <c r="B12" t="n">
-        <v>78431</v>
+        <v>98504</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,41 +1837,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620544</v>
+        <v>620581</v>
       </c>
       <c r="R12" t="n">
-        <v>6648151</v>
+        <v>6648381</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1930,19 +1902,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>12:03</t>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mer än 35 bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,6 +1918,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1969,10 +1937,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123408853</v>
+        <v>123406533</v>
       </c>
       <c r="B13" t="n">
-        <v>98502</v>
+        <v>95951</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,25 +1949,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2013,10 +1981,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620759</v>
+        <v>620593</v>
       </c>
       <c r="R13" t="n">
-        <v>6648492</v>
+        <v>6648325</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2048,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2058,12 +2026,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2091,10 +2059,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123411112</v>
+        <v>123408009</v>
       </c>
       <c r="B14" t="n">
-        <v>98502</v>
+        <v>56700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,38 +2071,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620609</v>
+        <v>620718</v>
       </c>
       <c r="R14" t="n">
-        <v>6648334</v>
+        <v>6648486</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2166,7 +2142,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2176,12 +2152,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>3 bladrosetter</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123417364</v>
+        <v>123399110</v>
       </c>
       <c r="B15" t="n">
-        <v>78786</v>
+        <v>95068</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2220,44 +2191,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620549</v>
+        <v>620370</v>
       </c>
       <c r="R15" t="n">
-        <v>6648158</v>
+        <v>6648255</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2284,18 +2252,27 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:17</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2314,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123399110</v>
+        <v>123404274</v>
       </c>
       <c r="B16" t="n">
-        <v>95066</v>
+        <v>78433</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2326,38 +2303,41 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620370</v>
+        <v>620569</v>
       </c>
       <c r="R16" t="n">
-        <v>6648255</v>
+        <v>6648238</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2389,7 +2369,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2399,7 +2379,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2408,6 +2388,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2426,10 +2407,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123398864</v>
+        <v>123410978</v>
       </c>
       <c r="B17" t="n">
-        <v>56700</v>
+        <v>98504</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2438,35 +2419,31 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2474,10 +2451,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620370</v>
+        <v>620617</v>
       </c>
       <c r="R17" t="n">
-        <v>6648255</v>
+        <v>6648344</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2507,24 +2484,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>2 krokar på tallåga</t>
+          <t>Ca 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2533,6 +2500,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2551,10 +2519,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123405636</v>
+        <v>123402052</v>
       </c>
       <c r="B18" t="n">
-        <v>95066</v>
+        <v>79406</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2563,38 +2531,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620633</v>
+        <v>620544</v>
       </c>
       <c r="R18" t="n">
-        <v>6648297</v>
+        <v>6648151</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2626,7 +2594,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2636,7 +2604,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,10 +2631,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123402052</v>
+        <v>123411227</v>
       </c>
       <c r="B19" t="n">
-        <v>79404</v>
+        <v>98504</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,38 +2643,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620544</v>
+        <v>620502</v>
       </c>
       <c r="R19" t="n">
-        <v>6648151</v>
+        <v>6648313</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2738,7 +2710,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2748,7 +2720,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2757,6 +2734,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2775,10 +2753,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123404576</v>
+        <v>123417333</v>
       </c>
       <c r="B20" t="n">
-        <v>56700</v>
+        <v>98504</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2787,46 +2765,42 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620575</v>
+        <v>620596</v>
       </c>
       <c r="R20" t="n">
-        <v>6648228</v>
+        <v>6648322</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2856,24 +2830,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2882,6 +2846,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2900,10 +2865,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123417137</v>
+        <v>123399558</v>
       </c>
       <c r="B21" t="n">
-        <v>79404</v>
+        <v>56700</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2912,30 +2877,35 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2943,13 +2913,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620541</v>
+        <v>620398</v>
       </c>
       <c r="R21" t="n">
-        <v>6648142</v>
+        <v>6648248</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2976,18 +2946,27 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3006,10 +2985,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123410527</v>
+        <v>123404576</v>
       </c>
       <c r="B22" t="n">
-        <v>98502</v>
+        <v>56700</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3018,42 +2997,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620777</v>
+        <v>620575</v>
       </c>
       <c r="R22" t="n">
-        <v>6648494</v>
+        <v>6648228</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3085,7 +3068,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3095,12 +3078,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Ca 10 bladroseter</t>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3109,7 +3092,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3128,10 +3110,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123417333</v>
+        <v>123401959</v>
       </c>
       <c r="B23" t="n">
-        <v>98502</v>
+        <v>78433</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3140,42 +3122,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620596</v>
+        <v>620544</v>
       </c>
       <c r="R23" t="n">
-        <v>6648322</v>
+        <v>6648151</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3205,14 +3183,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>13 bladrosetter</t>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3221,7 +3204,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3240,10 +3222,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123405294</v>
+        <v>123397574</v>
       </c>
       <c r="B24" t="n">
-        <v>98502</v>
+        <v>56700</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3252,38 +3234,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620610</v>
+        <v>620364</v>
       </c>
       <c r="R24" t="n">
-        <v>6648299</v>
+        <v>6648233</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3315,7 +3305,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3325,12 +3315,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3357,7 +3347,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123402991</v>
+        <v>123398864</v>
       </c>
       <c r="B25" t="n">
         <v>56700</v>
@@ -3401,17 +3391,17 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620551</v>
+        <v>620370</v>
       </c>
       <c r="R25" t="n">
-        <v>6648134</v>
+        <v>6648255</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3440,7 +3430,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3450,7 +3440,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>2 krokar på tallåga</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3477,10 +3472,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123407003</v>
+        <v>123407548</v>
       </c>
       <c r="B26" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3511,23 +3506,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620581</v>
+        <v>620609</v>
       </c>
       <c r="R26" t="n">
-        <v>6648381</v>
+        <v>6648383</v>
       </c>
       <c r="S26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3554,14 +3545,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Mer än 35 bladrosetter</t>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3570,7 +3571,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3589,10 +3589,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123406533</v>
+        <v>123408853</v>
       </c>
       <c r="B27" t="n">
-        <v>95949</v>
+        <v>98504</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3601,25 +3601,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3633,10 +3633,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620593</v>
+        <v>620759</v>
       </c>
       <c r="R27" t="n">
-        <v>6648325</v>
+        <v>6648492</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3668,7 +3668,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3678,12 +3678,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>På understa lågan</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3711,10 +3711,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123404593</v>
+        <v>123411112</v>
       </c>
       <c r="B28" t="n">
-        <v>57643</v>
+        <v>98504</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3723,43 +3723,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620575</v>
+        <v>620609</v>
       </c>
       <c r="R28" t="n">
-        <v>6648228</v>
+        <v>6648334</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3791,7 +3786,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,7 +3796,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3957,10 +3957,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123634710</v>
+        <v>123634512</v>
       </c>
       <c r="B30" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -4011,13 +4011,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620635</v>
+        <v>620600</v>
       </c>
       <c r="R30" t="n">
-        <v>6648363</v>
+        <v>6648328</v>
       </c>
       <c r="S30" t="n">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4083,10 +4083,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123633877</v>
+        <v>123632944</v>
       </c>
       <c r="B31" t="n">
-        <v>57860</v>
+        <v>105520</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4099,51 +4099,41 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103015</v>
+        <v>221144</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620537</v>
+        <v>620398</v>
       </c>
       <c r="R31" t="n">
-        <v>6648292</v>
+        <v>6648248</v>
       </c>
       <c r="S31" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4172,7 +4162,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4182,7 +4172,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>25 bladrosetter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4191,28 +4186,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123632944</v>
+        <v>123635230</v>
       </c>
       <c r="B32" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4221,45 +4217,55 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620398</v>
+        <v>620593</v>
       </c>
       <c r="R32" t="n">
-        <v>6648248</v>
+        <v>6648376</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4288,7 +4294,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4298,12 +4304,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>25 bladrosetter</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4312,29 +4313,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123634512</v>
+        <v>123636168</v>
       </c>
       <c r="B33" t="n">
-        <v>98502</v>
+        <v>95951</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4343,55 +4343,45 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620600</v>
+        <v>620443</v>
       </c>
       <c r="R33" t="n">
-        <v>6648328</v>
+        <v>6648200</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4420,7 +4410,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4430,7 +4420,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4439,28 +4429,29 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123640236</v>
+        <v>123634559</v>
       </c>
       <c r="B34" t="n">
-        <v>105518</v>
+        <v>98504</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4469,45 +4460,55 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620584</v>
+        <v>620614</v>
       </c>
       <c r="R34" t="n">
-        <v>6648414</v>
+        <v>6648335</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4536,7 +4537,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4546,7 +4547,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4555,29 +4556,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123637481</v>
+        <v>123633877</v>
       </c>
       <c r="B35" t="n">
-        <v>56700</v>
+        <v>57861</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4590,42 +4590,51 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>103015</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620714</v>
+        <v>620537</v>
       </c>
       <c r="R35" t="n">
-        <v>6648494</v>
+        <v>6648292</v>
       </c>
       <c r="S35" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4654,7 +4663,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4664,7 +4673,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4691,10 +4700,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123634578</v>
+        <v>123635824</v>
       </c>
       <c r="B36" t="n">
-        <v>74817</v>
+        <v>98504</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4703,41 +4712,55 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620451</v>
+        <v>620523</v>
       </c>
       <c r="R36" t="n">
-        <v>6648229</v>
+        <v>6648363</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4766,7 +4789,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4776,7 +4799,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4791,22 +4814,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123638047</v>
+        <v>123634578</v>
       </c>
       <c r="B37" t="n">
-        <v>98502</v>
+        <v>74818</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4815,25 +4838,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4843,10 +4866,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620519</v>
+        <v>620451</v>
       </c>
       <c r="R37" t="n">
-        <v>6648333</v>
+        <v>6648229</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4878,7 +4901,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4888,12 +4911,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4920,10 +4938,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123634655</v>
+        <v>123634264</v>
       </c>
       <c r="B38" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4955,7 +4973,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4974,13 +4992,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620626</v>
+        <v>620584</v>
       </c>
       <c r="R38" t="n">
-        <v>6648342</v>
+        <v>6648323</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5009,7 +5027,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5019,7 +5037,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5046,10 +5064,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123638984</v>
+        <v>123637481</v>
       </c>
       <c r="B39" t="n">
-        <v>98502</v>
+        <v>56700</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5058,45 +5076,46 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620528</v>
+        <v>620714</v>
       </c>
       <c r="R39" t="n">
-        <v>6648364</v>
+        <v>6648494</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5125,7 +5144,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5135,12 +5154,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5149,29 +5163,28 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123634559</v>
+        <v>123635839</v>
       </c>
       <c r="B40" t="n">
-        <v>98502</v>
+        <v>57644</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5180,52 +5193,47 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620614</v>
+        <v>620523</v>
       </c>
       <c r="R40" t="n">
-        <v>6648335</v>
+        <v>6648363</v>
       </c>
       <c r="S40" t="n">
         <v>12</v>
@@ -5257,7 +5265,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5267,7 +5275,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5294,10 +5302,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123635839</v>
+        <v>123638984</v>
       </c>
       <c r="B41" t="n">
-        <v>57643</v>
+        <v>98504</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5306,50 +5314,45 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620523</v>
+        <v>620528</v>
       </c>
       <c r="R41" t="n">
-        <v>6648363</v>
+        <v>6648364</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5378,7 +5381,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5388,7 +5391,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5397,28 +5405,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123635824</v>
+        <v>123635390</v>
       </c>
       <c r="B42" t="n">
-        <v>98502</v>
+        <v>90990</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5427,55 +5436,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620523</v>
+        <v>620591</v>
       </c>
       <c r="R42" t="n">
-        <v>6648363</v>
+        <v>6648347</v>
       </c>
       <c r="S42" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5504,7 +5499,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5514,7 +5509,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5541,10 +5536,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123635230</v>
+        <v>123635547</v>
       </c>
       <c r="B43" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5576,7 +5571,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5595,13 +5590,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620593</v>
+        <v>620556</v>
       </c>
       <c r="R43" t="n">
-        <v>6648376</v>
+        <v>6648344</v>
       </c>
       <c r="S43" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5630,7 +5625,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5640,7 +5635,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5667,10 +5662,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123634264</v>
+        <v>123639666</v>
       </c>
       <c r="B44" t="n">
-        <v>98502</v>
+        <v>57644</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5679,55 +5674,55 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620584</v>
+        <v>620713</v>
       </c>
       <c r="R44" t="n">
-        <v>6648323</v>
+        <v>6648583</v>
       </c>
       <c r="S44" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5756,7 +5751,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5766,7 +5761,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5793,10 +5788,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123641070</v>
+        <v>123635541</v>
       </c>
       <c r="B45" t="n">
-        <v>74690</v>
+        <v>57507</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5805,41 +5800,46 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6428</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620466</v>
+        <v>620556</v>
       </c>
       <c r="R45" t="n">
-        <v>6648235</v>
+        <v>6648344</v>
       </c>
       <c r="S45" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5905,10 +5905,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123636168</v>
+        <v>123637283</v>
       </c>
       <c r="B46" t="n">
-        <v>95949</v>
+        <v>95951</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5939,20 +5939,16 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620443</v>
+        <v>620603</v>
       </c>
       <c r="R46" t="n">
-        <v>6648200</v>
+        <v>6648146</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5984,7 +5980,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5994,7 +5990,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6003,7 +5999,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6022,10 +6017,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123637283</v>
+        <v>123634500</v>
       </c>
       <c r="B47" t="n">
-        <v>95949</v>
+        <v>98504</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6034,41 +6029,55 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620603</v>
+        <v>620604</v>
       </c>
       <c r="R47" t="n">
-        <v>6648146</v>
+        <v>6648323</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6097,7 +6106,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6107,7 +6116,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6122,22 +6131,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123635548</v>
+        <v>123638047</v>
       </c>
       <c r="B48" t="n">
-        <v>57643</v>
+        <v>98504</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6146,49 +6155,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620334</v>
+        <v>620519</v>
       </c>
       <c r="R48" t="n">
-        <v>6648148</v>
+        <v>6648333</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6217,7 +6218,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6227,12 +6228,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 ex sjöng från tallgren</t>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6262,7 +6263,7 @@
         <v>123635666</v>
       </c>
       <c r="B49" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6385,10 +6386,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123635032</v>
+        <v>123635548</v>
       </c>
       <c r="B50" t="n">
-        <v>98502</v>
+        <v>57644</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6397,55 +6398,49 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620640</v>
+        <v>620334</v>
       </c>
       <c r="R50" t="n">
-        <v>6648367</v>
+        <v>6648148</v>
       </c>
       <c r="S50" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6474,7 +6469,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6484,7 +6479,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>1 ex sjöng från tallgren</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6499,22 +6499,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123639666</v>
+        <v>123640236</v>
       </c>
       <c r="B51" t="n">
-        <v>57643</v>
+        <v>105520</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6523,55 +6523,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620713</v>
+        <v>620584</v>
       </c>
       <c r="R51" t="n">
-        <v>6648583</v>
+        <v>6648414</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6600,7 +6590,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6610,7 +6600,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6619,28 +6609,29 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123635390</v>
+        <v>123634710</v>
       </c>
       <c r="B52" t="n">
-        <v>90988</v>
+        <v>98504</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6649,41 +6640,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620591</v>
+        <v>620635</v>
       </c>
       <c r="R52" t="n">
-        <v>6648347</v>
+        <v>6648363</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6712,7 +6717,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6722,7 +6727,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6749,10 +6754,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123635547</v>
+        <v>123634655</v>
       </c>
       <c r="B53" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6784,7 +6789,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6803,13 +6808,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620556</v>
+        <v>620626</v>
       </c>
       <c r="R53" t="n">
-        <v>6648344</v>
+        <v>6648342</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6838,7 +6843,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6848,7 +6853,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6875,10 +6880,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123634500</v>
+        <v>123635032</v>
       </c>
       <c r="B54" t="n">
-        <v>98502</v>
+        <v>98504</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6910,7 +6915,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6929,13 +6934,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620604</v>
+        <v>620640</v>
       </c>
       <c r="R54" t="n">
-        <v>6648323</v>
+        <v>6648367</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6964,7 +6969,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6974,7 +6979,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7001,10 +7006,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123635541</v>
+        <v>123641070</v>
       </c>
       <c r="B55" t="n">
-        <v>57506</v>
+        <v>74691</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7013,46 +7018,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6428</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620556</v>
+        <v>620466</v>
       </c>
       <c r="R55" t="n">
-        <v>6648344</v>
+        <v>6648235</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7121,7 +7121,7 @@
         <v>123829229</v>
       </c>
       <c r="B56" t="n">
-        <v>57643</v>
+        <v>57644</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -4574,10 +4574,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123633877</v>
+        <v>123634578</v>
       </c>
       <c r="B35" t="n">
-        <v>57861</v>
+        <v>74818</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4590,51 +4590,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103015</v>
+        <v>6426</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620537</v>
+        <v>620451</v>
       </c>
       <c r="R35" t="n">
-        <v>6648292</v>
+        <v>6648229</v>
       </c>
       <c r="S35" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4663,7 +4649,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4673,7 +4659,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4688,22 +4674,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123635824</v>
+        <v>123633877</v>
       </c>
       <c r="B36" t="n">
-        <v>98504</v>
+        <v>57861</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4712,40 +4698,40 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4754,13 +4740,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620523</v>
+        <v>620537</v>
       </c>
       <c r="R36" t="n">
-        <v>6648363</v>
+        <v>6648292</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4789,7 +4775,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4799,7 +4785,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4826,10 +4812,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123634578</v>
+        <v>123635824</v>
       </c>
       <c r="B37" t="n">
-        <v>74818</v>
+        <v>98504</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4838,41 +4824,55 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620451</v>
+        <v>620523</v>
       </c>
       <c r="R37" t="n">
-        <v>6648229</v>
+        <v>6648363</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4926,12 +4926,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5064,10 +5064,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123637481</v>
+        <v>123638984</v>
       </c>
       <c r="B39" t="n">
-        <v>56700</v>
+        <v>98504</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5076,46 +5076,45 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620714</v>
+        <v>620528</v>
       </c>
       <c r="R39" t="n">
-        <v>6648494</v>
+        <v>6648364</v>
       </c>
       <c r="S39" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5144,7 +5143,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5154,7 +5153,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5163,18 +5167,19 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5302,10 +5307,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123638984</v>
+        <v>123637481</v>
       </c>
       <c r="B41" t="n">
-        <v>98504</v>
+        <v>56700</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5314,45 +5319,46 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620528</v>
+        <v>620714</v>
       </c>
       <c r="R41" t="n">
-        <v>6648364</v>
+        <v>6648494</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5381,7 +5387,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5391,12 +5397,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5405,19 +5406,18 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6628,10 +6628,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123634710</v>
+        <v>123641070</v>
       </c>
       <c r="B52" t="n">
-        <v>98504</v>
+        <v>74691</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6640,55 +6640,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620635</v>
+        <v>620466</v>
       </c>
       <c r="R52" t="n">
-        <v>6648363</v>
+        <v>6648235</v>
       </c>
       <c r="S52" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6717,7 +6703,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6727,7 +6713,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6754,7 +6740,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123634655</v>
+        <v>123634710</v>
       </c>
       <c r="B53" t="n">
         <v>98504</v>
@@ -6789,7 +6775,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -6808,13 +6794,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620626</v>
+        <v>620635</v>
       </c>
       <c r="R53" t="n">
-        <v>6648342</v>
+        <v>6648363</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6843,7 +6829,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6853,7 +6839,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6880,7 +6866,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123635032</v>
+        <v>123634655</v>
       </c>
       <c r="B54" t="n">
         <v>98504</v>
@@ -6915,7 +6901,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6934,13 +6920,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620640</v>
+        <v>620626</v>
       </c>
       <c r="R54" t="n">
-        <v>6648367</v>
+        <v>6648342</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6969,7 +6955,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6979,7 +6965,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7006,10 +6992,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123641070</v>
+        <v>123635032</v>
       </c>
       <c r="B55" t="n">
-        <v>74691</v>
+        <v>98504</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7018,41 +7004,55 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620466</v>
+        <v>620640</v>
       </c>
       <c r="R55" t="n">
-        <v>6648235</v>
+        <v>6648367</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -2179,10 +2179,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123399110</v>
+        <v>123404274</v>
       </c>
       <c r="B15" t="n">
-        <v>95068</v>
+        <v>78433</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,38 +2191,41 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620370</v>
+        <v>620569</v>
       </c>
       <c r="R15" t="n">
-        <v>6648255</v>
+        <v>6648238</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2254,7 +2257,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2264,7 +2267,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2273,6 +2276,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2291,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123404274</v>
+        <v>123399110</v>
       </c>
       <c r="B16" t="n">
-        <v>78433</v>
+        <v>95068</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,41 +2307,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>353</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620569</v>
+        <v>620370</v>
       </c>
       <c r="R16" t="n">
-        <v>6648238</v>
+        <v>6648255</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,7 +2370,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2379,7 +2380,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2388,7 +2389,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123417137</v>
+        <v>123401959</v>
       </c>
       <c r="B2" t="n">
-        <v>79406</v>
+        <v>78433</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620541</v>
+        <v>620544</v>
       </c>
       <c r="R2" t="n">
-        <v>6648142</v>
+        <v>6648151</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,18 +748,27 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:03</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -781,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123410527</v>
+        <v>123408853</v>
       </c>
       <c r="B3" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,14 +827,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620777</v>
+        <v>620759</v>
       </c>
       <c r="R3" t="n">
-        <v>6648494</v>
+        <v>6648492</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -860,7 +866,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +876,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ca 10 bladroseter</t>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123417364</v>
+        <v>123411227</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,30 +921,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -946,13 +953,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620549</v>
+        <v>620502</v>
       </c>
       <c r="R4" t="n">
-        <v>6648158</v>
+        <v>6648313</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,9 +986,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,10 +1031,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123405636</v>
+        <v>123406533</v>
       </c>
       <c r="B5" t="n">
-        <v>95068</v>
+        <v>96332</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,38 +1043,42 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620633</v>
+        <v>620593</v>
       </c>
       <c r="R5" t="n">
-        <v>6648297</v>
+        <v>6648325</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1084,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,7 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,6 +1134,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1121,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123408488</v>
+        <v>123404576</v>
       </c>
       <c r="B6" t="n">
-        <v>98504</v>
+        <v>56700</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,38 +1165,46 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620679</v>
+        <v>620575</v>
       </c>
       <c r="R6" t="n">
-        <v>6648540</v>
+        <v>6648228</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1196,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,12 +1246,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123402991</v>
+        <v>123402052</v>
       </c>
       <c r="B7" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,49 +1290,41 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620551</v>
+        <v>620544</v>
       </c>
       <c r="R7" t="n">
-        <v>6648134</v>
+        <v>6648151</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1321,7 +1353,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1331,7 +1363,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,10 +1390,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123404593</v>
+        <v>123407548</v>
       </c>
       <c r="B8" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1370,43 +1402,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620575</v>
+        <v>620609</v>
       </c>
       <c r="R8" t="n">
-        <v>6648228</v>
+        <v>6648383</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1438,7 +1465,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1448,7 +1475,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1475,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123405294</v>
+        <v>123417137</v>
       </c>
       <c r="B9" t="n">
-        <v>98504</v>
+        <v>79406</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1487,41 +1519,44 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620610</v>
+        <v>620541</v>
       </c>
       <c r="R9" t="n">
-        <v>6648299</v>
+        <v>6648142</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1548,32 +1583,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1592,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123406069</v>
+        <v>123417364</v>
       </c>
       <c r="B10" t="n">
-        <v>98504</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1604,41 +1625,44 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620600</v>
+        <v>620549</v>
       </c>
       <c r="R10" t="n">
-        <v>6648303</v>
+        <v>6648158</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1665,32 +1689,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1709,10 +1719,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123409471</v>
+        <v>123411112</v>
       </c>
       <c r="B11" t="n">
-        <v>74818</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,41 +1731,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620802</v>
+        <v>620609</v>
       </c>
       <c r="R11" t="n">
-        <v>6648510</v>
+        <v>6648334</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1787,7 +1794,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1797,7 +1804,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,7 +1818,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1825,10 +1836,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123407003</v>
+        <v>123397574</v>
       </c>
       <c r="B12" t="n">
-        <v>98504</v>
+        <v>56700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,31 +1848,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1869,13 +1884,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620581</v>
+        <v>620364</v>
       </c>
       <c r="R12" t="n">
-        <v>6648381</v>
+        <v>6648233</v>
       </c>
       <c r="S12" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1902,14 +1917,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Mer än 35 bladrosetter</t>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,7 +1943,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1937,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123406533</v>
+        <v>123399110</v>
       </c>
       <c r="B13" t="n">
-        <v>95951</v>
+        <v>95576</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1949,42 +1973,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620593</v>
+        <v>620370</v>
       </c>
       <c r="R13" t="n">
-        <v>6648325</v>
+        <v>6648255</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2016,7 +2036,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,12 +2046,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>På understa lågan</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2040,7 +2055,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2059,10 +2073,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408009</v>
+        <v>123408488</v>
       </c>
       <c r="B14" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,46 +2085,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620718</v>
+        <v>620679</v>
       </c>
       <c r="R14" t="n">
-        <v>6648486</v>
+        <v>6648540</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2142,7 +2148,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2152,7 +2158,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2179,10 +2190,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123404274</v>
+        <v>123410978</v>
       </c>
       <c r="B15" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,41 +2202,42 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620569</v>
+        <v>620617</v>
       </c>
       <c r="R15" t="n">
-        <v>6648238</v>
+        <v>6648344</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2255,19 +2267,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:08</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ca 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2295,10 +2302,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123399110</v>
+        <v>123406069</v>
       </c>
       <c r="B16" t="n">
-        <v>95068</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,38 +2314,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620370</v>
+        <v>620600</v>
       </c>
       <c r="R16" t="n">
-        <v>6648255</v>
+        <v>6648303</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2370,7 +2377,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2380,7 +2387,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,10 +2419,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123410978</v>
+        <v>123405294</v>
       </c>
       <c r="B17" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2441,20 +2453,16 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620617</v>
+        <v>620610</v>
       </c>
       <c r="R17" t="n">
-        <v>6648344</v>
+        <v>6648299</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2484,14 +2492,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ca 30 bladrosetter</t>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2500,7 +2518,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2519,10 +2536,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123402052</v>
+        <v>123410527</v>
       </c>
       <c r="B18" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2531,38 +2548,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620544</v>
+        <v>620777</v>
       </c>
       <c r="R18" t="n">
-        <v>6648151</v>
+        <v>6648494</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2594,7 +2615,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2604,7 +2625,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2613,6 +2639,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2631,10 +2658,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123411227</v>
+        <v>123405636</v>
       </c>
       <c r="B19" t="n">
-        <v>98504</v>
+        <v>95576</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2643,42 +2670,38 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620502</v>
+        <v>620633</v>
       </c>
       <c r="R19" t="n">
-        <v>6648313</v>
+        <v>6648297</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2710,7 +2733,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2720,12 +2743,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2734,7 +2752,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2756,7 +2773,7 @@
         <v>123417333</v>
       </c>
       <c r="B20" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2865,7 +2882,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123399558</v>
+        <v>123398864</v>
       </c>
       <c r="B21" t="n">
         <v>56700</v>
@@ -2913,10 +2930,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620398</v>
+        <v>620370</v>
       </c>
       <c r="R21" t="n">
-        <v>6648248</v>
+        <v>6648255</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2948,7 +2965,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2958,7 +2975,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>2 krokar på tallåga</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2985,10 +3007,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123404576</v>
+        <v>123404593</v>
       </c>
       <c r="B22" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2997,36 +3019,33 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Bålmyran, norr om , Upl</t>
@@ -3068,7 +3087,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3078,12 +3097,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3110,10 +3124,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123401959</v>
+        <v>123408009</v>
       </c>
       <c r="B23" t="n">
-        <v>78433</v>
+        <v>56700</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3122,38 +3136,46 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620544</v>
+        <v>620718</v>
       </c>
       <c r="R23" t="n">
-        <v>6648151</v>
+        <v>6648486</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3185,7 +3207,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3195,7 +3217,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3222,7 +3244,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123397574</v>
+        <v>123402991</v>
       </c>
       <c r="B24" t="n">
         <v>56700</v>
@@ -3270,13 +3292,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620364</v>
+        <v>620551</v>
       </c>
       <c r="R24" t="n">
-        <v>6648233</v>
+        <v>6648134</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3305,7 +3327,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3315,12 +3337,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>5 krokar på höjd</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3347,10 +3364,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123398864</v>
+        <v>123404274</v>
       </c>
       <c r="B25" t="n">
-        <v>56700</v>
+        <v>78433</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3359,46 +3376,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620370</v>
+        <v>620569</v>
       </c>
       <c r="R25" t="n">
-        <v>6648255</v>
+        <v>6648238</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3430,7 +3442,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3440,12 +3452,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>2 krokar på tallåga</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3454,6 +3461,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3472,10 +3480,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123407548</v>
+        <v>123399558</v>
       </c>
       <c r="B26" t="n">
-        <v>98504</v>
+        <v>56700</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3484,38 +3492,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620609</v>
+        <v>620398</v>
       </c>
       <c r="R26" t="n">
-        <v>6648383</v>
+        <v>6648248</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3547,7 +3563,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3557,12 +3573,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3589,10 +3600,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123408853</v>
+        <v>123409471</v>
       </c>
       <c r="B27" t="n">
-        <v>98504</v>
+        <v>74818</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3601,31 +3612,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3633,10 +3643,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620759</v>
+        <v>620802</v>
       </c>
       <c r="R27" t="n">
-        <v>6648492</v>
+        <v>6648510</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3668,7 +3678,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3678,12 +3688,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>5 bladrosetter</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3711,10 +3716,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123411112</v>
+        <v>123407003</v>
       </c>
       <c r="B28" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3745,19 +3750,23 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620609</v>
+        <v>620581</v>
       </c>
       <c r="R28" t="n">
-        <v>6648334</v>
+        <v>6648381</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3784,24 +3793,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>16:49</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>16:49</t>
-        </is>
-      </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>3 bladrosetter</t>
+          <t>Mer än 35 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3810,6 +3809,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3957,10 +3957,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123634512</v>
+        <v>123635548</v>
       </c>
       <c r="B30" t="n">
-        <v>98504</v>
+        <v>57644</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3969,55 +3969,49 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620600</v>
+        <v>620334</v>
       </c>
       <c r="R30" t="n">
-        <v>6648328</v>
+        <v>6648148</v>
       </c>
       <c r="S30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4046,7 +4040,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4056,7 +4050,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>1 ex sjöng från tallgren</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4071,22 +4070,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123632944</v>
+        <v>123637283</v>
       </c>
       <c r="B31" t="n">
-        <v>105520</v>
+        <v>96332</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4095,45 +4094,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620398</v>
+        <v>620603</v>
       </c>
       <c r="R31" t="n">
-        <v>6648248</v>
+        <v>6648146</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4162,7 +4157,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4172,12 +4167,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>25 bladrosetter</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4186,7 +4176,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4205,10 +4194,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123635230</v>
+        <v>123641070</v>
       </c>
       <c r="B32" t="n">
-        <v>98504</v>
+        <v>74691</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4217,52 +4206,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620593</v>
+        <v>620466</v>
       </c>
       <c r="R32" t="n">
-        <v>6648376</v>
+        <v>6648235</v>
       </c>
       <c r="S32" t="n">
         <v>4</v>
@@ -4294,7 +4269,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4304,7 +4279,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4331,10 +4306,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123636168</v>
+        <v>123635666</v>
       </c>
       <c r="B33" t="n">
-        <v>95951</v>
+        <v>57644</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4347,41 +4322,51 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620443</v>
+        <v>620526</v>
       </c>
       <c r="R33" t="n">
-        <v>6648200</v>
+        <v>6648364</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4410,7 +4395,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4420,7 +4405,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4429,29 +4414,28 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123634559</v>
+        <v>123634264</v>
       </c>
       <c r="B34" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4483,7 +4467,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4502,13 +4486,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620614</v>
+        <v>620584</v>
       </c>
       <c r="R34" t="n">
-        <v>6648335</v>
+        <v>6648323</v>
       </c>
       <c r="S34" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4537,7 +4521,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4547,7 +4531,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4574,10 +4558,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123634578</v>
+        <v>123636168</v>
       </c>
       <c r="B35" t="n">
-        <v>74818</v>
+        <v>96332</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4586,38 +4570,42 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6426</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620451</v>
+        <v>620443</v>
       </c>
       <c r="R35" t="n">
-        <v>6648229</v>
+        <v>6648200</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4649,7 +4637,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4659,7 +4647,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4668,6 +4656,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4686,10 +4675,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123633877</v>
+        <v>123635824</v>
       </c>
       <c r="B36" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4698,40 +4687,40 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4740,13 +4729,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620537</v>
+        <v>620523</v>
       </c>
       <c r="R36" t="n">
-        <v>6648292</v>
+        <v>6648363</v>
       </c>
       <c r="S36" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4775,7 +4764,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4785,7 +4774,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4812,10 +4801,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123635824</v>
+        <v>123635547</v>
       </c>
       <c r="B37" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4847,7 +4836,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -4866,13 +4855,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620523</v>
+        <v>620556</v>
       </c>
       <c r="R37" t="n">
-        <v>6648363</v>
+        <v>6648344</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4901,7 +4890,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4911,7 +4900,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4938,10 +4927,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123634264</v>
+        <v>123634655</v>
       </c>
       <c r="B38" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4973,7 +4962,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>87</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4992,13 +4981,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620584</v>
+        <v>620626</v>
       </c>
       <c r="R38" t="n">
-        <v>6648323</v>
+        <v>6648342</v>
       </c>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5027,7 +5016,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5037,7 +5026,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5064,10 +5053,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123638984</v>
+        <v>123640236</v>
       </c>
       <c r="B39" t="n">
-        <v>98504</v>
+        <v>105095</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5076,25 +5065,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5108,10 +5097,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620528</v>
+        <v>620584</v>
       </c>
       <c r="R39" t="n">
-        <v>6648364</v>
+        <v>6648414</v>
       </c>
       <c r="S39" t="n">
         <v>20</v>
@@ -5143,7 +5132,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5153,12 +5142,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5186,10 +5170,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123635839</v>
+        <v>123635032</v>
       </c>
       <c r="B40" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5198,47 +5182,52 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620523</v>
+        <v>620640</v>
       </c>
       <c r="R40" t="n">
-        <v>6648363</v>
+        <v>6648367</v>
       </c>
       <c r="S40" t="n">
         <v>12</v>
@@ -5270,7 +5259,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5280,7 +5269,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5307,10 +5296,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123637481</v>
+        <v>123632944</v>
       </c>
       <c r="B41" t="n">
-        <v>56700</v>
+        <v>105095</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5323,42 +5312,41 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>221144</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620714</v>
+        <v>620398</v>
       </c>
       <c r="R41" t="n">
-        <v>6648494</v>
+        <v>6648248</v>
       </c>
       <c r="S41" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5387,7 +5375,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5397,7 +5385,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>25 bladrosetter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5406,28 +5399,29 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123635390</v>
+        <v>123635541</v>
       </c>
       <c r="B42" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5440,37 +5434,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620591</v>
+        <v>620556</v>
       </c>
       <c r="R42" t="n">
-        <v>6648347</v>
+        <v>6648344</v>
       </c>
       <c r="S42" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5499,7 +5498,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5509,7 +5508,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5536,10 +5535,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123635547</v>
+        <v>123634710</v>
       </c>
       <c r="B43" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5571,7 +5570,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5590,13 +5589,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620556</v>
+        <v>620635</v>
       </c>
       <c r="R43" t="n">
-        <v>6648344</v>
+        <v>6648363</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5625,7 +5624,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5635,7 +5634,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5662,10 +5661,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123639666</v>
+        <v>123634559</v>
       </c>
       <c r="B44" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5674,52 +5673,52 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620713</v>
+        <v>620614</v>
       </c>
       <c r="R44" t="n">
-        <v>6648583</v>
+        <v>6648335</v>
       </c>
       <c r="S44" t="n">
         <v>12</v>
@@ -5751,7 +5750,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5761,7 +5760,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5788,10 +5787,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123635541</v>
+        <v>123634578</v>
       </c>
       <c r="B45" t="n">
-        <v>57507</v>
+        <v>74818</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5800,46 +5799,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6426</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620556</v>
+        <v>620451</v>
       </c>
       <c r="R45" t="n">
-        <v>6648344</v>
+        <v>6648229</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5868,7 +5862,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5878,7 +5872,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5893,22 +5887,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123637283</v>
+        <v>123638047</v>
       </c>
       <c r="B46" t="n">
-        <v>95951</v>
+        <v>98079</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5917,25 +5911,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5945,10 +5939,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620603</v>
+        <v>620519</v>
       </c>
       <c r="R46" t="n">
-        <v>6648146</v>
+        <v>6648333</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5980,7 +5974,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5990,7 +5984,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6017,10 +6016,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123634500</v>
+        <v>123635390</v>
       </c>
       <c r="B47" t="n">
-        <v>98504</v>
+        <v>90990</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6029,52 +6028,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620604</v>
+        <v>620591</v>
       </c>
       <c r="R47" t="n">
-        <v>6648323</v>
+        <v>6648347</v>
       </c>
       <c r="S47" t="n">
         <v>4</v>
@@ -6106,7 +6091,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6116,7 +6101,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6143,10 +6128,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123638047</v>
+        <v>123639666</v>
       </c>
       <c r="B48" t="n">
-        <v>98504</v>
+        <v>57644</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6155,41 +6140,55 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620519</v>
+        <v>620713</v>
       </c>
       <c r="R48" t="n">
-        <v>6648333</v>
+        <v>6648583</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6218,7 +6217,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6228,12 +6227,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6248,22 +6242,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123635666</v>
+        <v>123637481</v>
       </c>
       <c r="B49" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6272,55 +6266,46 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620526</v>
+        <v>620714</v>
       </c>
       <c r="R49" t="n">
-        <v>6648364</v>
+        <v>6648494</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6349,7 +6334,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6359,7 +6344,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6386,10 +6371,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123635548</v>
+        <v>123633877</v>
       </c>
       <c r="B50" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6398,49 +6383,55 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620334</v>
+        <v>620537</v>
       </c>
       <c r="R50" t="n">
-        <v>6648148</v>
+        <v>6648292</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6469,7 +6460,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6479,12 +6470,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>1 ex sjöng från tallgren</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6499,22 +6485,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123640236</v>
+        <v>123634500</v>
       </c>
       <c r="B51" t="n">
-        <v>105520</v>
+        <v>98079</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6523,45 +6509,55 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620584</v>
+        <v>620604</v>
       </c>
       <c r="R51" t="n">
-        <v>6648414</v>
+        <v>6648323</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6590,7 +6586,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6600,7 +6596,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6609,29 +6605,28 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123641070</v>
+        <v>123634512</v>
       </c>
       <c r="B52" t="n">
-        <v>74691</v>
+        <v>98079</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6640,41 +6635,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620466</v>
+        <v>620600</v>
       </c>
       <c r="R52" t="n">
-        <v>6648235</v>
+        <v>6648328</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6703,7 +6712,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6713,7 +6722,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6740,10 +6749,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123634710</v>
+        <v>123638984</v>
       </c>
       <c r="B53" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6773,34 +6782,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620635</v>
+        <v>620528</v>
       </c>
       <c r="R53" t="n">
-        <v>6648363</v>
+        <v>6648364</v>
       </c>
       <c r="S53" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6829,7 +6828,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6839,7 +6838,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6848,28 +6852,29 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123634655</v>
+        <v>123635230</v>
       </c>
       <c r="B54" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6901,7 +6906,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -6920,10 +6925,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620626</v>
+        <v>620593</v>
       </c>
       <c r="R54" t="n">
-        <v>6648342</v>
+        <v>6648376</v>
       </c>
       <c r="S54" t="n">
         <v>4</v>
@@ -6955,7 +6960,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6965,7 +6970,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6992,10 +6997,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123635032</v>
+        <v>123635839</v>
       </c>
       <c r="B55" t="n">
-        <v>98504</v>
+        <v>57644</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7004,52 +7009,47 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620640</v>
+        <v>620523</v>
       </c>
       <c r="R55" t="n">
-        <v>6648367</v>
+        <v>6648363</v>
       </c>
       <c r="S55" t="n">
         <v>12</v>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -3007,10 +3007,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123404593</v>
+        <v>123408009</v>
       </c>
       <c r="B22" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3019,43 +3019,46 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620575</v>
+        <v>620718</v>
       </c>
       <c r="R22" t="n">
-        <v>6648228</v>
+        <v>6648486</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3087,7 +3090,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3097,7 +3100,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3124,7 +3127,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123408009</v>
+        <v>123402991</v>
       </c>
       <c r="B23" t="n">
         <v>56700</v>
@@ -3172,13 +3175,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620718</v>
+        <v>620551</v>
       </c>
       <c r="R23" t="n">
-        <v>6648486</v>
+        <v>6648134</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3207,7 +3210,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3217,7 +3220,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3244,10 +3247,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123402991</v>
+        <v>123404593</v>
       </c>
       <c r="B24" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3256,49 +3259,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620551</v>
+        <v>620575</v>
       </c>
       <c r="R24" t="n">
-        <v>6648134</v>
+        <v>6648228</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -6871,10 +6871,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123635230</v>
+        <v>123635839</v>
       </c>
       <c r="B54" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6883,55 +6883,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620593</v>
+        <v>620523</v>
       </c>
       <c r="R54" t="n">
-        <v>6648376</v>
+        <v>6648363</v>
       </c>
       <c r="S54" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6960,7 +6955,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6970,7 +6965,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6997,10 +6992,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123635839</v>
+        <v>123635230</v>
       </c>
       <c r="B55" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7009,50 +7004,55 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620523</v>
+        <v>620593</v>
       </c>
       <c r="R55" t="n">
-        <v>6648363</v>
+        <v>6648376</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123401959</v>
+        <v>123417364</v>
       </c>
       <c r="B2" t="n">
-        <v>78433</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620544</v>
+        <v>620549</v>
       </c>
       <c r="R2" t="n">
-        <v>6648151</v>
+        <v>6648158</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +751,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:03</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123408853</v>
+        <v>123404593</v>
       </c>
       <c r="B3" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,42 +793,43 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620759</v>
+        <v>620575</v>
       </c>
       <c r="R3" t="n">
-        <v>6648492</v>
+        <v>6648228</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -866,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -876,12 +871,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>5 bladrosetter</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -890,7 +880,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -909,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123411227</v>
+        <v>123397574</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,42 +910,46 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620502</v>
+        <v>620364</v>
       </c>
       <c r="R4" t="n">
-        <v>6648313</v>
+        <v>6648233</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,7 +981,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,12 +991,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1012,7 +1005,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1031,10 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123406533</v>
+        <v>123417137</v>
       </c>
       <c r="B5" t="n">
-        <v>96332</v>
+        <v>79406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1047,41 +1039,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620593</v>
+        <v>620541</v>
       </c>
       <c r="R5" t="n">
-        <v>6648325</v>
+        <v>6648142</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1108,24 +1099,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123404576</v>
+        <v>123410527</v>
       </c>
       <c r="B6" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,46 +1141,42 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620575</v>
+        <v>620777</v>
       </c>
       <c r="R6" t="n">
-        <v>6648228</v>
+        <v>6648494</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1236,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,12 +1218,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
+          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1260,6 +1232,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1278,10 +1251,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123402052</v>
+        <v>123404576</v>
       </c>
       <c r="B7" t="n">
-        <v>79406</v>
+        <v>56700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,38 +1263,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620544</v>
+        <v>620575</v>
       </c>
       <c r="R7" t="n">
-        <v>6648151</v>
+        <v>6648228</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1353,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1344,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:14</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1390,10 +1376,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123407548</v>
+        <v>123408009</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,38 +1388,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620609</v>
+        <v>620718</v>
       </c>
       <c r="R8" t="n">
-        <v>6648383</v>
+        <v>6648486</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1465,7 +1459,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,12 +1469,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,10 +1496,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123417137</v>
+        <v>123408488</v>
       </c>
       <c r="B9" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,44 +1508,41 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620541</v>
+        <v>620679</v>
       </c>
       <c r="R9" t="n">
-        <v>6648142</v>
+        <v>6648540</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1583,18 +1569,32 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1613,10 +1613,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123417364</v>
+        <v>123407548</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1625,44 +1625,41 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620549</v>
+        <v>620609</v>
       </c>
       <c r="R10" t="n">
-        <v>6648158</v>
+        <v>6648383</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,18 +1686,32 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1719,10 +1730,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123411112</v>
+        <v>123404274</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>78433</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1731,38 +1742,41 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620609</v>
+        <v>620569</v>
       </c>
       <c r="R11" t="n">
-        <v>6648334</v>
+        <v>6648238</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1794,7 +1808,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:49</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1804,12 +1818,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3 bladrosetter</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1818,6 +1827,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1836,10 +1846,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123397574</v>
+        <v>123410978</v>
       </c>
       <c r="B12" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1848,46 +1858,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620364</v>
+        <v>620617</v>
       </c>
       <c r="R12" t="n">
-        <v>6648233</v>
+        <v>6648344</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1917,24 +1923,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>10:30</t>
-        </is>
-      </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>5 krokar på höjd</t>
+          <t>Ca 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1943,6 +1939,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1961,10 +1958,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123399110</v>
+        <v>123405294</v>
       </c>
       <c r="B13" t="n">
-        <v>95576</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,38 +1970,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620370</v>
+        <v>620610</v>
       </c>
       <c r="R13" t="n">
-        <v>6648255</v>
+        <v>6648299</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2036,7 +2033,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2046,7 +2043,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408488</v>
+        <v>123398864</v>
       </c>
       <c r="B14" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2085,38 +2087,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620679</v>
+        <v>620370</v>
       </c>
       <c r="R14" t="n">
-        <v>6648540</v>
+        <v>6648255</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2148,7 +2158,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2158,12 +2168,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>2 krokar på tallåga</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2190,10 +2200,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123410978</v>
+        <v>123406533</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>96332</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2202,25 +2212,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2230,14 +2240,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620617</v>
+        <v>620593</v>
       </c>
       <c r="R15" t="n">
-        <v>6648344</v>
+        <v>6648325</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2267,14 +2277,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ca 30 bladrosetter</t>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2302,10 +2322,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123406069</v>
+        <v>123405636</v>
       </c>
       <c r="B16" t="n">
-        <v>98079</v>
+        <v>95576</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2314,25 +2334,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2342,10 +2362,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620600</v>
+        <v>620633</v>
       </c>
       <c r="R16" t="n">
-        <v>6648303</v>
+        <v>6648297</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2377,7 +2397,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2387,12 +2407,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2419,10 +2434,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123405294</v>
+        <v>123409471</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>74818</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2431,38 +2446,41 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620610</v>
+        <v>620802</v>
       </c>
       <c r="R17" t="n">
-        <v>6648299</v>
+        <v>6648510</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2494,7 +2512,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2504,12 +2522,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2518,6 +2531,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2536,7 +2550,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123410527</v>
+        <v>123411227</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2580,10 +2594,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620777</v>
+        <v>620502</v>
       </c>
       <c r="R18" t="n">
-        <v>6648494</v>
+        <v>6648313</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2615,7 +2629,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2625,12 +2639,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ca 10 bladroseter</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2658,10 +2672,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123405636</v>
+        <v>123399558</v>
       </c>
       <c r="B19" t="n">
-        <v>95576</v>
+        <v>56700</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2674,34 +2688,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2170</v>
+        <v>100138</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620633</v>
+        <v>620398</v>
       </c>
       <c r="R19" t="n">
-        <v>6648297</v>
+        <v>6648248</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2733,7 +2755,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2743,7 +2765,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2770,7 +2792,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123417333</v>
+        <v>123406069</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -2804,20 +2826,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620596</v>
+        <v>620600</v>
       </c>
       <c r="R20" t="n">
-        <v>6648322</v>
+        <v>6648303</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2847,14 +2865,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2863,7 +2891,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2882,10 +2909,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123398864</v>
+        <v>123407003</v>
       </c>
       <c r="B21" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2894,49 +2921,45 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620370</v>
+        <v>620581</v>
       </c>
       <c r="R21" t="n">
-        <v>6648255</v>
+        <v>6648381</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2963,24 +2986,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>2 krokar på tallåga</t>
+          <t>Mer än 35 bladrosetter</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2989,6 +3002,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3007,10 +3021,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123408009</v>
+        <v>123417333</v>
       </c>
       <c r="B22" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3019,35 +3033,31 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3055,10 +3065,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620718</v>
+        <v>620596</v>
       </c>
       <c r="R22" t="n">
-        <v>6648486</v>
+        <v>6648322</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3088,19 +3098,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:05</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3109,6 +3114,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3127,10 +3133,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123402991</v>
+        <v>123399110</v>
       </c>
       <c r="B23" t="n">
-        <v>56700</v>
+        <v>95576</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3143,45 +3149,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620551</v>
+        <v>620370</v>
       </c>
       <c r="R23" t="n">
-        <v>6648134</v>
+        <v>6648255</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3210,7 +3208,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3220,7 +3218,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3247,10 +3245,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123404593</v>
+        <v>123402052</v>
       </c>
       <c r="B24" t="n">
-        <v>57644</v>
+        <v>79406</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3263,39 +3261,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620575</v>
+        <v>620544</v>
       </c>
       <c r="R24" t="n">
-        <v>6648228</v>
+        <v>6648151</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3327,7 +3320,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3337,7 +3330,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3364,7 +3357,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123404274</v>
+        <v>123401959</v>
       </c>
       <c r="B25" t="n">
         <v>78433</v>
@@ -3398,19 +3391,16 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620569</v>
+        <v>620544</v>
       </c>
       <c r="R25" t="n">
-        <v>6648238</v>
+        <v>6648151</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3442,7 +3432,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3452,7 +3442,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3461,7 +3451,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3480,10 +3469,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123399558</v>
+        <v>123408853</v>
       </c>
       <c r="B26" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3492,46 +3481,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620398</v>
+        <v>620759</v>
       </c>
       <c r="R26" t="n">
-        <v>6648248</v>
+        <v>6648492</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3563,7 +3548,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3573,7 +3558,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3582,6 +3572,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3600,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123409471</v>
+        <v>123411112</v>
       </c>
       <c r="B27" t="n">
-        <v>74818</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3612,41 +3603,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620802</v>
+        <v>620609</v>
       </c>
       <c r="R27" t="n">
-        <v>6648510</v>
+        <v>6648334</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3678,7 +3666,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3688,7 +3676,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3697,7 +3690,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3716,10 +3708,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123407003</v>
+        <v>123402991</v>
       </c>
       <c r="B28" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3728,31 +3720,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3760,13 +3756,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620581</v>
+        <v>620551</v>
       </c>
       <c r="R28" t="n">
-        <v>6648381</v>
+        <v>6648134</v>
       </c>
       <c r="S28" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3793,14 +3789,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Mer än 35 bladrosetter</t>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3809,7 +3810,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3957,10 +3957,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123635548</v>
+        <v>123635541</v>
       </c>
       <c r="B30" t="n">
-        <v>57644</v>
+        <v>57507</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3973,45 +3973,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620334</v>
+        <v>620556</v>
       </c>
       <c r="R30" t="n">
-        <v>6648148</v>
+        <v>6648344</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4040,7 +4037,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4050,12 +4047,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>1 ex sjöng från tallgren</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4070,22 +4062,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123637283</v>
+        <v>123639666</v>
       </c>
       <c r="B31" t="n">
-        <v>96332</v>
+        <v>57644</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4098,37 +4090,51 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>53</v>
+        <v>103021</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620603</v>
+        <v>620713</v>
       </c>
       <c r="R31" t="n">
-        <v>6648146</v>
+        <v>6648583</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4157,7 +4163,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4167,7 +4173,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4182,22 +4188,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123641070</v>
+        <v>123634578</v>
       </c>
       <c r="B32" t="n">
-        <v>74691</v>
+        <v>74818</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4210,37 +4216,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6428</v>
+        <v>6426</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620466</v>
+        <v>620451</v>
       </c>
       <c r="R32" t="n">
-        <v>6648235</v>
+        <v>6648229</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4269,7 +4275,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4279,7 +4285,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4294,22 +4300,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123635666</v>
+        <v>123633877</v>
       </c>
       <c r="B33" t="n">
-        <v>57644</v>
+        <v>57861</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4318,25 +4324,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4360,13 +4366,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620526</v>
+        <v>620537</v>
       </c>
       <c r="R33" t="n">
-        <v>6648364</v>
+        <v>6648292</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4395,7 +4401,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4405,7 +4411,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4432,7 +4438,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123634264</v>
+        <v>123634559</v>
       </c>
       <c r="B34" t="n">
         <v>98079</v>
@@ -4467,7 +4473,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4486,13 +4492,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620584</v>
+        <v>620614</v>
       </c>
       <c r="R34" t="n">
-        <v>6648323</v>
+        <v>6648335</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4521,7 +4527,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4531,7 +4537,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4558,10 +4564,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123636168</v>
+        <v>123632944</v>
       </c>
       <c r="B35" t="n">
-        <v>96332</v>
+        <v>105095</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4570,25 +4576,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4602,13 +4608,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620443</v>
+        <v>620398</v>
       </c>
       <c r="R35" t="n">
-        <v>6648200</v>
+        <v>6648248</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4637,7 +4643,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4647,7 +4653,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>25 bladrosetter</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4801,10 +4812,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123635547</v>
+        <v>123641070</v>
       </c>
       <c r="B37" t="n">
-        <v>98079</v>
+        <v>74691</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4813,55 +4824,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620556</v>
+        <v>620466</v>
       </c>
       <c r="R37" t="n">
-        <v>6648344</v>
+        <v>6648235</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4890,7 +4887,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4900,7 +4897,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4927,10 +4924,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123634655</v>
+        <v>123635666</v>
       </c>
       <c r="B38" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4939,40 +4936,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4981,13 +4978,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620626</v>
+        <v>620526</v>
       </c>
       <c r="R38" t="n">
-        <v>6648342</v>
+        <v>6648364</v>
       </c>
       <c r="S38" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5016,7 +5013,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5026,7 +5023,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5053,10 +5050,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123640236</v>
+        <v>123634655</v>
       </c>
       <c r="B39" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5065,45 +5062,55 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620584</v>
+        <v>620626</v>
       </c>
       <c r="R39" t="n">
-        <v>6648414</v>
+        <v>6648342</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5132,7 +5139,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5142,7 +5149,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5151,26 +5158,25 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123635032</v>
+        <v>123635230</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5205,7 +5211,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5224,13 +5230,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620640</v>
+        <v>620593</v>
       </c>
       <c r="R40" t="n">
-        <v>6648367</v>
+        <v>6648376</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5259,7 +5265,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5269,7 +5275,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5296,10 +5302,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123632944</v>
+        <v>123634512</v>
       </c>
       <c r="B41" t="n">
-        <v>105095</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5308,45 +5314,55 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620398</v>
+        <v>620600</v>
       </c>
       <c r="R41" t="n">
-        <v>6648248</v>
+        <v>6648328</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5375,7 +5391,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5385,12 +5401,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>25 bladrosetter</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5399,29 +5410,28 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123635541</v>
+        <v>123637283</v>
       </c>
       <c r="B42" t="n">
-        <v>57507</v>
+        <v>96332</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5434,42 +5444,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>53</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620556</v>
+        <v>620603</v>
       </c>
       <c r="R42" t="n">
-        <v>6648344</v>
+        <v>6648146</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5498,7 +5503,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5508,7 +5513,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5523,19 +5528,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123634710</v>
+        <v>123635547</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -5570,7 +5575,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5589,13 +5594,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620635</v>
+        <v>620556</v>
       </c>
       <c r="R43" t="n">
-        <v>6648363</v>
+        <v>6648344</v>
       </c>
       <c r="S43" t="n">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5624,7 +5629,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5634,7 +5639,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5661,7 +5666,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123634559</v>
+        <v>123635032</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -5696,7 +5701,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5715,10 +5720,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620614</v>
+        <v>620640</v>
       </c>
       <c r="R44" t="n">
-        <v>6648335</v>
+        <v>6648367</v>
       </c>
       <c r="S44" t="n">
         <v>12</v>
@@ -5750,7 +5755,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5760,7 +5765,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5787,10 +5792,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123634578</v>
+        <v>123637481</v>
       </c>
       <c r="B45" t="n">
-        <v>74818</v>
+        <v>56700</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5803,37 +5808,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6426</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620451</v>
+        <v>620714</v>
       </c>
       <c r="R45" t="n">
-        <v>6648229</v>
+        <v>6648494</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5862,7 +5872,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5872,7 +5882,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5887,19 +5897,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123638047</v>
+        <v>123638984</v>
       </c>
       <c r="B46" t="n">
         <v>98079</v>
@@ -5933,16 +5943,20 @@
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620519</v>
+        <v>620528</v>
       </c>
       <c r="R46" t="n">
-        <v>6648333</v>
+        <v>6648364</v>
       </c>
       <c r="S46" t="n">
         <v>20</v>
@@ -5974,7 +5988,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5984,12 +5998,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5998,6 +6012,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6016,10 +6031,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123635390</v>
+        <v>123640236</v>
       </c>
       <c r="B47" t="n">
-        <v>90990</v>
+        <v>105095</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6028,41 +6043,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1202</v>
+        <v>221144</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620591</v>
+        <v>620584</v>
       </c>
       <c r="R47" t="n">
-        <v>6648347</v>
+        <v>6648414</v>
       </c>
       <c r="S47" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6091,7 +6110,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6101,7 +6120,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6110,25 +6129,26 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123639666</v>
+        <v>123635548</v>
       </c>
       <c r="B48" t="n">
         <v>57644</v>
@@ -6161,34 +6181,28 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620713</v>
+        <v>620334</v>
       </c>
       <c r="R48" t="n">
-        <v>6648583</v>
+        <v>6648148</v>
       </c>
       <c r="S48" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6217,7 +6231,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6227,7 +6241,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>1 ex sjöng från tallgren</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6242,22 +6261,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123637481</v>
+        <v>123634710</v>
       </c>
       <c r="B49" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6266,46 +6285,55 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620714</v>
+        <v>620635</v>
       </c>
       <c r="R49" t="n">
-        <v>6648494</v>
+        <v>6648363</v>
       </c>
       <c r="S49" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6334,7 +6362,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6344,7 +6372,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6371,10 +6399,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123633877</v>
+        <v>123635390</v>
       </c>
       <c r="B50" t="n">
-        <v>57861</v>
+        <v>90990</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6383,55 +6411,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103015</v>
+        <v>1202</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620537</v>
+        <v>620591</v>
       </c>
       <c r="R50" t="n">
-        <v>6648292</v>
+        <v>6648347</v>
       </c>
       <c r="S50" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6460,7 +6474,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6470,7 +6484,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6497,10 +6511,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123634500</v>
+        <v>123635839</v>
       </c>
       <c r="B51" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6509,55 +6523,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620604</v>
+        <v>620523</v>
       </c>
       <c r="R51" t="n">
-        <v>6648323</v>
+        <v>6648363</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6586,7 +6595,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6596,7 +6605,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6623,7 +6632,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123634512</v>
+        <v>123638047</v>
       </c>
       <c r="B52" t="n">
         <v>98079</v>
@@ -6656,34 +6665,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620600</v>
+        <v>620519</v>
       </c>
       <c r="R52" t="n">
-        <v>6648328</v>
+        <v>6648333</v>
       </c>
       <c r="S52" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6712,7 +6707,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6722,7 +6717,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6737,19 +6737,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123638984</v>
+        <v>123634500</v>
       </c>
       <c r="B53" t="n">
         <v>98079</v>
@@ -6782,24 +6782,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620528</v>
+        <v>620604</v>
       </c>
       <c r="R53" t="n">
-        <v>6648364</v>
+        <v>6648323</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6828,7 +6838,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6838,12 +6848,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6852,29 +6857,28 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123635839</v>
+        <v>123634264</v>
       </c>
       <c r="B54" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6883,50 +6887,55 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620523</v>
+        <v>620584</v>
       </c>
       <c r="R54" t="n">
-        <v>6648363</v>
+        <v>6648323</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6955,7 +6964,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6965,7 +6974,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6992,10 +7001,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123635230</v>
+        <v>123636168</v>
       </c>
       <c r="B55" t="n">
-        <v>98079</v>
+        <v>96332</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7004,55 +7013,45 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620593</v>
+        <v>620443</v>
       </c>
       <c r="R55" t="n">
-        <v>6648376</v>
+        <v>6648200</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7081,7 +7080,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7091,7 +7090,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7100,18 +7099,19 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123417364</v>
+        <v>123406533</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>96332</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,40 +691,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620549</v>
+        <v>620593</v>
       </c>
       <c r="R2" t="n">
-        <v>6648158</v>
+        <v>6648325</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -751,9 +752,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +797,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123404593</v>
+        <v>123397574</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,43 +809,46 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620575</v>
+        <v>620364</v>
       </c>
       <c r="R3" t="n">
-        <v>6648228</v>
+        <v>6648233</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -861,7 +880,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -871,7 +890,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,10 +922,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123397574</v>
+        <v>123405636</v>
       </c>
       <c r="B4" t="n">
-        <v>56700</v>
+        <v>95576</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -914,42 +938,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620364</v>
+        <v>620633</v>
       </c>
       <c r="R4" t="n">
-        <v>6648233</v>
+        <v>6648297</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,7 +997,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -991,12 +1007,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>5 krokar på höjd</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,10 +1034,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123417137</v>
+        <v>123408488</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1035,44 +1046,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620541</v>
+        <v>620679</v>
       </c>
       <c r="R5" t="n">
-        <v>6648142</v>
+        <v>6648540</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,18 +1107,32 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,7 +1151,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123410527</v>
+        <v>123417333</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1169,14 +1191,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620777</v>
+        <v>620596</v>
       </c>
       <c r="R6" t="n">
-        <v>6648494</v>
+        <v>6648322</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1206,24 +1228,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ca 10 bladroseter</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1251,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123404576</v>
+        <v>123401959</v>
       </c>
       <c r="B7" t="n">
-        <v>56700</v>
+        <v>78433</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1263,46 +1275,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620575</v>
+        <v>620544</v>
       </c>
       <c r="R7" t="n">
-        <v>6648228</v>
+        <v>6648151</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1334,7 +1338,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,12 +1348,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1375,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123408009</v>
+        <v>123399110</v>
       </c>
       <c r="B8" t="n">
-        <v>56700</v>
+        <v>95576</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,42 +1391,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620718</v>
+        <v>620370</v>
       </c>
       <c r="R8" t="n">
-        <v>6648486</v>
+        <v>6648255</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1459,7 +1450,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1469,7 +1460,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1496,10 +1487,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408488</v>
+        <v>123399558</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1508,38 +1499,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620679</v>
+        <v>620398</v>
       </c>
       <c r="R9" t="n">
-        <v>6648540</v>
+        <v>6648248</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1571,7 +1570,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,12 +1580,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1613,7 +1607,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123407548</v>
+        <v>123411227</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1647,16 +1641,20 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620609</v>
+        <v>620502</v>
       </c>
       <c r="R10" t="n">
-        <v>6648383</v>
+        <v>6648313</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1688,7 +1686,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1698,12 +1696,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,6 +1710,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1730,10 +1729,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123404274</v>
+        <v>123398864</v>
       </c>
       <c r="B11" t="n">
-        <v>78433</v>
+        <v>56700</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1742,41 +1741,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620569</v>
+        <v>620370</v>
       </c>
       <c r="R11" t="n">
-        <v>6648238</v>
+        <v>6648255</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1808,7 +1812,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1818,7 +1822,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2 krokar på tallåga</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,7 +1836,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1958,10 +1966,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123405294</v>
+        <v>123417364</v>
       </c>
       <c r="B13" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1970,41 +1978,44 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620610</v>
+        <v>620549</v>
       </c>
       <c r="R13" t="n">
-        <v>6648299</v>
+        <v>6648158</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2031,32 +2042,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2075,10 +2072,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123398864</v>
+        <v>123407003</v>
       </c>
       <c r="B14" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,49 +2084,45 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620370</v>
+        <v>620581</v>
       </c>
       <c r="R14" t="n">
-        <v>6648255</v>
+        <v>6648381</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2156,24 +2149,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>2 krokar på tallåga</t>
+          <t>Mer än 35 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2182,6 +2165,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2200,10 +2184,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123406533</v>
+        <v>123405294</v>
       </c>
       <c r="B15" t="n">
-        <v>96332</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,42 +2196,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620593</v>
+        <v>620610</v>
       </c>
       <c r="R15" t="n">
-        <v>6648325</v>
+        <v>6648299</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2279,7 +2259,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2289,12 +2269,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På understa lågan</t>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2303,7 +2283,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2322,10 +2301,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123405636</v>
+        <v>123410527</v>
       </c>
       <c r="B16" t="n">
-        <v>95576</v>
+        <v>98079</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2334,38 +2313,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620633</v>
+        <v>620777</v>
       </c>
       <c r="R16" t="n">
-        <v>6648297</v>
+        <v>6648494</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2397,7 +2380,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2407,7 +2390,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2416,6 +2404,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2434,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123409471</v>
+        <v>123406069</v>
       </c>
       <c r="B17" t="n">
-        <v>74818</v>
+        <v>98079</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2446,41 +2435,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620802</v>
+        <v>620600</v>
       </c>
       <c r="R17" t="n">
-        <v>6648510</v>
+        <v>6648303</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2512,7 +2498,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2522,7 +2508,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,7 +2522,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2550,10 +2540,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123411227</v>
+        <v>123408009</v>
       </c>
       <c r="B18" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2562,42 +2552,46 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620502</v>
+        <v>620718</v>
       </c>
       <c r="R18" t="n">
-        <v>6648313</v>
+        <v>6648486</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2629,7 +2623,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2639,12 +2633,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2653,7 +2642,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2672,10 +2660,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123399558</v>
+        <v>123408853</v>
       </c>
       <c r="B19" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,46 +2672,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620398</v>
+        <v>620759</v>
       </c>
       <c r="R19" t="n">
-        <v>6648248</v>
+        <v>6648492</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2755,7 +2739,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2765,7 +2749,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2774,6 +2763,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2792,10 +2782,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123406069</v>
+        <v>123402991</v>
       </c>
       <c r="B20" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2804,41 +2794,49 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620600</v>
+        <v>620551</v>
       </c>
       <c r="R20" t="n">
-        <v>6648303</v>
+        <v>6648134</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2867,7 +2865,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2877,12 +2875,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2909,10 +2902,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123407003</v>
+        <v>123404593</v>
       </c>
       <c r="B21" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2921,45 +2914,46 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620581</v>
+        <v>620575</v>
       </c>
       <c r="R21" t="n">
-        <v>6648381</v>
+        <v>6648228</v>
       </c>
       <c r="S21" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2986,14 +2980,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Mer än 35 bladrosetter</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3002,7 +3001,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3021,10 +3019,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123417333</v>
+        <v>123404274</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>78433</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3033,42 +3031,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620596</v>
+        <v>620569</v>
       </c>
       <c r="R22" t="n">
-        <v>6648322</v>
+        <v>6648238</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3098,14 +3095,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>13 bladrosetter</t>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3133,10 +3135,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123399110</v>
+        <v>123409471</v>
       </c>
       <c r="B23" t="n">
-        <v>95576</v>
+        <v>74818</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3149,34 +3151,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620370</v>
+        <v>620802</v>
       </c>
       <c r="R23" t="n">
-        <v>6648255</v>
+        <v>6648510</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3208,7 +3213,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3218,7 +3223,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3227,6 +3232,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3357,10 +3363,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123401959</v>
+        <v>123411112</v>
       </c>
       <c r="B25" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3369,25 +3375,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3397,10 +3403,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620544</v>
+        <v>620609</v>
       </c>
       <c r="R25" t="n">
-        <v>6648151</v>
+        <v>6648334</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3432,7 +3438,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3442,7 +3448,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3469,10 +3480,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123408853</v>
+        <v>123404576</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3481,42 +3492,46 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620759</v>
+        <v>620575</v>
       </c>
       <c r="R26" t="n">
-        <v>6648492</v>
+        <v>6648228</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3548,7 +3563,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3558,12 +3573,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>5 bladrosetter</t>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3572,7 +3587,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3591,10 +3605,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123411112</v>
+        <v>123417137</v>
       </c>
       <c r="B27" t="n">
-        <v>98079</v>
+        <v>79406</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3603,41 +3617,44 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620609</v>
+        <v>620541</v>
       </c>
       <c r="R27" t="n">
-        <v>6648334</v>
+        <v>6648142</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3664,32 +3681,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>16:49</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>3 bladrosetter</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3708,10 +3711,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123402991</v>
+        <v>123407548</v>
       </c>
       <c r="B28" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3720,49 +3723,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620551</v>
+        <v>620609</v>
       </c>
       <c r="R28" t="n">
-        <v>6648134</v>
+        <v>6648383</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3791,7 +3786,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3801,7 +3796,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4074,10 +4074,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123639666</v>
+        <v>123634710</v>
       </c>
       <c r="B31" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4086,55 +4086,55 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620713</v>
+        <v>620635</v>
       </c>
       <c r="R31" t="n">
-        <v>6648583</v>
+        <v>6648363</v>
       </c>
       <c r="S31" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4200,10 +4200,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123634578</v>
+        <v>123633877</v>
       </c>
       <c r="B32" t="n">
-        <v>74818</v>
+        <v>57861</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4216,37 +4216,51 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6426</v>
+        <v>103015</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620451</v>
+        <v>620537</v>
       </c>
       <c r="R32" t="n">
-        <v>6648229</v>
+        <v>6648292</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4275,7 +4289,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4285,7 +4299,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4300,22 +4314,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123633877</v>
+        <v>123635547</v>
       </c>
       <c r="B33" t="n">
-        <v>57861</v>
+        <v>98079</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4324,40 +4338,40 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103015</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4366,13 +4380,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620537</v>
+        <v>620556</v>
       </c>
       <c r="R33" t="n">
-        <v>6648292</v>
+        <v>6648344</v>
       </c>
       <c r="S33" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4401,7 +4415,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4411,7 +4425,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4686,7 +4700,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123635824</v>
+        <v>123638047</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -4719,34 +4733,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620523</v>
+        <v>620519</v>
       </c>
       <c r="R36" t="n">
-        <v>6648363</v>
+        <v>6648333</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4785,7 +4785,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4800,22 +4805,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123641070</v>
+        <v>123637481</v>
       </c>
       <c r="B37" t="n">
-        <v>74691</v>
+        <v>56700</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4828,37 +4833,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6428</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620466</v>
+        <v>620714</v>
       </c>
       <c r="R37" t="n">
-        <v>6648235</v>
+        <v>6648494</v>
       </c>
       <c r="S37" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4887,7 +4897,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4897,7 +4907,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4924,10 +4934,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123635666</v>
+        <v>123635824</v>
       </c>
       <c r="B38" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4936,40 +4946,40 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4978,10 +4988,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620526</v>
+        <v>620523</v>
       </c>
       <c r="R38" t="n">
-        <v>6648364</v>
+        <v>6648363</v>
       </c>
       <c r="S38" t="n">
         <v>12</v>
@@ -5013,7 +5023,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5023,7 +5033,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5050,10 +5060,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123634655</v>
+        <v>123635839</v>
       </c>
       <c r="B39" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5062,55 +5072,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620626</v>
+        <v>620523</v>
       </c>
       <c r="R39" t="n">
-        <v>6648342</v>
+        <v>6648363</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5139,7 +5144,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5149,7 +5154,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5176,7 +5181,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123635230</v>
+        <v>123634512</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5211,7 +5216,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5230,13 +5235,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620593</v>
+        <v>620600</v>
       </c>
       <c r="R40" t="n">
-        <v>6648376</v>
+        <v>6648328</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5265,7 +5270,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5275,7 +5280,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5302,10 +5307,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123634512</v>
+        <v>123639666</v>
       </c>
       <c r="B41" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5314,52 +5319,52 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620600</v>
+        <v>620713</v>
       </c>
       <c r="R41" t="n">
-        <v>6648328</v>
+        <v>6648583</v>
       </c>
       <c r="S41" t="n">
         <v>12</v>
@@ -5391,7 +5396,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5401,7 +5406,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5428,10 +5433,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123637283</v>
+        <v>123640236</v>
       </c>
       <c r="B42" t="n">
-        <v>96332</v>
+        <v>105095</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5440,38 +5445,42 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>53</v>
+        <v>221144</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620603</v>
+        <v>620584</v>
       </c>
       <c r="R42" t="n">
-        <v>6648146</v>
+        <v>6648414</v>
       </c>
       <c r="S42" t="n">
         <v>20</v>
@@ -5503,7 +5512,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5513,7 +5522,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5522,6 +5531,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
@@ -5540,7 +5550,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123635547</v>
+        <v>123634500</v>
       </c>
       <c r="B43" t="n">
         <v>98079</v>
@@ -5575,7 +5585,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>79</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -5594,13 +5604,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620556</v>
+        <v>620604</v>
       </c>
       <c r="R43" t="n">
-        <v>6648344</v>
+        <v>6648323</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5629,7 +5639,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5639,7 +5649,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5666,10 +5676,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123635032</v>
+        <v>123641070</v>
       </c>
       <c r="B44" t="n">
-        <v>98079</v>
+        <v>74691</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5678,55 +5688,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620640</v>
+        <v>620466</v>
       </c>
       <c r="R44" t="n">
-        <v>6648367</v>
+        <v>6648235</v>
       </c>
       <c r="S44" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5755,7 +5751,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5765,7 +5761,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5792,10 +5788,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123637481</v>
+        <v>123634264</v>
       </c>
       <c r="B45" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5804,43 +5800,52 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620714</v>
+        <v>620584</v>
       </c>
       <c r="R45" t="n">
-        <v>6648494</v>
+        <v>6648323</v>
       </c>
       <c r="S45" t="n">
         <v>2</v>
@@ -5872,7 +5877,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5882,7 +5887,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5909,7 +5914,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123638984</v>
+        <v>123634655</v>
       </c>
       <c r="B46" t="n">
         <v>98079</v>
@@ -5942,24 +5947,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620528</v>
+        <v>620626</v>
       </c>
       <c r="R46" t="n">
-        <v>6648364</v>
+        <v>6648342</v>
       </c>
       <c r="S46" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5988,7 +6003,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5998,12 +6013,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6012,29 +6022,28 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123640236</v>
+        <v>123637283</v>
       </c>
       <c r="B47" t="n">
-        <v>105095</v>
+        <v>96332</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6043,42 +6052,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620584</v>
+        <v>620603</v>
       </c>
       <c r="R47" t="n">
-        <v>6648414</v>
+        <v>6648146</v>
       </c>
       <c r="S47" t="n">
         <v>20</v>
@@ -6110,7 +6115,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6120,7 +6125,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6129,7 +6134,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -6148,10 +6152,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123635548</v>
+        <v>123638984</v>
       </c>
       <c r="B48" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6160,35 +6164,31 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6196,13 +6196,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620334</v>
+        <v>620528</v>
       </c>
       <c r="R48" t="n">
-        <v>6648148</v>
+        <v>6648364</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>1 ex sjöng från tallgren</t>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6255,6 +6255,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6273,10 +6274,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123634710</v>
+        <v>123635548</v>
       </c>
       <c r="B49" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6285,55 +6286,49 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620635</v>
+        <v>620334</v>
       </c>
       <c r="R49" t="n">
-        <v>6648363</v>
+        <v>6648148</v>
       </c>
       <c r="S49" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6362,7 +6357,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6372,7 +6367,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>1 ex sjöng från tallgren</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6387,22 +6387,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123635390</v>
+        <v>123635032</v>
       </c>
       <c r="B50" t="n">
-        <v>90990</v>
+        <v>98079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6411,41 +6411,55 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620591</v>
+        <v>620640</v>
       </c>
       <c r="R50" t="n">
-        <v>6648347</v>
+        <v>6648367</v>
       </c>
       <c r="S50" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6474,7 +6488,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6484,7 +6498,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6511,10 +6525,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123635839</v>
+        <v>123635390</v>
       </c>
       <c r="B51" t="n">
-        <v>57644</v>
+        <v>90990</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6527,46 +6541,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620523</v>
+        <v>620591</v>
       </c>
       <c r="R51" t="n">
-        <v>6648363</v>
+        <v>6648347</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6595,7 +6600,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6605,7 +6610,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6632,10 +6637,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123638047</v>
+        <v>123636168</v>
       </c>
       <c r="B52" t="n">
-        <v>98079</v>
+        <v>96332</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6644,38 +6649,42 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620519</v>
+        <v>620443</v>
       </c>
       <c r="R52" t="n">
-        <v>6648333</v>
+        <v>6648200</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6707,7 +6716,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6717,12 +6726,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6731,6 +6735,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -6749,10 +6754,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123634500</v>
+        <v>123634578</v>
       </c>
       <c r="B53" t="n">
-        <v>98079</v>
+        <v>74818</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6761,55 +6766,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>6426</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620604</v>
+        <v>620451</v>
       </c>
       <c r="R53" t="n">
-        <v>6648323</v>
+        <v>6648229</v>
       </c>
       <c r="S53" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6838,7 +6829,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6848,7 +6839,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6863,22 +6854,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123634264</v>
+        <v>123635666</v>
       </c>
       <c r="B54" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6887,40 +6878,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6929,13 +6920,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620584</v>
+        <v>620526</v>
       </c>
       <c r="R54" t="n">
-        <v>6648323</v>
+        <v>6648364</v>
       </c>
       <c r="S54" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6964,7 +6955,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6974,7 +6965,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7001,10 +6992,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123636168</v>
+        <v>123635230</v>
       </c>
       <c r="B55" t="n">
-        <v>96332</v>
+        <v>98079</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -7013,45 +7004,55 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620443</v>
+        <v>620593</v>
       </c>
       <c r="R55" t="n">
-        <v>6648200</v>
+        <v>6648376</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7080,7 +7081,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7090,7 +7091,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7099,19 +7100,18 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123406533</v>
+        <v>123405636</v>
       </c>
       <c r="B2" t="n">
-        <v>96332</v>
+        <v>95576</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,42 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620593</v>
+        <v>620633</v>
       </c>
       <c r="R2" t="n">
-        <v>6648325</v>
+        <v>6648297</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -764,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På understa lågan</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,7 +769,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -797,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123397574</v>
+        <v>123402052</v>
       </c>
       <c r="B3" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -809,46 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620364</v>
+        <v>620544</v>
       </c>
       <c r="R3" t="n">
-        <v>6648233</v>
+        <v>6648151</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -880,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>5 krokar på höjd</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123405636</v>
+        <v>123401959</v>
       </c>
       <c r="B4" t="n">
-        <v>95576</v>
+        <v>78433</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -934,38 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2170</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620633</v>
+        <v>620544</v>
       </c>
       <c r="R4" t="n">
-        <v>6648297</v>
+        <v>6648151</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -997,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1007,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1034,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123408488</v>
+        <v>123404576</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1046,38 +1023,46 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620679</v>
+        <v>620575</v>
       </c>
       <c r="R5" t="n">
-        <v>6648540</v>
+        <v>6648228</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1109,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1119,12 +1104,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,7 +1136,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123417333</v>
+        <v>123411227</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1191,14 +1176,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620596</v>
+        <v>620502</v>
       </c>
       <c r="R6" t="n">
-        <v>6648322</v>
+        <v>6648313</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1228,14 +1213,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,7 +1258,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123401959</v>
+        <v>123404274</v>
       </c>
       <c r="B7" t="n">
         <v>78433</v>
@@ -1297,16 +1292,19 @@
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620544</v>
+        <v>620569</v>
       </c>
       <c r="R7" t="n">
-        <v>6648151</v>
+        <v>6648238</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1338,7 +1336,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1348,7 +1346,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,6 +1355,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1375,10 +1374,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123399110</v>
+        <v>123407003</v>
       </c>
       <c r="B8" t="n">
-        <v>95576</v>
+        <v>98079</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,41 +1386,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620370</v>
+        <v>620581</v>
       </c>
       <c r="R8" t="n">
-        <v>6648255</v>
+        <v>6648381</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1448,19 +1451,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:17</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:17</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Mer än 35 bladrosetter</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,6 +1467,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1487,10 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123399558</v>
+        <v>123399110</v>
       </c>
       <c r="B9" t="n">
-        <v>56700</v>
+        <v>95576</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1503,42 +1502,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620398</v>
+        <v>620370</v>
       </c>
       <c r="R9" t="n">
-        <v>6648248</v>
+        <v>6648255</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1570,7 +1561,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1580,7 +1571,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1607,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123411227</v>
+        <v>123417364</v>
       </c>
       <c r="B10" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1619,31 +1610,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1651,13 +1641,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620502</v>
+        <v>620549</v>
       </c>
       <c r="R10" t="n">
-        <v>6648313</v>
+        <v>6648158</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1684,24 +1674,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,10 +1704,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123398864</v>
+        <v>123410527</v>
       </c>
       <c r="B11" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1741,35 +1716,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1777,10 +1748,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620370</v>
+        <v>620777</v>
       </c>
       <c r="R11" t="n">
-        <v>6648255</v>
+        <v>6648494</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1812,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1822,12 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2 krokar på tallåga</t>
+          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1836,6 +1807,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1854,10 +1826,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123410978</v>
+        <v>123402991</v>
       </c>
       <c r="B12" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,45 +1838,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620617</v>
+        <v>620551</v>
       </c>
       <c r="R12" t="n">
-        <v>6648344</v>
+        <v>6648134</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1931,14 +1907,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 30 bladrosetter</t>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1947,7 +1928,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1966,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123417364</v>
+        <v>123406069</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1978,44 +1958,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620549</v>
+        <v>620600</v>
       </c>
       <c r="R13" t="n">
-        <v>6648158</v>
+        <v>6648303</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2042,18 +2019,32 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>12 bladrosetter</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2072,7 +2063,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123407003</v>
+        <v>123408488</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2106,23 +2097,19 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620581</v>
+        <v>620679</v>
       </c>
       <c r="R14" t="n">
-        <v>6648381</v>
+        <v>6648540</v>
       </c>
       <c r="S14" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2149,14 +2136,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Mer än 35 bladrosetter</t>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,7 +2162,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2184,10 +2180,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123405294</v>
+        <v>123397574</v>
       </c>
       <c r="B15" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2196,38 +2192,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620610</v>
+        <v>620364</v>
       </c>
       <c r="R15" t="n">
-        <v>6648299</v>
+        <v>6648233</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2259,7 +2263,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2269,12 +2273,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,7 +2305,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123410527</v>
+        <v>123405294</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2335,20 +2339,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620777</v>
+        <v>620610</v>
       </c>
       <c r="R16" t="n">
-        <v>6648494</v>
+        <v>6648299</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2380,7 +2380,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ca 10 bladroseter</t>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,7 +2404,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2423,7 +2422,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123406069</v>
+        <v>123417333</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2457,16 +2456,20 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620600</v>
+        <v>620596</v>
       </c>
       <c r="R17" t="n">
-        <v>6648303</v>
+        <v>6648322</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2496,24 +2499,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:54</t>
-        </is>
-      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>12 bladrosetter</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2522,6 +2515,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2540,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123408009</v>
+        <v>123417137</v>
       </c>
       <c r="B18" t="n">
-        <v>56700</v>
+        <v>79406</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2552,49 +2546,44 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620718</v>
+        <v>620541</v>
       </c>
       <c r="R18" t="n">
-        <v>6648486</v>
+        <v>6648142</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2621,27 +2610,18 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:05</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2660,10 +2640,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123408853</v>
+        <v>123404593</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2672,42 +2652,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620759</v>
+        <v>620575</v>
       </c>
       <c r="R19" t="n">
-        <v>6648492</v>
+        <v>6648228</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2739,7 +2720,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2749,12 +2730,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>5 bladrosetter</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2763,7 +2739,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2782,10 +2757,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123402991</v>
+        <v>123407548</v>
       </c>
       <c r="B20" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2794,49 +2769,41 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620551</v>
+        <v>620609</v>
       </c>
       <c r="R20" t="n">
-        <v>6648134</v>
+        <v>6648383</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2865,7 +2832,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2875,7 +2842,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2902,10 +2874,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123404593</v>
+        <v>123406533</v>
       </c>
       <c r="B21" t="n">
-        <v>57644</v>
+        <v>96332</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2918,39 +2890,38 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620575</v>
+        <v>620593</v>
       </c>
       <c r="R21" t="n">
-        <v>6648228</v>
+        <v>6648325</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2982,7 +2953,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2992,7 +2963,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3001,6 +2977,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3019,10 +2996,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123404274</v>
+        <v>123409471</v>
       </c>
       <c r="B22" t="n">
-        <v>78433</v>
+        <v>74818</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3031,25 +3008,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>6426</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3058,14 +3035,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620569</v>
+        <v>620802</v>
       </c>
       <c r="R22" t="n">
-        <v>6648238</v>
+        <v>6648510</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3097,7 +3074,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3107,7 +3084,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>15:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3135,10 +3112,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123409471</v>
+        <v>123408853</v>
       </c>
       <c r="B23" t="n">
-        <v>74818</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3147,30 +3124,31 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3178,10 +3156,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620802</v>
+        <v>620759</v>
       </c>
       <c r="R23" t="n">
-        <v>6648510</v>
+        <v>6648492</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3213,7 +3191,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3223,7 +3201,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:52</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3251,10 +3234,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123402052</v>
+        <v>123408009</v>
       </c>
       <c r="B24" t="n">
-        <v>79406</v>
+        <v>56700</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3263,38 +3246,46 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620544</v>
+        <v>620718</v>
       </c>
       <c r="R24" t="n">
-        <v>6648151</v>
+        <v>6648486</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3326,7 +3317,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3336,7 +3327,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3363,7 +3354,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123411112</v>
+        <v>123410978</v>
       </c>
       <c r="B25" t="n">
         <v>98079</v>
@@ -3397,16 +3388,20 @@
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620609</v>
+        <v>620617</v>
       </c>
       <c r="R25" t="n">
-        <v>6648334</v>
+        <v>6648344</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3436,24 +3431,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>16:49</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>16:49</t>
-        </is>
-      </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>3 bladrosetter</t>
+          <t>Ca 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3462,6 +3447,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3480,7 +3466,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123404576</v>
+        <v>123398864</v>
       </c>
       <c r="B26" t="n">
         <v>56700</v>
@@ -3524,14 +3510,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620575</v>
+        <v>620370</v>
       </c>
       <c r="R26" t="n">
-        <v>6648228</v>
+        <v>6648255</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3563,7 +3549,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3573,12 +3559,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
+          <t>2 krokar på tallåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3605,10 +3591,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123417137</v>
+        <v>123399558</v>
       </c>
       <c r="B27" t="n">
-        <v>79406</v>
+        <v>56700</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3617,30 +3603,35 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3648,13 +3639,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620541</v>
+        <v>620398</v>
       </c>
       <c r="R27" t="n">
-        <v>6648142</v>
+        <v>6648248</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3681,18 +3672,27 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3711,7 +3711,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123407548</v>
+        <v>123411112</v>
       </c>
       <c r="B28" t="n">
         <v>98079</v>
@@ -3747,14 +3747,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
         <v>620609</v>
       </c>
       <c r="R28" t="n">
-        <v>6648383</v>
+        <v>6648334</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3957,10 +3957,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123635541</v>
+        <v>123639666</v>
       </c>
       <c r="B30" t="n">
-        <v>57507</v>
+        <v>57644</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3973,42 +3973,51 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620556</v>
+        <v>620713</v>
       </c>
       <c r="R30" t="n">
-        <v>6648344</v>
+        <v>6648583</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4037,7 +4046,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4047,7 +4056,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4074,7 +4083,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123634710</v>
+        <v>123638984</v>
       </c>
       <c r="B31" t="n">
         <v>98079</v>
@@ -4107,34 +4116,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620635</v>
+        <v>620528</v>
       </c>
       <c r="R31" t="n">
-        <v>6648363</v>
+        <v>6648364</v>
       </c>
       <c r="S31" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4163,7 +4162,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4173,7 +4172,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4182,28 +4186,29 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123633877</v>
+        <v>123636168</v>
       </c>
       <c r="B32" t="n">
-        <v>57861</v>
+        <v>96332</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4212,55 +4217,45 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103015</v>
+        <v>53</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620537</v>
+        <v>620443</v>
       </c>
       <c r="R32" t="n">
-        <v>6648292</v>
+        <v>6648200</v>
       </c>
       <c r="S32" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4289,7 +4284,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4299,7 +4294,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4308,25 +4303,26 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123635547</v>
+        <v>123635230</v>
       </c>
       <c r="B33" t="n">
         <v>98079</v>
@@ -4361,7 +4357,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>92</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -4380,13 +4376,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620556</v>
+        <v>620593</v>
       </c>
       <c r="R33" t="n">
-        <v>6648344</v>
+        <v>6648376</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4415,7 +4411,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4425,7 +4421,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4452,7 +4448,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123634559</v>
+        <v>123634512</v>
       </c>
       <c r="B34" t="n">
         <v>98079</v>
@@ -4487,7 +4483,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -4506,10 +4502,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620614</v>
+        <v>620600</v>
       </c>
       <c r="R34" t="n">
-        <v>6648335</v>
+        <v>6648328</v>
       </c>
       <c r="S34" t="n">
         <v>12</v>
@@ -4541,7 +4537,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4551,7 +4547,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4578,10 +4574,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123632944</v>
+        <v>123637283</v>
       </c>
       <c r="B35" t="n">
-        <v>105095</v>
+        <v>96332</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4590,45 +4586,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221144</v>
+        <v>53</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620398</v>
+        <v>620603</v>
       </c>
       <c r="R35" t="n">
-        <v>6648248</v>
+        <v>6648146</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4657,7 +4649,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4667,12 +4659,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>25 bladrosetter</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4681,7 +4668,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4700,7 +4686,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123638047</v>
+        <v>123635547</v>
       </c>
       <c r="B36" t="n">
         <v>98079</v>
@@ -4733,20 +4719,34 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620519</v>
+        <v>620556</v>
       </c>
       <c r="R36" t="n">
-        <v>6648333</v>
+        <v>6648344</v>
       </c>
       <c r="S36" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4785,12 +4785,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4805,22 +4800,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123637481</v>
+        <v>123635666</v>
       </c>
       <c r="B37" t="n">
-        <v>56700</v>
+        <v>57644</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4829,46 +4824,55 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620714</v>
+        <v>620526</v>
       </c>
       <c r="R37" t="n">
-        <v>6648494</v>
+        <v>6648364</v>
       </c>
       <c r="S37" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4897,7 +4901,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4907,7 +4911,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4934,7 +4938,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123635824</v>
+        <v>123635032</v>
       </c>
       <c r="B38" t="n">
         <v>98079</v>
@@ -4969,7 +4973,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4988,10 +4992,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620523</v>
+        <v>620640</v>
       </c>
       <c r="R38" t="n">
-        <v>6648363</v>
+        <v>6648367</v>
       </c>
       <c r="S38" t="n">
         <v>12</v>
@@ -5023,7 +5027,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5033,7 +5037,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5060,10 +5064,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123635839</v>
+        <v>123638047</v>
       </c>
       <c r="B39" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5072,50 +5076,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620523</v>
+        <v>620519</v>
       </c>
       <c r="R39" t="n">
-        <v>6648363</v>
+        <v>6648333</v>
       </c>
       <c r="S39" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5144,7 +5139,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5154,7 +5149,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5169,19 +5169,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123634512</v>
+        <v>123634264</v>
       </c>
       <c r="B40" t="n">
         <v>98079</v>
@@ -5216,7 +5216,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -5235,13 +5235,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620600</v>
+        <v>620584</v>
       </c>
       <c r="R40" t="n">
-        <v>6648328</v>
+        <v>6648323</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5280,7 +5280,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5307,10 +5307,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123639666</v>
+        <v>123637481</v>
       </c>
       <c r="B41" t="n">
-        <v>57644</v>
+        <v>56700</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5319,40 +5319,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5361,13 +5352,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620713</v>
+        <v>620714</v>
       </c>
       <c r="R41" t="n">
-        <v>6648583</v>
+        <v>6648494</v>
       </c>
       <c r="S41" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5396,7 +5387,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5406,7 +5397,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5433,10 +5424,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123640236</v>
+        <v>123633877</v>
       </c>
       <c r="B42" t="n">
-        <v>105095</v>
+        <v>57861</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5449,41 +5440,51 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221144</v>
+        <v>103015</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620584</v>
+        <v>620537</v>
       </c>
       <c r="R42" t="n">
-        <v>6648414</v>
+        <v>6648292</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5512,7 +5513,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5522,7 +5523,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5531,29 +5532,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123634500</v>
+        <v>123641070</v>
       </c>
       <c r="B43" t="n">
-        <v>98079</v>
+        <v>74691</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5562,52 +5562,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Leight.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620604</v>
+        <v>620466</v>
       </c>
       <c r="R43" t="n">
-        <v>6648323</v>
+        <v>6648235</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
@@ -5639,7 +5625,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5649,7 +5635,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5676,10 +5662,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123641070</v>
+        <v>123635390</v>
       </c>
       <c r="B44" t="n">
-        <v>74691</v>
+        <v>90990</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5688,25 +5674,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6428</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5716,10 +5702,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620466</v>
+        <v>620591</v>
       </c>
       <c r="R44" t="n">
-        <v>6648235</v>
+        <v>6648347</v>
       </c>
       <c r="S44" t="n">
         <v>4</v>
@@ -5751,7 +5737,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5761,7 +5747,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5788,10 +5774,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123634264</v>
+        <v>123635541</v>
       </c>
       <c r="B45" t="n">
-        <v>98079</v>
+        <v>57507</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5800,40 +5786,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5842,13 +5819,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620584</v>
+        <v>620556</v>
       </c>
       <c r="R45" t="n">
-        <v>6648323</v>
+        <v>6648344</v>
       </c>
       <c r="S45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5877,7 +5854,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5887,7 +5864,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5914,7 +5891,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123634655</v>
+        <v>123634559</v>
       </c>
       <c r="B46" t="n">
         <v>98079</v>
@@ -5949,7 +5926,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>21</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -5968,13 +5945,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620626</v>
+        <v>620614</v>
       </c>
       <c r="R46" t="n">
-        <v>6648342</v>
+        <v>6648335</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6003,7 +5980,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -6013,7 +5990,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6040,10 +6017,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123637283</v>
+        <v>123634710</v>
       </c>
       <c r="B47" t="n">
-        <v>96332</v>
+        <v>98079</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6052,41 +6029,55 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620603</v>
+        <v>620635</v>
       </c>
       <c r="R47" t="n">
-        <v>6648146</v>
+        <v>6648363</v>
       </c>
       <c r="S47" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6115,7 +6106,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6125,7 +6116,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6140,22 +6131,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123638984</v>
+        <v>123635548</v>
       </c>
       <c r="B48" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6164,31 +6155,35 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
@@ -6196,13 +6191,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620528</v>
+        <v>620334</v>
       </c>
       <c r="R48" t="n">
-        <v>6648364</v>
+        <v>6648148</v>
       </c>
       <c r="S48" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6231,7 +6226,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6241,12 +6236,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>1 ex sjöng från tallgren</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6255,7 +6250,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -6274,10 +6268,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123635548</v>
+        <v>123640236</v>
       </c>
       <c r="B49" t="n">
-        <v>57644</v>
+        <v>105095</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6286,35 +6280,31 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>221144</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
@@ -6322,13 +6312,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620334</v>
+        <v>620584</v>
       </c>
       <c r="R49" t="n">
-        <v>6648148</v>
+        <v>6648414</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6357,7 +6347,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6367,12 +6357,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>10:51</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>1 ex sjöng från tallgren</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6381,6 +6366,7 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -6399,10 +6385,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123635032</v>
+        <v>123632944</v>
       </c>
       <c r="B50" t="n">
-        <v>98079</v>
+        <v>105095</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6411,55 +6397,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620640</v>
+        <v>620398</v>
       </c>
       <c r="R50" t="n">
-        <v>6648367</v>
+        <v>6648248</v>
       </c>
       <c r="S50" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6488,7 +6464,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6498,7 +6474,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>25 bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6507,28 +6488,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123635390</v>
+        <v>123635839</v>
       </c>
       <c r="B51" t="n">
-        <v>90990</v>
+        <v>57644</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6541,37 +6523,46 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620591</v>
+        <v>620523</v>
       </c>
       <c r="R51" t="n">
-        <v>6648347</v>
+        <v>6648363</v>
       </c>
       <c r="S51" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6600,7 +6591,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6610,7 +6601,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6637,10 +6628,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123636168</v>
+        <v>123634500</v>
       </c>
       <c r="B52" t="n">
-        <v>96332</v>
+        <v>98079</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6649,45 +6640,55 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620443</v>
+        <v>620604</v>
       </c>
       <c r="R52" t="n">
-        <v>6648200</v>
+        <v>6648323</v>
       </c>
       <c r="S52" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6716,7 +6717,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6726,7 +6727,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6735,19 +6736,18 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6866,10 +6866,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123635666</v>
+        <v>123634655</v>
       </c>
       <c r="B54" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6878,40 +6878,40 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6920,13 +6920,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620526</v>
+        <v>620626</v>
       </c>
       <c r="R54" t="n">
-        <v>6648364</v>
+        <v>6648342</v>
       </c>
       <c r="S54" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6992,7 +6992,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123635230</v>
+        <v>123635824</v>
       </c>
       <c r="B55" t="n">
         <v>98079</v>
@@ -7027,7 +7027,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -7046,13 +7046,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620593</v>
+        <v>620523</v>
       </c>
       <c r="R55" t="n">
-        <v>6648376</v>
+        <v>6648363</v>
       </c>
       <c r="S55" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -1258,10 +1258,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123404274</v>
+        <v>123407003</v>
       </c>
       <c r="B7" t="n">
-        <v>78433</v>
+        <v>98079</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,44 +1270,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620569</v>
+        <v>620581</v>
       </c>
       <c r="R7" t="n">
-        <v>6648238</v>
+        <v>6648381</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,19 +1335,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>13:08</t>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Mer än 35 bladrosetter</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,10 +1370,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123407003</v>
+        <v>123404274</v>
       </c>
       <c r="B8" t="n">
-        <v>98079</v>
+        <v>78433</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1386,45 +1382,44 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620581</v>
+        <v>620569</v>
       </c>
       <c r="R8" t="n">
-        <v>6648381</v>
+        <v>6648238</v>
       </c>
       <c r="S8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,14 +1446,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Mer än 35 bladrosetter</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1598,10 +1598,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123417364</v>
+        <v>123402991</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1610,41 +1610,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620549</v>
+        <v>620551</v>
       </c>
       <c r="R10" t="n">
-        <v>6648158</v>
+        <v>6648134</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1674,18 +1679,27 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:27</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1704,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123410527</v>
+        <v>123417364</v>
       </c>
       <c r="B11" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1716,31 +1730,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1748,13 +1761,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620777</v>
+        <v>620549</v>
       </c>
       <c r="R11" t="n">
-        <v>6648494</v>
+        <v>6648158</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1781,24 +1794,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1826,10 +1824,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123402991</v>
+        <v>123410527</v>
       </c>
       <c r="B12" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1838,49 +1836,45 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620551</v>
+        <v>620777</v>
       </c>
       <c r="R12" t="n">
-        <v>6648134</v>
+        <v>6648494</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,7 +1903,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1919,7 +1913,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1928,6 +1927,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2180,10 +2180,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123397574</v>
+        <v>123405294</v>
       </c>
       <c r="B15" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2192,46 +2192,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>620364</v>
+        <v>620610</v>
       </c>
       <c r="R15" t="n">
-        <v>6648233</v>
+        <v>6648299</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2263,7 +2255,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2273,12 +2265,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5 krokar på höjd</t>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2305,7 +2297,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123405294</v>
+        <v>123417333</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2339,16 +2331,20 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620610</v>
+        <v>620596</v>
       </c>
       <c r="R16" t="n">
-        <v>6648299</v>
+        <v>6648322</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2378,24 +2374,14 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:17</t>
-        </is>
-      </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2404,6 +2390,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2422,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123417333</v>
+        <v>123397574</v>
       </c>
       <c r="B17" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2434,31 +2421,35 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2466,10 +2457,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620596</v>
+        <v>620364</v>
       </c>
       <c r="R17" t="n">
-        <v>6648322</v>
+        <v>6648233</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2499,14 +2490,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>13 bladrosetter</t>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,7 +2516,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123417137</v>
+        <v>123406533</v>
       </c>
       <c r="B18" t="n">
-        <v>79406</v>
+        <v>96332</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2550,40 +2550,41 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>53</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620541</v>
+        <v>620593</v>
       </c>
       <c r="R18" t="n">
-        <v>6648142</v>
+        <v>6648325</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2610,9 +2611,24 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2874,10 +2890,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123406533</v>
+        <v>123417137</v>
       </c>
       <c r="B21" t="n">
-        <v>96332</v>
+        <v>79406</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2890,41 +2906,40 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620593</v>
+        <v>620541</v>
       </c>
       <c r="R21" t="n">
-        <v>6648325</v>
+        <v>6648142</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2951,24 +2966,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>14:12</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4686,10 +4686,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123635547</v>
+        <v>123635666</v>
       </c>
       <c r="B36" t="n">
-        <v>98079</v>
+        <v>57644</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4698,40 +4698,40 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4740,13 +4740,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620556</v>
+        <v>620526</v>
       </c>
       <c r="R36" t="n">
-        <v>6648344</v>
+        <v>6648364</v>
       </c>
       <c r="S36" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4785,7 +4785,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4812,10 +4812,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123635666</v>
+        <v>123635547</v>
       </c>
       <c r="B37" t="n">
-        <v>57644</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4824,40 +4824,40 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4866,13 +4866,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620526</v>
+        <v>620556</v>
       </c>
       <c r="R37" t="n">
-        <v>6648364</v>
+        <v>6648344</v>
       </c>
       <c r="S37" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD37" t="b">

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY56"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7242,6 +7242,516 @@
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125489625</v>
+      </c>
+      <c r="B57" t="n">
+        <v>74964</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Ramsmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>620619</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6648126</v>
+      </c>
+      <c r="S57" t="n">
+        <v>15</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125489618</v>
+      </c>
+      <c r="B58" t="n">
+        <v>96522</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>53</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Ramsmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>620511</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6648241</v>
+      </c>
+      <c r="S58" t="n">
+        <v>15</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125489622</v>
+      </c>
+      <c r="B59" t="n">
+        <v>78683</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Ramsmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>620607</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6648209</v>
+      </c>
+      <c r="S59" t="n">
+        <v>15</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>125489631</v>
+      </c>
+      <c r="B60" t="n">
+        <v>95766</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Ramsmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>620455</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6648217</v>
+      </c>
+      <c r="S60" t="n">
+        <v>15</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>125489624</v>
+      </c>
+      <c r="B61" t="n">
+        <v>74964</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>6426</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Kattfotslav</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Felipes leucopellaeus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Ramsmossen, Upl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>620437</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6648207</v>
+      </c>
+      <c r="S61" t="n">
+        <v>15</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -7244,37 +7244,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125489625</v>
+        <v>125489622</v>
       </c>
       <c r="B57" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78725</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6426</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7284,10 +7279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>620619</v>
+        <v>620607</v>
       </c>
       <c r="R57" t="n">
-        <v>6648126</v>
+        <v>6648209</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -7346,37 +7341,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125489618</v>
+        <v>125489625</v>
       </c>
       <c r="B58" t="n">
-        <v>96522</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>53</v>
+        <v>6426</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -7386,10 +7376,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>620511</v>
+        <v>620619</v>
       </c>
       <c r="R58" t="n">
-        <v>6648241</v>
+        <v>6648126</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -7448,15 +7438,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125489622</v>
+        <v>125489618</v>
       </c>
       <c r="B59" t="n">
-        <v>78683</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96577</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7464,21 +7449,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6446</v>
+        <v>53</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7488,10 +7473,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>620607</v>
+        <v>620511</v>
       </c>
       <c r="R59" t="n">
-        <v>6648209</v>
+        <v>6648241</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -7550,15 +7535,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125489631</v>
+        <v>125489624</v>
       </c>
       <c r="B60" t="n">
-        <v>95766</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75005</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7566,21 +7546,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7590,10 +7570,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>620455</v>
+        <v>620437</v>
       </c>
       <c r="R60" t="n">
-        <v>6648217</v>
+        <v>6648207</v>
       </c>
       <c r="S60" t="n">
         <v>15</v>
@@ -7652,15 +7632,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125489624</v>
+        <v>125489631</v>
       </c>
       <c r="B61" t="n">
-        <v>74964</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95820</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7668,21 +7643,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6426</v>
+        <v>2170</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7692,10 +7667,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>620437</v>
+        <v>620455</v>
       </c>
       <c r="R61" t="n">
-        <v>6648207</v>
+        <v>6648217</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -7441,7 +7441,7 @@
         <v>125489618</v>
       </c>
       <c r="B59" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>125489631</v>
       </c>
       <c r="B61" t="n">
-        <v>95820</v>
+        <v>95827</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -7247,7 +7247,7 @@
         <v>125489622</v>
       </c>
       <c r="B57" t="n">
-        <v>78725</v>
+        <v>78726</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>125489625</v>
       </c>
       <c r="B58" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>125489618</v>
       </c>
       <c r="B59" t="n">
-        <v>96584</v>
+        <v>96587</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>125489624</v>
       </c>
       <c r="B60" t="n">
-        <v>75005</v>
+        <v>75006</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>125489631</v>
       </c>
       <c r="B61" t="n">
-        <v>95827</v>
+        <v>95830</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -7247,7 +7247,7 @@
         <v>125489622</v>
       </c>
       <c r="B57" t="n">
-        <v>78726</v>
+        <v>78730</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>125489618</v>
       </c>
       <c r="B59" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>125489631</v>
       </c>
       <c r="B61" t="n">
-        <v>95830</v>
+        <v>95834</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -7441,7 +7441,7 @@
         <v>125489618</v>
       </c>
       <c r="B59" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>125489631</v>
       </c>
       <c r="B61" t="n">
-        <v>95834</v>
+        <v>95835</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -7247,7 +7247,7 @@
         <v>125489622</v>
       </c>
       <c r="B57" t="n">
-        <v>78730</v>
+        <v>78731</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>125489625</v>
       </c>
       <c r="B58" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>125489618</v>
       </c>
       <c r="B59" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>125489624</v>
       </c>
       <c r="B60" t="n">
-        <v>75006</v>
+        <v>75007</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>125489631</v>
       </c>
       <c r="B61" t="n">
-        <v>95835</v>
+        <v>95837</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -7441,7 +7441,7 @@
         <v>125489618</v>
       </c>
       <c r="B59" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>125489631</v>
       </c>
       <c r="B61" t="n">
-        <v>95837</v>
+        <v>95839</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -7441,7 +7441,7 @@
         <v>125489618</v>
       </c>
       <c r="B59" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>125489631</v>
       </c>
       <c r="B61" t="n">
-        <v>95839</v>
+        <v>95841</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -7247,7 +7247,7 @@
         <v>125489622</v>
       </c>
       <c r="B57" t="n">
-        <v>78731</v>
+        <v>78735</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>125489625</v>
       </c>
       <c r="B58" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7441,7 +7441,7 @@
         <v>125489618</v>
       </c>
       <c r="B59" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         <v>125489624</v>
       </c>
       <c r="B60" t="n">
-        <v>75007</v>
+        <v>75011</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>125489631</v>
       </c>
       <c r="B61" t="n">
-        <v>95841</v>
+        <v>95845</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -7441,7 +7441,7 @@
         <v>125489618</v>
       </c>
       <c r="B59" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7635,7 +7635,7 @@
         <v>125489631</v>
       </c>
       <c r="B61" t="n">
-        <v>95845</v>
+        <v>95848</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -3831,12 +3831,7 @@
         <v>123398368</v>
       </c>
       <c r="B29" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -3865,7 +3865,7 @@
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>parning/parningsceremonier</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -5773,7 +5773,7 @@
         <v>123635839</v>
       </c>
       <c r="B45" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -5773,7 +5773,7 @@
         <v>123635839</v>
       </c>
       <c r="B45" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 11833-2025 artfynd.xlsx
+++ b/artfynd/A 11833-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123401959</v>
+        <v>123406533</v>
       </c>
       <c r="B2" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>353</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>620544</v>
+        <v>620593</v>
       </c>
       <c r="R2" t="n">
-        <v>6648151</v>
+        <v>6648325</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +749,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +759,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På understa lågan</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,47 +792,38 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123399558</v>
+        <v>123636168</v>
       </c>
       <c r="B3" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -835,13 +831,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>620398</v>
+        <v>620443</v>
       </c>
       <c r="R3" t="n">
-        <v>6648248</v>
+        <v>6648200</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -865,22 +861,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,6 +885,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -907,15 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123404593</v>
+        <v>123637283</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,42 +915,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>620575</v>
+        <v>620603</v>
       </c>
       <c r="R4" t="n">
-        <v>6648228</v>
+        <v>6648146</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -982,22 +969,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,53 +1011,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123411112</v>
+        <v>125489618</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Ramsmossen, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>620609</v>
+        <v>620511</v>
       </c>
       <c r="R5" t="n">
-        <v>6648334</v>
+        <v>6648241</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1094,27 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:49</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:49</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>3 bladrosetter</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,61 +1108,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123402991</v>
+        <v>123401959</v>
       </c>
       <c r="B6" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>620551</v>
+        <v>620544</v>
       </c>
       <c r="R6" t="n">
-        <v>6648134</v>
+        <v>6648151</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1224,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1234,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:27</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1261,54 +1215,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123417333</v>
+        <v>123404274</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>620596</v>
+        <v>620569</v>
       </c>
       <c r="R7" t="n">
-        <v>6648322</v>
+        <v>6648238</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1338,14 +1286,19 @@
           <t>2025-03-23</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>13 bladrosetter</t>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1373,57 +1326,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123410978</v>
+        <v>123635390</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>620617</v>
+        <v>620591</v>
       </c>
       <c r="R8" t="n">
-        <v>6648344</v>
+        <v>6648347</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,17 +1391,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ca 30 bladrosetter</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,69 +1415,63 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123408488</v>
+        <v>123399110</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>620679</v>
+        <v>620370</v>
       </c>
       <c r="R9" t="n">
-        <v>6648540</v>
+        <v>6648255</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1560,7 +1503,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:19</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1570,12 +1513,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:19</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Mer än 10 bladrosetter</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,15 +1540,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123398864</v>
+        <v>123405636</v>
       </c>
       <c r="B10" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1618,42 +1551,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>620370</v>
+        <v>620633</v>
       </c>
       <c r="R10" t="n">
-        <v>6648255</v>
+        <v>6648297</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1685,7 +1610,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,12 +1620,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2 krokar på tallåga</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1727,57 +1647,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123407003</v>
+        <v>125489631</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>2170</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Ramsmossen, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>620581</v>
+        <v>620455</v>
       </c>
       <c r="R11" t="n">
-        <v>6648381</v>
+        <v>6648217</v>
       </c>
       <c r="S11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1801,17 +1712,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Mer än 35 bladrosetter</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1820,7 +1726,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1839,53 +1744,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123407548</v>
+        <v>123639324</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>620609</v>
+        <v>620521</v>
       </c>
       <c r="R12" t="n">
-        <v>6648383</v>
+        <v>6648416</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1909,27 +1809,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ca 10 bladrosetter</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,15 +1851,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123406069</v>
+        <v>123409705</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1972,21 +1862,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1996,10 +1886,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>620600</v>
+        <v>620866</v>
       </c>
       <c r="R13" t="n">
-        <v>6648303</v>
+        <v>6648512</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2031,7 +1921,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:54</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2041,12 +1931,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:54</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>12 bladrosetter</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2073,15 +1958,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123408853</v>
+        <v>123417364</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2089,41 +1969,40 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>620759</v>
+        <v>620549</v>
       </c>
       <c r="R14" t="n">
-        <v>6648492</v>
+        <v>6648158</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2150,24 +2029,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2198,16 +2062,11 @@
         <v>123409471</v>
       </c>
       <c r="B15" t="n">
-        <v>74840</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2311,61 +2170,48 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123397574</v>
+        <v>123634578</v>
       </c>
       <c r="B16" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>620364</v>
+        <v>620451</v>
       </c>
       <c r="R16" t="n">
-        <v>6648233</v>
+        <v>6648229</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2389,27 +2235,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:30</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>5 krokar på höjd</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2436,61 +2277,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123404576</v>
+        <v>125489624</v>
       </c>
       <c r="B17" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>6426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Ramsmossen, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>620575</v>
+        <v>620437</v>
       </c>
       <c r="R17" t="n">
-        <v>6648228</v>
+        <v>6648207</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2514,27 +2342,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2561,53 +2374,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123405636</v>
+        <v>125489625</v>
       </c>
       <c r="B18" t="n">
-        <v>95598</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75428</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2170</v>
+        <v>6426</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Ramsmossen, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>620633</v>
+        <v>620619</v>
       </c>
       <c r="R18" t="n">
-        <v>6648297</v>
+        <v>6648126</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2631,22 +2439,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:44</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2673,56 +2471,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123417137</v>
+        <v>123641070</v>
       </c>
       <c r="B19" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6453</v>
+        <v>6428</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>620541</v>
+        <v>620466</v>
       </c>
       <c r="R19" t="n">
-        <v>6648142</v>
+        <v>6648235</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2746,48 +2536,52 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123402052</v>
+        <v>125489622</v>
       </c>
       <c r="B20" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2795,37 +2589,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Ramsmossen, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620544</v>
+        <v>620607</v>
       </c>
       <c r="R20" t="n">
-        <v>6648151</v>
+        <v>6648209</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2849,22 +2643,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:05</t>
+          <t>2025-05-28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2891,37 +2675,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123399110</v>
+        <v>123402052</v>
       </c>
       <c r="B21" t="n">
-        <v>95598</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2170</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2931,10 +2710,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620370</v>
+        <v>620544</v>
       </c>
       <c r="R21" t="n">
-        <v>6648255</v>
+        <v>6648151</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2966,7 +2745,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2976,7 +2755,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3003,43 +2782,37 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123411227</v>
+        <v>123417137</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3047,13 +2820,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620502</v>
+        <v>620541</v>
       </c>
       <c r="R22" t="n">
-        <v>6648313</v>
+        <v>6648142</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3080,24 +2853,9 @@
           <t>2025-03-23</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-03-23</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3125,15 +2883,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123417364</v>
+        <v>123636266</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3141,40 +2894,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620549</v>
+        <v>620454</v>
       </c>
       <c r="R23" t="n">
-        <v>6648158</v>
+        <v>6648385</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3198,12 +2948,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3212,34 +2972,28 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123408009</v>
+        <v>123635541</v>
       </c>
       <c r="B24" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3247,45 +3001,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620718</v>
+        <v>620556</v>
       </c>
       <c r="R24" t="n">
-        <v>6648486</v>
+        <v>6648344</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3309,22 +3060,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:05</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3339,55 +3090,54 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123406533</v>
+        <v>123397574</v>
       </c>
       <c r="B25" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3395,10 +3145,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>620593</v>
+        <v>620364</v>
       </c>
       <c r="R25" t="n">
-        <v>6648325</v>
+        <v>6648233</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3430,7 +3180,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3440,12 +3190,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>På understa lågan</t>
+          <t>5 krokar på höjd</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3454,7 +3204,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3473,43 +3222,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123410527</v>
+        <v>123398864</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3517,10 +3265,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620777</v>
+        <v>620370</v>
       </c>
       <c r="R26" t="n">
-        <v>6648494</v>
+        <v>6648255</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3552,7 +3300,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3562,12 +3310,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ca 10 bladroseter</t>
+          <t>2 krokar på tallåga</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3576,7 +3324,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3595,53 +3342,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123404274</v>
+        <v>123399558</v>
       </c>
       <c r="B27" t="n">
-        <v>78455</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Bålmyran, norr om , Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620569</v>
+        <v>620398</v>
       </c>
       <c r="R27" t="n">
-        <v>6648238</v>
+        <v>6648248</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3673,7 +3420,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3683,7 +3430,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3692,7 +3439,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3711,53 +3457,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123405294</v>
+        <v>123402991</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620610</v>
+        <v>620551</v>
       </c>
       <c r="R28" t="n">
-        <v>6648299</v>
+        <v>6648134</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3786,7 +3535,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3796,12 +3545,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:17</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
+          <t>12:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3828,57 +3572,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123398368</v>
+        <v>123404576</v>
       </c>
       <c r="B29" t="n">
-        <v>57064</v>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>620347</v>
+        <v>620575</v>
       </c>
       <c r="R29" t="n">
-        <v>6648171</v>
+        <v>6648228</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3910,7 +3650,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3920,12 +3660,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Två stycken stöttes upp från samma ställe, flög tillsammans ca 20 meter söderut. Därefter hördes visslingar/sång</t>
+          <t>4 krokar under tall på häll. Ytterligare 4 st strax nedanför hällen, under gran</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3952,67 +3692,56 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123634500</v>
+        <v>123408009</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620604</v>
+        <v>620718</v>
       </c>
       <c r="R30" t="n">
-        <v>6648323</v>
+        <v>6648486</v>
       </c>
       <c r="S30" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4036,22 +3765,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>15:05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4066,65 +3795,68 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123638047</v>
+        <v>123409800</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620519</v>
+        <v>620856</v>
       </c>
       <c r="R31" t="n">
-        <v>6648333</v>
+        <v>6648480</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4148,27 +3880,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>12:46</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mer än 20 bladrosetter</t>
+          <t>16:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4195,67 +3922,56 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123635547</v>
+        <v>123409875</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620556</v>
+        <v>620848</v>
       </c>
       <c r="R32" t="n">
-        <v>6648344</v>
+        <v>6648449</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4279,22 +3995,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>16:07</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>4 krokar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4309,27 +4030,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123640236</v>
+        <v>123637481</v>
       </c>
       <c r="B33" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4337,41 +4053,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221144</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620584</v>
+        <v>620714</v>
       </c>
       <c r="R33" t="n">
-        <v>6648414</v>
+        <v>6648494</v>
       </c>
       <c r="S33" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4400,7 +4117,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4410,7 +4127,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4419,72 +4136,71 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123637283</v>
+        <v>123638405</v>
       </c>
       <c r="B34" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620603</v>
+        <v>620882</v>
       </c>
       <c r="R34" t="n">
-        <v>6648146</v>
+        <v>6648504</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4513,7 +4229,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4523,7 +4239,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4538,55 +4254,58 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123636168</v>
+        <v>123398368</v>
       </c>
       <c r="B35" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>53</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4594,13 +4313,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>620443</v>
+        <v>620347</v>
       </c>
       <c r="R35" t="n">
-        <v>6648200</v>
+        <v>6648171</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4624,22 +4343,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Två stycken stöttes upp från samma ställe, flög tillsammans ca 20 meter söderut. Därefter hördes visslingar/sång</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4648,7 +4372,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4667,37 +4390,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123639666</v>
+        <v>123633877</v>
       </c>
       <c r="B36" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4717,17 +4435,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>620713</v>
+        <v>620537</v>
       </c>
       <c r="R36" t="n">
-        <v>6648583</v>
+        <v>6648292</v>
       </c>
       <c r="S36" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4756,7 +4474,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4766,7 +4484,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4793,15 +4511,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123635541</v>
+        <v>123404593</v>
       </c>
       <c r="B37" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4809,42 +4522,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, norr om , Upl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>620556</v>
+        <v>620575</v>
       </c>
       <c r="R37" t="n">
-        <v>6648344</v>
+        <v>6648228</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4868,22 +4581,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4898,79 +4611,68 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123634559</v>
+        <v>123635548</v>
       </c>
       <c r="B38" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>620614</v>
+        <v>620334</v>
       </c>
       <c r="R38" t="n">
-        <v>6648335</v>
+        <v>6648148</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4999,7 +4701,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5009,7 +4711,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>10:52</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>1 ex sjöng från tallgren</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5024,64 +4731,59 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123634655</v>
+        <v>123635666</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5090,13 +4792,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>620626</v>
+        <v>620526</v>
       </c>
       <c r="R39" t="n">
-        <v>6648342</v>
+        <v>6648364</v>
       </c>
       <c r="S39" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5125,7 +4827,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5135,7 +4837,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5162,53 +4864,57 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123641070</v>
+        <v>123635839</v>
       </c>
       <c r="B40" t="n">
-        <v>74713</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6428</v>
+        <v>103021</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Leight.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>620466</v>
+        <v>620523</v>
       </c>
       <c r="R40" t="n">
-        <v>6648235</v>
+        <v>6648363</v>
       </c>
       <c r="S40" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5237,7 +4943,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5247,14 +4953,14 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
       <c r="AE40" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="b">
         <v>0</v>
@@ -5274,37 +4980,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123633877</v>
+        <v>123639666</v>
       </c>
       <c r="B41" t="n">
-        <v>57883</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103015</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -5324,17 +5025,17 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Grönmossen, Grönmossen, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>620537</v>
+        <v>620713</v>
       </c>
       <c r="R41" t="n">
-        <v>6648292</v>
+        <v>6648583</v>
       </c>
       <c r="S41" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5363,7 +5064,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5373,7 +5074,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5400,57 +5101,62 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123638984</v>
+        <v>123829229</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>620528</v>
+        <v>620373</v>
       </c>
       <c r="R42" t="n">
-        <v>6648364</v>
+        <v>6648191</v>
       </c>
       <c r="S42" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5474,27 +5180,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-04-07</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:13</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ca 20 bladrosetter</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5503,73 +5204,63 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123632944</v>
+        <v>123405294</v>
       </c>
       <c r="B43" t="n">
-        <v>105117</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>620398</v>
+        <v>620610</v>
       </c>
       <c r="R43" t="n">
-        <v>6648248</v>
+        <v>6648299</v>
       </c>
       <c r="S43" t="n">
         <v>25</v>
@@ -5596,27 +5287,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>25 bladrosetter</t>
+          <t>1 bladrosett, ca 35 m väster om hyggeskant</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5625,7 +5316,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5644,15 +5334,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123635230</v>
+        <v>123406069</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5677,34 +5362,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>620593</v>
+        <v>620600</v>
       </c>
       <c r="R44" t="n">
-        <v>6648376</v>
+        <v>6648303</v>
       </c>
       <c r="S44" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5728,22 +5399,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:12</t>
+          <t>13:54</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>12 bladrosetter</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5758,69 +5434,64 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123635839</v>
+        <v>123407003</v>
       </c>
       <c r="B45" t="n">
-        <v>58063</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Bålmyran, Morgongåva-Östfora, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>620523</v>
+        <v>620581</v>
       </c>
       <c r="R45" t="n">
-        <v>6648363</v>
+        <v>6648381</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5844,22 +5515,17 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>11:33</t>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Mer än 35 bladrosetter</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5868,33 +5534,29 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123634710</v>
+        <v>123407548</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5919,34 +5581,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>620635</v>
+        <v>620609</v>
       </c>
       <c r="R46" t="n">
-        <v>6648363</v>
+        <v>6648383</v>
       </c>
       <c r="S46" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5970,22 +5618,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ca 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6000,79 +5653,60 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123635666</v>
+        <v>123408488</v>
       </c>
       <c r="B47" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>620526</v>
+        <v>620679</v>
       </c>
       <c r="R47" t="n">
-        <v>6648364</v>
+        <v>6648540</v>
       </c>
       <c r="S47" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6096,22 +5730,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Mer än 10 bladrosetter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6126,27 +5765,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123634264</v>
+        <v>123408853</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6171,34 +5805,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>620584</v>
+        <v>620759</v>
       </c>
       <c r="R48" t="n">
-        <v>6648323</v>
+        <v>6648492</v>
       </c>
       <c r="S48" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6222,22 +5846,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:32</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>5 bladrosetter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6246,33 +5875,29 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123635032</v>
+        <v>123410527</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6297,34 +5922,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>620640</v>
+        <v>620777</v>
       </c>
       <c r="R49" t="n">
-        <v>6648367</v>
+        <v>6648494</v>
       </c>
       <c r="S49" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6348,22 +5963,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ca 10 bladroseter</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6372,33 +5992,29 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123634512</v>
+        <v>123410978</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6423,34 +6039,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>620600</v>
+        <v>620617</v>
       </c>
       <c r="R50" t="n">
-        <v>6648328</v>
+        <v>6648344</v>
       </c>
       <c r="S50" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6474,22 +6080,17 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>10:50</t>
+          <t>2025-03-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ca 30 bladrosetter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6498,33 +6099,29 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123635824</v>
+        <v>123411112</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6549,34 +6146,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>620523</v>
+        <v>620609</v>
       </c>
       <c r="R51" t="n">
-        <v>6648363</v>
+        <v>6648334</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6600,22 +6183,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>16:49</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>16:49</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>3 bladrosetter</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6630,65 +6218,64 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123635390</v>
+        <v>123411227</v>
       </c>
       <c r="B52" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Bålmyran, Bålmyran, Upl</t>
+          <t>Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>620591</v>
+        <v>620502</v>
       </c>
       <c r="R52" t="n">
-        <v>6648347</v>
+        <v>6648313</v>
       </c>
       <c r="S52" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6712,22 +6299,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6736,79 +6328,71 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Vilhelm Kroon</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123635548</v>
+        <v>123417333</v>
       </c>
       <c r="B53" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, norr om, Upl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>620334</v>
+        <v>620596</v>
       </c>
       <c r="R53" t="n">
-        <v>6648148</v>
+        <v>6648322</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6832,27 +6416,17 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1 ex sjöng från tallgren</t>
+          <t>13 bladrosetter</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6861,6 +6435,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -6879,53 +6454,62 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123634578</v>
+        <v>123634264</v>
       </c>
       <c r="B54" t="n">
-        <v>74840</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bålmyran, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>620451</v>
+        <v>620584</v>
       </c>
       <c r="R54" t="n">
-        <v>6648229</v>
+        <v>6648323</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6954,7 +6538,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6964,7 +6548,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6979,70 +6563,74 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123637481</v>
+        <v>123634500</v>
       </c>
       <c r="B55" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Grönmossen, Grönmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>620714</v>
+        <v>620604</v>
       </c>
       <c r="R55" t="n">
-        <v>6648494</v>
+        <v>6648323</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7071,7 +6659,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7081,7 +6669,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7108,52 +6696,47 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123829229</v>
+        <v>123634512</v>
       </c>
       <c r="B56" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7162,10 +6745,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>620373</v>
+        <v>620600</v>
       </c>
       <c r="R56" t="n">
-        <v>6648191</v>
+        <v>6648328</v>
       </c>
       <c r="S56" t="n">
         <v>12</v>
@@ -7192,22 +6775,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-07</t>
+          <t>2025-03-31</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7234,48 +6817,62 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>125489622</v>
+        <v>123634559</v>
       </c>
       <c r="B57" t="n">
-        <v>78735</v>
+        <v>99118</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ramsmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>620607</v>
+        <v>620614</v>
       </c>
       <c r="R57" t="n">
-        <v>6648209</v>
+        <v>6648335</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7299,12 +6896,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7319,60 +6926,74 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>125489625</v>
+        <v>123634655</v>
       </c>
       <c r="B58" t="n">
-        <v>75011</v>
+        <v>99118</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ramsmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>620619</v>
+        <v>620626</v>
       </c>
       <c r="R58" t="n">
-        <v>6648126</v>
+        <v>6648342</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7396,12 +7017,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>10:55</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7416,60 +7047,74 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>125489618</v>
+        <v>123634710</v>
       </c>
       <c r="B59" t="n">
-        <v>96605</v>
+        <v>99118</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ramsmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>620511</v>
+        <v>620635</v>
       </c>
       <c r="R59" t="n">
-        <v>6648241</v>
+        <v>6648363</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7493,12 +7138,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7513,60 +7168,74 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>125489624</v>
+        <v>123635032</v>
       </c>
       <c r="B60" t="n">
-        <v>75011</v>
+        <v>99118</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6426</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Kattfotslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Felipes leucopellaeus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Frisch &amp; G.Thor</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ramsmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>620437</v>
+        <v>620640</v>
       </c>
       <c r="R60" t="n">
-        <v>6648207</v>
+        <v>6648367</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7590,12 +7259,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7610,60 +7289,74 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>125489631</v>
+        <v>123635230</v>
       </c>
       <c r="B61" t="n">
-        <v>95848</v>
+        <v>99118</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2170</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Hedw.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ramsmossen, Upl</t>
+          <t>Bålmyran, Bålmyran, Upl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>620455</v>
+        <v>620593</v>
       </c>
       <c r="R61" t="n">
-        <v>6648217</v>
+        <v>6648376</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7687,12 +7380,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7707,15 +7410,715 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>123635547</v>
+      </c>
+      <c r="B62" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Bålmyran, Bålmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>620556</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6648344</v>
+      </c>
+      <c r="S62" t="n">
+        <v>5</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>123635824</v>
+      </c>
+      <c r="B63" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Bålmyran, Bålmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>620523</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6648363</v>
+      </c>
+      <c r="S63" t="n">
+        <v>12</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>11:32</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Emil V. Nilsson</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>123638047</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Bålmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>620519</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6648333</v>
+      </c>
+      <c r="S64" t="n">
+        <v>20</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>12:46</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Mer än 20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>123638984</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Bålmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>620528</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6648364</v>
+      </c>
+      <c r="S65" t="n">
+        <v>20</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ca 20 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>123632944</v>
+      </c>
+      <c r="B66" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Bålmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>620398</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6648248</v>
+      </c>
+      <c r="S66" t="n">
+        <v>25</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>25 bladrosetter</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>123640236</v>
+      </c>
+      <c r="B67" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Bålmyran, Upl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>620584</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6648414</v>
+      </c>
+      <c r="S67" t="n">
+        <v>20</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF67" t="inlineStr"/>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
